--- a/input/reg_partnership.xlsx
+++ b/input/reg_partnership.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B130E6B7-32EA-4A6C-97E1-4587A4E5C08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97DF83C3-6CAD-4F60-8222-4FDC6ADE1DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="28800" windowHeight="15345" tabRatio="901" activeTab="1" xr2:uid="{23DD8559-F003-43B3-945C-B71846295B58}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="17363" tabRatio="901" activeTab="3" xr2:uid="{23DD8559-F003-43B3-945C-B71846295B58}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="11" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="69">
   <si>
     <t>Constant</t>
   </si>
@@ -238,6 +238,12 @@
   <si>
     <t>COEFFICIENT</t>
   </si>
+  <si>
+    <t>Y2021</t>
+  </si>
+  <si>
+    <t>Y2020</t>
+  </si>
 </sst>
 </file>
 
@@ -311,8 +317,8 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="5" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="5"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -633,14 +639,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2912273F-E984-4B39-93F8-C80E0A415E58}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="2" width="10.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -648,7 +654,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>28</v>
       </c>
@@ -656,7 +662,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
@@ -664,7 +670,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
@@ -672,11 +678,11 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
         <v>47</v>
       </c>
@@ -684,7 +690,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -692,7 +698,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -700,7 +706,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -708,15 +714,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10"/>
       <c r="B10"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11"/>
       <c r="B11"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
         <v>51</v>
       </c>
@@ -724,13 +730,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13"/>
       <c r="B13" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14"/>
       <c r="B14" t="s">
         <v>54</v>
@@ -744,582 +750,582 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B222CC59-87EC-426E-9308-62866657AA83}">
   <dimension ref="A1:N13"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" style="6" customWidth="1"/>
-    <col min="2" max="16384" width="8.85546875" style="6"/>
+    <col min="1" max="1" width="19.3984375" style="5" customWidth="1"/>
+    <col min="2" max="16384" width="8.86328125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="5" t="s">
+      <c r="I1" t="s">
         <v>55</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="J1" t="s">
         <v>56</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="K1" t="s">
         <v>57</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="L1" t="s">
         <v>33</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="M1" t="s">
+        <v>67</v>
+      </c>
+      <c r="N1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>-0.14207781397738986</v>
+      <c r="B2" s="6">
+        <v>-0.2840886912379702</v>
       </c>
       <c r="C2">
-        <v>3.9099736512404268E-2</v>
+        <v>2.9541779993733086E-2</v>
       </c>
       <c r="D2">
-        <v>-2.618773595208243E-2</v>
+        <v>-2.5578353237355397E-3</v>
       </c>
       <c r="E2">
-        <v>5.8598518496328841E-4</v>
+        <v>6.2662675226170662E-6</v>
       </c>
       <c r="F2">
-        <v>3.7526975228583531E-3</v>
+        <v>1.3320581269483309E-2</v>
       </c>
       <c r="G2">
-        <v>1.0572877447602047E-2</v>
+        <v>1.3671028042921522E-2</v>
       </c>
       <c r="H2">
-        <v>2.3104007605285824E-2</v>
+        <v>2.7573207964958695E-2</v>
       </c>
       <c r="I2">
-        <v>3.123338556850451E-3</v>
+        <v>2.3129887129919886E-3</v>
       </c>
       <c r="J2">
-        <v>4.0560258119748914E-4</v>
+        <v>-2.9479554188526751E-2</v>
       </c>
       <c r="K2">
-        <v>-4.1727704056742893E-2</v>
+        <v>-2.5423569876370452E-2</v>
       </c>
       <c r="L2">
-        <v>-3.3616158247294754E-2</v>
+        <v>-7.0410427462576949E-4</v>
       </c>
       <c r="M2">
-        <v>1.4633370720082244E-3</v>
+        <v>6.085953448064646E-4</v>
       </c>
       <c r="N2">
-        <v>0.26993629683316778</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+        <v>5.5147526780065736E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>0.91595425602714586</v>
+      <c r="B3" s="6">
+        <v>-0.25206937001050272</v>
       </c>
       <c r="C3">
-        <v>-2.618773595208243E-2</v>
+        <v>-2.5578353237355397E-3</v>
       </c>
       <c r="D3">
-        <v>0.77227331779013397</v>
+        <v>0.57861766007757143</v>
       </c>
       <c r="E3">
-        <v>-1.7868253106205989E-2</v>
+        <v>-1.3382614522231408E-2</v>
       </c>
       <c r="F3">
-        <v>-3.7394954911670553E-2</v>
+        <v>4.0487682489863008E-2</v>
       </c>
       <c r="G3">
-        <v>-0.13967597249802388</v>
+        <v>3.7255360958022177E-2</v>
       </c>
       <c r="H3">
-        <v>6.6725660850274315E-2</v>
+        <v>0.10955157670010918</v>
       </c>
       <c r="I3">
-        <v>-8.0128946048574345E-3</v>
+        <v>1.6276958218040316E-2</v>
       </c>
       <c r="J3">
-        <v>-4.7346964551454485E-2</v>
+        <v>-1.8152585462073989E-2</v>
       </c>
       <c r="K3">
-        <v>-0.10753579576157302</v>
+        <v>-6.4625912321536028E-2</v>
       </c>
       <c r="L3">
-        <v>-1.6805353605709783E-2</v>
+        <v>-6.7974844372706567E-3</v>
       </c>
       <c r="M3">
-        <v>1.4029596075838535E-3</v>
+        <v>3.7344190567253799E-2</v>
       </c>
       <c r="N3">
-        <v>-7.9691541135136958</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+        <v>-6.121371225664566</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>-2.2270470896169778E-2</v>
+      <c r="B4" s="6">
+        <v>6.5808976426778298E-3</v>
       </c>
       <c r="C4">
-        <v>5.8598518496328841E-4</v>
+        <v>6.2662675226170662E-6</v>
       </c>
       <c r="D4">
-        <v>-1.7868253106205989E-2</v>
+        <v>-1.3382614522231408E-2</v>
       </c>
       <c r="E4">
-        <v>4.1502823114809503E-4</v>
+        <v>3.1018879801113572E-4</v>
       </c>
       <c r="F4">
-        <v>7.2805086520663642E-4</v>
+        <v>-9.162241764238202E-4</v>
       </c>
       <c r="G4">
-        <v>3.08056731284026E-3</v>
+        <v>-9.4915709235881413E-4</v>
       </c>
       <c r="H4">
-        <v>-1.5257164527659236E-3</v>
+        <v>-2.5070301086740979E-3</v>
       </c>
       <c r="I4">
-        <v>2.5399765414441458E-4</v>
+        <v>-4.0725462385995601E-4</v>
       </c>
       <c r="J4">
-        <v>1.1689079215027876E-3</v>
+        <v>4.2481571518158262E-4</v>
       </c>
       <c r="K4">
-        <v>2.6427450608180192E-3</v>
+        <v>1.4959234215940441E-3</v>
       </c>
       <c r="L4">
-        <v>3.3224448668943418E-4</v>
+        <v>1.749693547104538E-4</v>
       </c>
       <c r="M4">
-        <v>-9.1271085454844997E-6</v>
+        <v>-8.9052618655723406E-4</v>
       </c>
       <c r="N4">
-        <v>0.18306269763041705</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+        <v>0.1411588130000897</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>-0.32709430964378433</v>
+      <c r="B5" s="6">
+        <v>4.6279186617954722E-2</v>
       </c>
       <c r="C5">
-        <v>3.7526975228583531E-3</v>
+        <v>1.3320581269483309E-2</v>
       </c>
       <c r="D5">
-        <v>-3.7394954911670553E-2</v>
+        <v>4.0487682489863008E-2</v>
       </c>
       <c r="E5">
-        <v>7.2805086520663642E-4</v>
+        <v>-9.162241764238202E-4</v>
       </c>
       <c r="F5">
-        <v>7.0513101545748871E-2</v>
+        <v>4.8942010191554135E-2</v>
       </c>
       <c r="G5">
-        <v>1.996431402641629E-2</v>
+        <v>2.8185882840745854E-2</v>
       </c>
       <c r="H5">
-        <v>6.1561442211249453E-3</v>
+        <v>3.8001972865971942E-2</v>
       </c>
       <c r="I5">
-        <v>-3.3204129319544164E-3</v>
+        <v>1.1449653397380102E-2</v>
       </c>
       <c r="J5">
-        <v>-5.3198194806704071E-3</v>
+        <v>-4.3602589610730403E-3</v>
       </c>
       <c r="K5">
-        <v>-3.791241687210989E-3</v>
+        <v>-3.3374883425856865E-2</v>
       </c>
       <c r="L5">
-        <v>6.4611284148303316E-3</v>
+        <v>1.7560992542596172E-3</v>
       </c>
       <c r="M5">
-        <v>3.9370561063523622E-3</v>
+        <v>1.1888485704539006E-2</v>
       </c>
       <c r="N5">
-        <v>0.39982721517354414</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+        <v>-0.53484333906392145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>-0.15178401145857037</v>
+      <c r="B6" s="6">
+        <v>1.7998765142206202E-2</v>
       </c>
       <c r="C6">
-        <v>1.0572877447602047E-2</v>
+        <v>1.3671028042921522E-2</v>
       </c>
       <c r="D6">
-        <v>-0.13967597249802388</v>
+        <v>3.7255360958022177E-2</v>
       </c>
       <c r="E6">
-        <v>3.08056731284026E-3</v>
+        <v>-9.4915709235881413E-4</v>
       </c>
       <c r="F6">
-        <v>1.996431402641629E-2</v>
+        <v>2.8185882840745854E-2</v>
       </c>
       <c r="G6">
-        <v>4.1233758580018598E-2</v>
+        <v>5.7429789955957142E-2</v>
       </c>
       <c r="H6">
-        <v>-1.822709277687808E-2</v>
+        <v>2.8814445088112817E-2</v>
       </c>
       <c r="I6">
-        <v>-4.4678536908201588E-3</v>
+        <v>1.4554887055156947E-2</v>
       </c>
       <c r="J6">
-        <v>4.0601149925975979E-3</v>
+        <v>1.0257338815439554E-2</v>
       </c>
       <c r="K6">
-        <v>-2.6529309933064904E-3</v>
+        <v>-1.7130375702767001E-2</v>
       </c>
       <c r="L6">
-        <v>1.4722325361961608E-3</v>
+        <v>3.9658476758358194E-4</v>
       </c>
       <c r="M6">
-        <v>-2.1085473478027611E-3</v>
+        <v>8.7658736760209965E-4</v>
       </c>
       <c r="N6">
-        <v>1.5538975083032049</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+        <v>-0.45388867868933414</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>-6.2890788086950353E-2</v>
+      <c r="B7" s="6">
+        <v>-6.3698248161157739E-2</v>
       </c>
       <c r="C7">
-        <v>2.3104007605285824E-2</v>
+        <v>2.7573207964958695E-2</v>
       </c>
       <c r="D7">
-        <v>6.6725660850274315E-2</v>
+        <v>0.10955157670010918</v>
       </c>
       <c r="E7">
-        <v>-1.5257164527659236E-3</v>
+        <v>-2.5070301086740979E-3</v>
       </c>
       <c r="F7">
-        <v>6.1561442211249453E-3</v>
+        <v>3.8001972865971942E-2</v>
       </c>
       <c r="G7">
-        <v>-1.822709277687808E-2</v>
+        <v>2.8814445088112817E-2</v>
       </c>
       <c r="H7">
-        <v>0.10911202882183177</v>
+        <v>0.13604428914000033</v>
       </c>
       <c r="I7">
-        <v>-5.4740086371200536E-3</v>
+        <v>-8.5607432264020733E-3</v>
       </c>
       <c r="J7">
-        <v>-3.2259892463744194E-2</v>
+        <v>6.5825189628000574E-3</v>
       </c>
       <c r="K7">
-        <v>-7.0095466919185556E-3</v>
+        <v>-1.4750376305774859E-2</v>
       </c>
       <c r="L7">
-        <v>7.1115188747810087E-3</v>
+        <v>-1.4671900726484499E-4</v>
       </c>
       <c r="M7">
-        <v>1.3879288912782145E-3</v>
+        <v>1.3230390764952193E-2</v>
       </c>
       <c r="N7">
-        <v>-0.61313481186356</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>8.0314423940431381E-2</v>
+        <v>-1.1765589494266941</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A8" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="6">
+        <v>-0.13402417320103474</v>
       </c>
       <c r="C8">
-        <v>3.123338556850451E-3</v>
+        <v>2.3129887129919886E-3</v>
       </c>
       <c r="D8">
-        <v>-8.0128946048574345E-3</v>
+        <v>1.6276958218040316E-2</v>
       </c>
       <c r="E8">
-        <v>2.5399765414441458E-4</v>
+        <v>-4.0725462385995601E-4</v>
       </c>
       <c r="F8">
-        <v>-3.3204129319544164E-3</v>
+        <v>1.1449653397380102E-2</v>
       </c>
       <c r="G8">
-        <v>-4.4678536908201588E-3</v>
+        <v>1.4554887055156947E-2</v>
       </c>
       <c r="H8">
-        <v>-5.4740086371200536E-3</v>
+        <v>-8.5607432264020733E-3</v>
       </c>
       <c r="I8">
-        <v>6.2801808381461122E-3</v>
+        <v>1.0667553138943577E-2</v>
       </c>
       <c r="J8">
-        <v>6.4121021336828142E-3</v>
+        <v>-4.3987815815048781E-3</v>
       </c>
       <c r="K8">
-        <v>4.028493455235406E-3</v>
+        <v>-1.3860946672362592E-2</v>
       </c>
       <c r="L8">
-        <v>-4.3032014843607316E-3</v>
+        <v>-8.2025653407757047E-5</v>
       </c>
       <c r="M8">
-        <v>1.159068718196727E-3</v>
+        <v>-7.6958421494116918E-3</v>
       </c>
       <c r="N8">
-        <v>8.3563390140843907E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9">
-        <v>-6.9952798698799626E-2</v>
+        <v>-0.20342254550920827</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A9" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="6">
+        <v>0.42911226313069628</v>
       </c>
       <c r="C9">
-        <v>4.0560258119748914E-4</v>
+        <v>-2.9479554188526751E-2</v>
       </c>
       <c r="D9">
-        <v>-4.7346964551454485E-2</v>
+        <v>-1.8152585462073989E-2</v>
       </c>
       <c r="E9">
-        <v>1.1689079215027876E-3</v>
+        <v>4.2481571518158262E-4</v>
       </c>
       <c r="F9">
-        <v>-5.3198194806704071E-3</v>
+        <v>-4.3602589610730403E-3</v>
       </c>
       <c r="G9">
-        <v>4.0601149925975979E-3</v>
+        <v>1.0257338815439554E-2</v>
       </c>
       <c r="H9">
-        <v>-3.2259892463744194E-2</v>
+        <v>6.5825189628000574E-3</v>
       </c>
       <c r="I9">
-        <v>6.4121021336828142E-3</v>
+        <v>-4.3987815815048781E-3</v>
       </c>
       <c r="J9">
-        <v>1.6737684879381386E-2</v>
+        <v>9.34396333705345E-2</v>
       </c>
       <c r="K9">
-        <v>7.795262747052889E-4</v>
+        <v>7.3522939303523244E-2</v>
       </c>
       <c r="L9">
-        <v>-1.6463150465742392E-2</v>
+        <v>-5.4430737972279049E-4</v>
       </c>
       <c r="M9">
-        <v>1.5430686955089073E-3</v>
+        <v>1.4668354378948274E-2</v>
       </c>
       <c r="N9">
-        <v>0.38657918714809858</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10">
-        <v>0.28698026707993862</v>
+        <v>0.1529605834722817</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A10" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="6">
+        <v>0.47224265310637092</v>
       </c>
       <c r="C10">
-        <v>-4.1727704056742893E-2</v>
+        <v>-2.5423569876370452E-2</v>
       </c>
       <c r="D10">
-        <v>-0.10753579576157302</v>
+        <v>-6.4625912321536028E-2</v>
       </c>
       <c r="E10">
-        <v>2.6427450608180192E-3</v>
+        <v>1.4959234215940441E-3</v>
       </c>
       <c r="F10">
-        <v>-3.791241687210989E-3</v>
+        <v>-3.3374883425856865E-2</v>
       </c>
       <c r="G10">
-        <v>-2.6529309933064904E-3</v>
+        <v>-1.7130375702767001E-2</v>
       </c>
       <c r="H10">
-        <v>-7.0095466919185556E-3</v>
+        <v>-1.4750376305774859E-2</v>
       </c>
       <c r="I10">
-        <v>4.028493455235406E-3</v>
+        <v>-1.3860946672362592E-2</v>
       </c>
       <c r="J10">
-        <v>7.795262747052889E-4</v>
+        <v>7.3522939303523244E-2</v>
       </c>
       <c r="K10">
-        <v>0.11758966698153482</v>
+        <v>8.5915325054860298E-2</v>
       </c>
       <c r="L10">
-        <v>7.6596526702307391E-2</v>
+        <v>-1.2102644213285297E-3</v>
       </c>
       <c r="M10">
-        <v>-2.3975540522050975E-3</v>
+        <v>2.1715529132701819E-3</v>
       </c>
       <c r="N10">
-        <v>1.0528365402341322</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11">
-        <v>0.4029488529453894</v>
+        <v>0.7221736432427166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="6">
+        <v>-1.2493063330274528E-3</v>
       </c>
       <c r="C11">
-        <v>-3.3616158247294754E-2</v>
+        <v>-7.0410427462576949E-4</v>
       </c>
       <c r="D11">
-        <v>-1.6805353605709783E-2</v>
+        <v>-6.7974844372706567E-3</v>
       </c>
       <c r="E11">
-        <v>3.3224448668943418E-4</v>
+        <v>1.749693547104538E-4</v>
       </c>
       <c r="F11">
-        <v>6.4611284148303316E-3</v>
+        <v>1.7560992542596172E-3</v>
       </c>
       <c r="G11">
-        <v>1.4722325361961608E-3</v>
+        <v>3.9658476758358194E-4</v>
       </c>
       <c r="H11">
-        <v>7.1115188747810087E-3</v>
+        <v>-1.4671900726484499E-4</v>
       </c>
       <c r="I11">
-        <v>-4.3032014843607316E-3</v>
+        <v>-8.2025653407757047E-5</v>
       </c>
       <c r="J11">
-        <v>-1.6463150465742392E-2</v>
+        <v>-5.4430737972279049E-4</v>
       </c>
       <c r="K11">
-        <v>7.6596526702307391E-2</v>
+        <v>-1.2102644213285297E-3</v>
       </c>
       <c r="L11">
-        <v>9.0075935470496415E-2</v>
+        <v>1.2127664679174677E-3</v>
       </c>
       <c r="M11">
-        <v>-5.6347966817148973E-3</v>
+        <v>-6.3754207965684342E-3</v>
       </c>
       <c r="N11">
-        <v>0.29678918708959046</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12">
-        <v>-6.443959417262439E-2</v>
+        <v>4.5936951895988273E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A12" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="6">
+        <v>0.16362499178502155</v>
       </c>
       <c r="C12">
-        <v>1.4633370720082244E-3</v>
+        <v>6.085953448064646E-4</v>
       </c>
       <c r="D12">
-        <v>1.4029596075838535E-3</v>
+        <v>3.7344190567253799E-2</v>
       </c>
       <c r="E12">
-        <v>-9.1271085454844997E-6</v>
+        <v>-8.9052618655723406E-4</v>
       </c>
       <c r="F12">
-        <v>3.9370561063523622E-3</v>
+        <v>1.1888485704539006E-2</v>
       </c>
       <c r="G12">
-        <v>-2.1085473478027611E-3</v>
+        <v>8.7658736760209965E-4</v>
       </c>
       <c r="H12">
-        <v>1.3879288912782145E-3</v>
+        <v>1.3230390764952193E-2</v>
       </c>
       <c r="I12">
-        <v>1.159068718196727E-3</v>
+        <v>-7.6958421494116918E-3</v>
       </c>
       <c r="J12">
-        <v>1.5430686955089073E-3</v>
+        <v>1.4668354378948274E-2</v>
       </c>
       <c r="K12">
-        <v>-2.3975540522050975E-3</v>
+        <v>2.1715529132701819E-3</v>
       </c>
       <c r="L12">
-        <v>-5.6347966817148973E-3</v>
+        <v>-6.3754207965684342E-3</v>
       </c>
       <c r="M12">
-        <v>1.45632446695021E-3</v>
+        <v>0.14240684916410903</v>
       </c>
       <c r="N12">
-        <v>-5.0505140231000029E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+        <v>-0.27319150736771303</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A13" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B13">
-        <v>-11.295675051520156</v>
+      <c r="B13" s="6">
+        <v>-0.30919028847181518</v>
       </c>
       <c r="C13">
-        <v>0.26993629683316778</v>
+        <v>5.5147526780065736E-2</v>
       </c>
       <c r="D13">
-        <v>-7.9691541135136958</v>
+        <v>-6.121371225664566</v>
       </c>
       <c r="E13">
-        <v>0.18306269763041705</v>
+        <v>0.1411588130000897</v>
       </c>
       <c r="F13">
-        <v>0.39982721517354414</v>
+        <v>-0.53484333906392145</v>
       </c>
       <c r="G13">
-        <v>1.5538975083032049</v>
+        <v>-0.45388867868933414</v>
       </c>
       <c r="H13">
-        <v>-0.61313481186356</v>
+        <v>-1.1765589494266941</v>
       </c>
       <c r="I13">
-        <v>8.3563390140843907E-3</v>
+        <v>-0.20342254550920827</v>
       </c>
       <c r="J13">
-        <v>0.38657918714809858</v>
+        <v>0.1529605834722817</v>
       </c>
       <c r="K13">
-        <v>1.0528365402341322</v>
+        <v>0.7221736432427166</v>
       </c>
       <c r="L13">
-        <v>0.29678918708959046</v>
+        <v>4.5936951895988273E-2</v>
       </c>
       <c r="M13">
-        <v>-5.0505140231000029E-2</v>
+        <v>-0.27319150736771303</v>
       </c>
       <c r="N13">
-        <v>83.733272096101246</v>
+        <v>65.545831199619812</v>
       </c>
     </row>
   </sheetData>
@@ -1329,17 +1335,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9B78B7B-0319-4FC5-9F77-F32E3D0A2357}">
-  <dimension ref="A1:AA26"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AC28"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" customWidth="1"/>
+    <col min="1" max="1" width="29.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="6" t="s">
         <v>66</v>
       </c>
       <c r="C1" t="s">
@@ -1415,2082 +1421,2416 @@
         <v>33</v>
       </c>
       <c r="AA1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>2.3805611114292843E-2</v>
+      <c r="B2" s="6">
+        <v>2.2650660100977115E-2</v>
       </c>
       <c r="C2">
-        <v>9.2996636656408435E-5</v>
+        <v>6.6144915045992654E-5</v>
       </c>
       <c r="D2">
-        <v>-1.0122218232827859E-6</v>
+        <v>-7.1724850940022866E-7</v>
       </c>
       <c r="E2">
-        <v>5.506590880087806E-5</v>
+        <v>3.8541160513129815E-5</v>
       </c>
       <c r="F2">
-        <v>3.5675310834236591E-7</v>
+        <v>3.8459080992273237E-5</v>
       </c>
       <c r="G2">
-        <v>1.1516588968841677E-5</v>
+        <v>4.0604339951309961E-6</v>
       </c>
       <c r="H2">
-        <v>1.2538761013920286E-4</v>
+        <v>3.359865104772845E-5</v>
       </c>
       <c r="I2">
-        <v>-1.2683050403921307E-4</v>
+        <v>-7.6118787044420405E-5</v>
       </c>
       <c r="J2">
-        <v>2.382030087482881E-4</v>
+        <v>1.2628636207495626E-4</v>
       </c>
       <c r="K2">
-        <v>-5.6701671151218082E-5</v>
+        <v>-2.9258057911208703E-5</v>
       </c>
       <c r="L2">
-        <v>-5.7248221353960719E-5</v>
+        <v>-4.5080397324237878E-5</v>
       </c>
       <c r="M2">
-        <v>-2.0404206844034972E-4</v>
+        <v>-7.6355945419629868E-5</v>
       </c>
       <c r="N2">
-        <v>6.8924155807696517E-5</v>
+        <v>-8.9811639071983346E-7</v>
       </c>
       <c r="O2">
-        <v>-7.8907894174247472E-5</v>
+        <v>-1.4243661615498507E-4</v>
       </c>
       <c r="P2">
-        <v>-1.9348500366965689E-4</v>
+        <v>-2.108862071695163E-4</v>
       </c>
       <c r="Q2">
-        <v>-2.0538462979886166E-4</v>
+        <v>-2.4974769598487431E-4</v>
       </c>
       <c r="R2">
-        <v>9.9086668147713283E-6</v>
+        <v>-6.3330174480018749E-5</v>
       </c>
       <c r="S2">
-        <v>9.2292659783235821E-5</v>
+        <v>6.7302917304754657E-5</v>
       </c>
       <c r="T2">
-        <v>-8.8814752344549717E-5</v>
+        <v>-2.4815879461119407E-5</v>
       </c>
       <c r="U2">
-        <v>-9.9942440618480544E-5</v>
+        <v>8.2571381940919788E-6</v>
       </c>
       <c r="V2">
-        <v>-2.1073227776707956E-5</v>
+        <v>5.7835062224182571E-5</v>
       </c>
       <c r="W2">
-        <v>1.0298972521610456E-4</v>
+        <v>1.2735351168067198E-4</v>
       </c>
       <c r="X2">
-        <v>-2.0892343686299691E-5</v>
+        <v>-2.9693500119010348E-5</v>
       </c>
       <c r="Y2">
-        <v>5.6416418968749556E-5</v>
+        <v>1.5571456501394876E-5</v>
       </c>
       <c r="Z2">
-        <v>4.667843896244959E-6</v>
+        <v>1.9103593262135595E-6</v>
       </c>
       <c r="AA2">
-        <v>-1.868090169805151E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+        <v>1.8223907379184856E-5</v>
+      </c>
+      <c r="AB2">
+        <v>8.9907345621433564E-5</v>
+      </c>
+      <c r="AC2">
+        <v>-1.2876505408453084E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>-3.7183322310481806E-4</v>
+      <c r="B3" s="6">
+        <v>-3.7572201545191974E-4</v>
       </c>
       <c r="C3">
-        <v>-1.0122218232827859E-6</v>
+        <v>-7.1724850940022866E-7</v>
       </c>
       <c r="D3">
-        <v>1.1596784056276834E-8</v>
+        <v>8.1940545578761826E-9</v>
       </c>
       <c r="E3">
-        <v>-6.9781285125149641E-7</v>
+        <v>-4.5427265999482332E-7</v>
       </c>
       <c r="F3">
-        <v>-2.8272488675793919E-7</v>
+        <v>-5.5648177502340114E-7</v>
       </c>
       <c r="G3">
-        <v>9.7199435523698725E-8</v>
+        <v>1.2424565140238948E-7</v>
       </c>
       <c r="H3">
-        <v>-8.6923131616583186E-7</v>
+        <v>1.7147924153705483E-7</v>
       </c>
       <c r="I3">
-        <v>1.247034454349264E-6</v>
+        <v>8.4874356927794072E-7</v>
       </c>
       <c r="J3">
-        <v>-4.0913831691643275E-6</v>
+        <v>-2.4508810230758713E-6</v>
       </c>
       <c r="K3">
-        <v>2.8144051931686538E-7</v>
+        <v>2.7776464583152683E-8</v>
       </c>
       <c r="L3">
-        <v>5.4526236658703974E-7</v>
+        <v>4.1099655365643492E-7</v>
       </c>
       <c r="M3">
-        <v>2.3342694071391416E-6</v>
+        <v>7.9437672360943896E-7</v>
       </c>
       <c r="N3">
-        <v>-7.4488190819115847E-7</v>
+        <v>1.5935842873785472E-7</v>
       </c>
       <c r="O3">
-        <v>6.3039984887366727E-7</v>
+        <v>1.5656349882650757E-6</v>
       </c>
       <c r="P3">
-        <v>1.8900745063745474E-6</v>
+        <v>2.2983261389426365E-6</v>
       </c>
       <c r="Q3">
-        <v>1.6961179499678863E-6</v>
+        <v>2.5562790126732803E-6</v>
       </c>
       <c r="R3">
-        <v>-8.8739646994525231E-9</v>
+        <v>7.0556436762683465E-7</v>
       </c>
       <c r="S3">
-        <v>-7.9066206450086279E-7</v>
+        <v>-5.1019457887426699E-7</v>
       </c>
       <c r="T3">
-        <v>1.0176751154849027E-6</v>
+        <v>2.3258793653721198E-7</v>
       </c>
       <c r="U3">
-        <v>9.3372537852237623E-7</v>
+        <v>-2.014664334014142E-7</v>
       </c>
       <c r="V3">
-        <v>6.1979349151858002E-7</v>
+        <v>-3.6559205822970531E-7</v>
       </c>
       <c r="W3">
-        <v>-5.422534230578261E-7</v>
+        <v>-9.2195479166456578E-7</v>
       </c>
       <c r="X3">
-        <v>1.4427746893717043E-7</v>
+        <v>2.3049860915558057E-7</v>
       </c>
       <c r="Y3">
-        <v>-7.0435708457544893E-7</v>
+        <v>-2.4775433473414816E-7</v>
       </c>
       <c r="Z3">
-        <v>-7.1458661797853307E-8</v>
+        <v>-3.5130397686171473E-8</v>
       </c>
       <c r="AA3">
-        <v>1.9700787690689118E-5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+        <v>-1.3754759373152996E-7</v>
+      </c>
+      <c r="AB3">
+        <v>-1.0212721864964888E-6</v>
+      </c>
+      <c r="AC3">
+        <v>1.3313527183669973E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B4">
-        <v>-0.17807180320490448</v>
+      <c r="B4" s="6">
+        <v>-0.15590694135262034</v>
       </c>
       <c r="C4">
-        <v>5.506590880087806E-5</v>
+        <v>3.8541160513129815E-5</v>
       </c>
       <c r="D4">
-        <v>-6.9781285125149641E-7</v>
+        <v>-4.5427265999482332E-7</v>
       </c>
       <c r="E4">
-        <v>4.2697480382741376E-3</v>
+        <v>2.8263405674097564E-3</v>
       </c>
       <c r="F4">
-        <v>3.5615140093344594E-3</v>
+        <v>2.2935170929283197E-3</v>
       </c>
       <c r="G4">
-        <v>-1.031427629690382E-3</v>
+        <v>-6.444447507266127E-4</v>
       </c>
       <c r="H4">
-        <v>-1.8044191652533314E-3</v>
+        <v>-1.7312885501741114E-3</v>
       </c>
       <c r="I4">
-        <v>-4.2946159367491491E-4</v>
+        <v>-3.7964705342244929E-4</v>
       </c>
       <c r="J4">
-        <v>1.0706968087990403E-4</v>
+        <v>-5.1427315352145704E-5</v>
       </c>
       <c r="K4">
-        <v>2.7745882577032755E-3</v>
+        <v>2.2707139165173873E-3</v>
       </c>
       <c r="L4">
-        <v>7.1431219125250584E-4</v>
+        <v>5.2590149333781315E-4</v>
       </c>
       <c r="M4">
-        <v>4.8524896107759975E-5</v>
+        <v>2.3541705924100406E-4</v>
       </c>
       <c r="N4">
-        <v>-1.0999530469873591E-4</v>
+        <v>8.0366711090506312E-6</v>
       </c>
       <c r="O4">
-        <v>-6.4944203977448597E-4</v>
+        <v>-4.3596226691410169E-4</v>
       </c>
       <c r="P4">
-        <v>-3.9627258200331417E-4</v>
+        <v>-2.8653758643618874E-4</v>
       </c>
       <c r="Q4">
-        <v>1.1722402915741155E-3</v>
+        <v>5.4794009906040855E-4</v>
       </c>
       <c r="R4">
-        <v>-5.8590788951267902E-5</v>
+        <v>-4.187421864698657E-5</v>
       </c>
       <c r="S4">
-        <v>-4.4395472444917397E-4</v>
+        <v>-7.1783076106090465E-5</v>
       </c>
       <c r="T4">
-        <v>-1.3506579339424155E-4</v>
+        <v>-7.0655755344125904E-5</v>
       </c>
       <c r="U4">
-        <v>-1.4978393960504824E-4</v>
+        <v>-7.9132332565974854E-5</v>
       </c>
       <c r="V4">
-        <v>1.7591994732640105E-4</v>
+        <v>2.2117416232010178E-4</v>
       </c>
       <c r="W4">
-        <v>-3.7992267386487849E-4</v>
+        <v>-6.2626569550536379E-5</v>
       </c>
       <c r="X4">
-        <v>6.8132918067830527E-4</v>
+        <v>1.4310500612577158E-4</v>
       </c>
       <c r="Y4">
-        <v>7.5400158646880963E-4</v>
+        <v>2.0958957240459208E-4</v>
       </c>
       <c r="Z4">
-        <v>-6.836835451377632E-5</v>
+        <v>-5.2024431154068301E-6</v>
       </c>
       <c r="AA4">
-        <v>-2.9512225068044854E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+        <v>-1.8095922953169277E-5</v>
+      </c>
+      <c r="AB4">
+        <v>4.234934148419692E-4</v>
+      </c>
+      <c r="AC4">
+        <v>-2.5315590998353527E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B5">
-        <v>-7.7207288306817987E-2</v>
+      <c r="B5" s="6">
+        <v>-5.5829966924280688E-2</v>
       </c>
       <c r="C5">
-        <v>3.5675310834236591E-7</v>
+        <v>3.8459080992273237E-5</v>
       </c>
       <c r="D5">
-        <v>-2.8272488675793919E-7</v>
+        <v>-5.5648177502340114E-7</v>
       </c>
       <c r="E5">
-        <v>3.5615140093344594E-3</v>
+        <v>2.2935170929283197E-3</v>
       </c>
       <c r="F5">
-        <v>5.6285589507517582E-3</v>
+        <v>4.2202654605969017E-3</v>
       </c>
       <c r="G5">
-        <v>-1.0706681580740756E-3</v>
+        <v>-4.797079781672602E-4</v>
       </c>
       <c r="H5">
-        <v>-1.7572984725018467E-3</v>
+        <v>-1.2443054049607028E-3</v>
       </c>
       <c r="I5">
-        <v>-3.1040690117201895E-4</v>
+        <v>-3.2946852867231401E-4</v>
       </c>
       <c r="J5">
-        <v>3.6157793453891964E-4</v>
+        <v>4.15257571619741E-4</v>
       </c>
       <c r="K5">
-        <v>2.8022190939428781E-3</v>
+        <v>2.1041834217173996E-3</v>
       </c>
       <c r="L5">
-        <v>9.1810499610562603E-4</v>
+        <v>4.1398881200588507E-4</v>
       </c>
       <c r="M5">
-        <v>4.3273833494101384E-4</v>
+        <v>5.2325357747627231E-4</v>
       </c>
       <c r="N5">
-        <v>-2.4101515916930778E-4</v>
+        <v>9.1941946587159248E-7</v>
       </c>
       <c r="O5">
-        <v>-4.8255309808465318E-4</v>
+        <v>-1.5815249903943773E-4</v>
       </c>
       <c r="P5">
-        <v>1.1693518898683994E-4</v>
+        <v>5.1106396496075916E-4</v>
       </c>
       <c r="Q5">
-        <v>1.8198139786145713E-3</v>
+        <v>1.201138430688731E-3</v>
       </c>
       <c r="R5">
-        <v>-2.3969707241329469E-4</v>
+        <v>-7.0166048484637046E-5</v>
       </c>
       <c r="S5">
-        <v>-7.3255249068182268E-4</v>
+        <v>-2.8479830204194848E-4</v>
       </c>
       <c r="T5">
-        <v>4.6160765776884032E-4</v>
+        <v>2.5451582694271122E-4</v>
       </c>
       <c r="U5">
-        <v>5.433477647007216E-4</v>
+        <v>2.9425065825773014E-4</v>
       </c>
       <c r="V5">
-        <v>1.3475010686484776E-3</v>
+        <v>1.0642959604795525E-3</v>
       </c>
       <c r="W5">
-        <v>6.7107135308089804E-4</v>
+        <v>6.9181451473607084E-4</v>
       </c>
       <c r="X5">
-        <v>4.302315724270785E-4</v>
+        <v>-9.2152882640451688E-5</v>
       </c>
       <c r="Y5">
-        <v>7.8545716169021508E-4</v>
+        <v>9.75061225358528E-6</v>
       </c>
       <c r="Z5">
-        <v>-8.2062628164357053E-5</v>
+        <v>-1.5558917202512836E-5</v>
       </c>
       <c r="AA5">
-        <v>-2.5917155908881358E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+        <v>1.6351182800877469E-5</v>
+      </c>
+      <c r="AB5">
+        <v>8.0779903324818729E-4</v>
+      </c>
+      <c r="AC5">
+        <v>-3.3957799221103792E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A6" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B6">
-        <v>3.6470118973022096E-2</v>
+      <c r="B6" s="6">
+        <v>2.5268031880264254E-2</v>
       </c>
       <c r="C6">
-        <v>1.1516588968841677E-5</v>
+        <v>4.0604339951309961E-6</v>
       </c>
       <c r="D6">
-        <v>9.7199435523698725E-8</v>
+        <v>1.2424565140238948E-7</v>
       </c>
       <c r="E6">
-        <v>-1.031427629690382E-3</v>
+        <v>-6.444447507266127E-4</v>
       </c>
       <c r="F6">
-        <v>-1.0706681580740756E-3</v>
+        <v>-4.797079781672602E-4</v>
       </c>
       <c r="G6">
-        <v>3.677752703602489E-3</v>
+        <v>2.7235646067633973E-3</v>
       </c>
       <c r="H6">
-        <v>2.8957951971522659E-3</v>
+        <v>2.3311212619612645E-3</v>
       </c>
       <c r="I6">
-        <v>2.1650971741036251E-3</v>
+        <v>1.418937620883728E-3</v>
       </c>
       <c r="J6">
-        <v>1.6185421770176065E-3</v>
+        <v>1.0878157790742246E-3</v>
       </c>
       <c r="K6">
-        <v>-3.9729538427415809E-3</v>
+        <v>-3.1124477944643085E-3</v>
       </c>
       <c r="L6">
-        <v>-3.4193050160394012E-3</v>
+        <v>-2.4162096099183544E-3</v>
       </c>
       <c r="M6">
-        <v>-3.4945868766390075E-3</v>
+        <v>-2.6200226867082979E-3</v>
       </c>
       <c r="N6">
-        <v>1.5314133290927608E-5</v>
+        <v>2.2142714147318197E-4</v>
       </c>
       <c r="O6">
-        <v>-1.9344169162051252E-4</v>
+        <v>-2.0759630597979137E-5</v>
       </c>
       <c r="P6">
-        <v>2.8491329249578294E-4</v>
+        <v>1.7033450552535596E-4</v>
       </c>
       <c r="Q6">
-        <v>8.6792427646375267E-4</v>
+        <v>5.5201424301613779E-4</v>
       </c>
       <c r="R6">
-        <v>2.6156926368368601E-4</v>
+        <v>4.2417334195124024E-4</v>
       </c>
       <c r="S6">
-        <v>-4.8703259731160082E-4</v>
+        <v>-3.3600870286515068E-4</v>
       </c>
       <c r="T6">
-        <v>-1.7150804829542973E-4</v>
+        <v>-2.7900812695077197E-5</v>
       </c>
       <c r="U6">
-        <v>5.164995881341833E-5</v>
+        <v>3.7353212408097384E-5</v>
       </c>
       <c r="V6">
-        <v>-9.5963907302334868E-5</v>
+        <v>-2.2868275642699067E-5</v>
       </c>
       <c r="W6">
-        <v>-5.0406943577341085E-4</v>
+        <v>-2.3425949705745526E-4</v>
       </c>
       <c r="X6">
-        <v>8.7985231420631199E-5</v>
+        <v>-1.2149062463784289E-6</v>
       </c>
       <c r="Y6">
-        <v>9.5646189017572873E-5</v>
+        <v>3.8817223602476397E-6</v>
       </c>
       <c r="Z6">
-        <v>-2.3984382686234568E-5</v>
+        <v>-2.2494839677385872E-5</v>
       </c>
       <c r="AA6">
-        <v>-1.6863565025339161E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+        <v>-2.5206524173308466E-5</v>
+      </c>
+      <c r="AB6">
+        <v>9.6466756696710087E-5</v>
+      </c>
+      <c r="AC6">
+        <v>-1.2241651038162791E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A7" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B7">
-        <v>-7.0048250109431318E-2</v>
+      <c r="B7" s="6">
+        <v>-0.31280850459274706</v>
       </c>
       <c r="C7">
-        <v>1.2538761013920286E-4</v>
+        <v>3.359865104772845E-5</v>
       </c>
       <c r="D7">
-        <v>-8.6923131616583186E-7</v>
+        <v>1.7147924153705483E-7</v>
       </c>
       <c r="E7">
-        <v>-1.8044191652533314E-3</v>
+        <v>-1.7312885501741114E-3</v>
       </c>
       <c r="F7">
-        <v>-1.7572984725018467E-3</v>
+        <v>-1.2443054049607028E-3</v>
       </c>
       <c r="G7">
-        <v>2.8957951971522659E-3</v>
+        <v>2.3311212619612645E-3</v>
       </c>
       <c r="H7">
-        <v>4.1129294107604346E-2</v>
+        <v>3.7999801836041458E-2</v>
       </c>
       <c r="I7">
-        <v>6.5843399123764745E-3</v>
+        <v>6.6981329468864528E-3</v>
       </c>
       <c r="J7">
-        <v>7.1202172452911293E-3</v>
+        <v>7.155136866228427E-3</v>
       </c>
       <c r="K7">
-        <v>-3.5765377654152469E-2</v>
+        <v>-3.1731763291663502E-2</v>
       </c>
       <c r="L7">
-        <v>-3.1186916123022053E-3</v>
+        <v>-2.1208006363192759E-3</v>
       </c>
       <c r="M7">
-        <v>-3.0181546714789466E-3</v>
+        <v>-2.4692645780759535E-3</v>
       </c>
       <c r="N7">
-        <v>1.007686384241706E-3</v>
+        <v>1.344729070829525E-3</v>
       </c>
       <c r="O7">
-        <v>7.5402621048960596E-3</v>
+        <v>8.7496762431333377E-3</v>
       </c>
       <c r="P7">
-        <v>7.854007226147295E-3</v>
+        <v>8.9424103588253076E-3</v>
       </c>
       <c r="Q7">
-        <v>7.4374470844209483E-3</v>
+        <v>8.4229404841254466E-3</v>
       </c>
       <c r="R7">
-        <v>-2.5927249638401907E-4</v>
+        <v>3.2604585615934043E-4</v>
       </c>
       <c r="S7">
-        <v>3.4074511389906774E-4</v>
+        <v>-2.7015694449222761E-5</v>
       </c>
       <c r="T7">
-        <v>-3.0001043364205875E-4</v>
+        <v>-2.9296018561280571E-4</v>
       </c>
       <c r="U7">
-        <v>-5.7091648098929709E-4</v>
+        <v>-6.9008104198721291E-4</v>
       </c>
       <c r="V7">
-        <v>-8.7058817626509469E-4</v>
+        <v>-1.0139989420001679E-3</v>
       </c>
       <c r="W7">
-        <v>1.9343581507100856E-4</v>
+        <v>1.7380208556720331E-4</v>
       </c>
       <c r="X7">
-        <v>-2.0664755103784469E-3</v>
+        <v>-1.6574989059658695E-3</v>
       </c>
       <c r="Y7">
-        <v>-2.13823787804804E-3</v>
+        <v>-1.817737952112976E-3</v>
       </c>
       <c r="Z7">
-        <v>5.1934087150985872E-5</v>
+        <v>-5.4038324636060072E-5</v>
       </c>
       <c r="AA7">
-        <v>-1.0664949113431455E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+        <v>-1.7632171503473076E-4</v>
+      </c>
+      <c r="AB7">
+        <v>-1.3129186436465915E-3</v>
+      </c>
+      <c r="AC7">
+        <v>-7.9062341569965614E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A8" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B8">
-        <v>0.15240817241157409</v>
+      <c r="B8" s="6">
+        <v>3.8478326909824549E-2</v>
       </c>
       <c r="C8">
-        <v>-1.2683050403921307E-4</v>
+        <v>-7.6118787044420405E-5</v>
       </c>
       <c r="D8">
-        <v>1.247034454349264E-6</v>
+        <v>8.4874356927794072E-7</v>
       </c>
       <c r="E8">
-        <v>-4.2946159367491491E-4</v>
+        <v>-3.7964705342244929E-4</v>
       </c>
       <c r="F8">
-        <v>-3.1040690117201895E-4</v>
+        <v>-3.2946852867231401E-4</v>
       </c>
       <c r="G8">
-        <v>2.1650971741036251E-3</v>
+        <v>1.418937620883728E-3</v>
       </c>
       <c r="H8">
-        <v>6.5843399123764745E-3</v>
+        <v>6.6981329468864528E-3</v>
       </c>
       <c r="I8">
-        <v>8.2765709926663992E-3</v>
+        <v>7.9169681523277597E-3</v>
       </c>
       <c r="J8">
-        <v>4.7899469764027414E-3</v>
+        <v>4.7614832226951509E-3</v>
       </c>
       <c r="K8">
-        <v>-4.5502468223120162E-3</v>
+        <v>-3.6363089178322958E-3</v>
       </c>
       <c r="L8">
-        <v>-6.0615812449860609E-3</v>
+        <v>-4.7151501078141842E-3</v>
       </c>
       <c r="M8">
-        <v>-2.0121715630319341E-3</v>
+        <v>-1.4488776529881994E-3</v>
       </c>
       <c r="N8">
-        <v>9.3388117113188309E-6</v>
+        <v>7.7146476162385721E-5</v>
       </c>
       <c r="O8">
-        <v>1.622899250920505E-3</v>
+        <v>2.7666371013096861E-3</v>
       </c>
       <c r="P8">
-        <v>3.9290740022983415E-3</v>
+        <v>4.6129350242532325E-3</v>
       </c>
       <c r="Q8">
-        <v>4.1466581030149292E-3</v>
+        <v>4.6057347355231374E-3</v>
       </c>
       <c r="R8">
-        <v>-2.6796234759059612E-4</v>
+        <v>-1.4868057444285398E-4</v>
       </c>
       <c r="S8">
-        <v>-1.4716833881053756E-3</v>
+        <v>-2.6157718582448626E-3</v>
       </c>
       <c r="T8">
-        <v>3.4634410730365116E-4</v>
+        <v>3.4597382670133907E-4</v>
       </c>
       <c r="U8">
-        <v>1.2417329787355422E-3</v>
+        <v>1.1108659131351683E-3</v>
       </c>
       <c r="V8">
-        <v>1.1225279712322369E-3</v>
+        <v>1.0278868775958074E-3</v>
       </c>
       <c r="W8">
-        <v>6.8300647557160586E-4</v>
+        <v>8.7855607215023344E-4</v>
       </c>
       <c r="X8">
-        <v>-1.3860929839552491E-4</v>
+        <v>-2.5055999157076302E-4</v>
       </c>
       <c r="Y8">
-        <v>-4.6118670933585366E-4</v>
+        <v>-5.1061968759366421E-4</v>
       </c>
       <c r="Z8">
-        <v>-9.1069452709808922E-6</v>
+        <v>3.9187170841608536E-5</v>
       </c>
       <c r="AA8">
-        <v>-2.6387004310563919E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+        <v>-4.7728506253634593E-4</v>
+      </c>
+      <c r="AB8">
+        <v>-8.2569422329143794E-4</v>
+      </c>
+      <c r="AC8">
+        <v>-4.9304255007563882E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A9" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B9">
-        <v>-0.26666117598557482</v>
+      <c r="B9" s="6">
+        <v>-0.26751553837198389</v>
       </c>
       <c r="C9">
-        <v>2.382030087482881E-4</v>
+        <v>1.2628636207495626E-4</v>
       </c>
       <c r="D9">
-        <v>-4.0913831691643275E-6</v>
+        <v>-2.4508810230758713E-6</v>
       </c>
       <c r="E9">
-        <v>1.0706968087990403E-4</v>
+        <v>-5.1427315352145704E-5</v>
       </c>
       <c r="F9">
-        <v>3.6157793453891964E-4</v>
+        <v>4.15257571619741E-4</v>
       </c>
       <c r="G9">
-        <v>1.6185421770176065E-3</v>
+        <v>1.0878157790742246E-3</v>
       </c>
       <c r="H9">
-        <v>7.1202172452911293E-3</v>
+        <v>7.155136866228427E-3</v>
       </c>
       <c r="I9">
-        <v>4.7899469764027414E-3</v>
+        <v>4.7614832226951509E-3</v>
       </c>
       <c r="J9">
-        <v>1.4130635837286652E-2</v>
+        <v>1.2126135163486141E-2</v>
       </c>
       <c r="K9">
-        <v>-4.7877229929833461E-3</v>
+        <v>-3.7231053725014437E-3</v>
       </c>
       <c r="L9">
-        <v>-2.0545100779324464E-3</v>
+        <v>-9.7388241790037503E-4</v>
       </c>
       <c r="M9">
-        <v>-6.9156967037248031E-3</v>
+        <v>-4.458197562881871E-3</v>
       </c>
       <c r="N9">
-        <v>1.0318269221543499E-4</v>
+        <v>-1.3623550838695402E-4</v>
       </c>
       <c r="O9">
-        <v>3.2326262450214091E-3</v>
+        <v>4.0042037434058339E-3</v>
       </c>
       <c r="P9">
-        <v>4.4241097123509281E-3</v>
+        <v>5.2841728949641464E-3</v>
       </c>
       <c r="Q9">
-        <v>5.5706625630447962E-3</v>
+        <v>5.9235396293028583E-3</v>
       </c>
       <c r="R9">
-        <v>-1.4590989058524688E-4</v>
+        <v>1.8571446140075351E-4</v>
       </c>
       <c r="S9">
-        <v>-4.6357827857202599E-4</v>
+        <v>-8.0240098090400428E-4</v>
       </c>
       <c r="T9">
-        <v>-2.4309608939494971E-4</v>
+        <v>1.6548602395249868E-4</v>
       </c>
       <c r="U9">
-        <v>5.8312626585185399E-4</v>
+        <v>2.0168717913846218E-4</v>
       </c>
       <c r="V9">
-        <v>3.3258977845107432E-4</v>
+        <v>-8.6184712382683659E-5</v>
       </c>
       <c r="W9">
-        <v>5.120380966654051E-5</v>
+        <v>-2.0493083256695362E-4</v>
       </c>
       <c r="X9">
-        <v>-2.0807174473237364E-5</v>
+        <v>1.4586561471782982E-4</v>
       </c>
       <c r="Y9">
-        <v>1.2132702993473618E-4</v>
+        <v>5.4613466622904609E-5</v>
       </c>
       <c r="Z9">
-        <v>2.3505173801232574E-5</v>
+        <v>4.5010309024486181E-5</v>
       </c>
       <c r="AA9">
-        <v>-9.1164263859241628E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+        <v>-6.2434279132598776E-4</v>
+      </c>
+      <c r="AB9">
+        <v>-1.2402345621786229E-3</v>
+      </c>
+      <c r="AC9">
+        <v>-7.7714187707702779E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A10" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B10">
-        <v>-0.53368909967324429</v>
+      <c r="B10" s="6">
+        <v>-0.54523792960880579</v>
       </c>
       <c r="C10">
-        <v>-5.6701671151218082E-5</v>
+        <v>-2.9258057911208703E-5</v>
       </c>
       <c r="D10">
-        <v>2.8144051931686538E-7</v>
+        <v>2.7776464583152683E-8</v>
       </c>
       <c r="E10">
-        <v>2.7745882577032755E-3</v>
+        <v>2.2707139165173873E-3</v>
       </c>
       <c r="F10">
-        <v>2.8022190939428781E-3</v>
+        <v>2.1041834217173996E-3</v>
       </c>
       <c r="G10">
-        <v>-3.9729538427415809E-3</v>
+        <v>-3.1124477944643085E-3</v>
       </c>
       <c r="H10">
-        <v>-3.5765377654152469E-2</v>
+        <v>-3.1731763291663502E-2</v>
       </c>
       <c r="I10">
-        <v>-4.5502468223120162E-3</v>
+        <v>-3.6363089178322958E-3</v>
       </c>
       <c r="J10">
-        <v>-4.7877229929833461E-3</v>
+        <v>-3.7231053725014437E-3</v>
       </c>
       <c r="K10">
-        <v>5.0612806498561404E-2</v>
+        <v>4.5804386075790363E-2</v>
       </c>
       <c r="L10">
-        <v>4.0898902740824968E-3</v>
+        <v>3.1257743005265177E-3</v>
       </c>
       <c r="M10">
-        <v>3.8663298148724091E-3</v>
+        <v>3.1156143366169618E-3</v>
       </c>
       <c r="N10">
-        <v>-5.8922135583437554E-4</v>
+        <v>-6.1752771414706037E-4</v>
       </c>
       <c r="O10">
-        <v>-5.0747377765732564E-3</v>
+        <v>-4.6513140412407627E-3</v>
       </c>
       <c r="P10">
-        <v>-3.9318902037786064E-3</v>
+        <v>-3.3564796114540084E-3</v>
       </c>
       <c r="Q10">
-        <v>-3.6333558570080049E-3</v>
+        <v>-3.038917292433115E-3</v>
       </c>
       <c r="R10">
-        <v>5.8768022456127334E-5</v>
+        <v>-3.5064477503457954E-4</v>
       </c>
       <c r="S10">
-        <v>1.4505170696460564E-3</v>
+        <v>6.5075808459909962E-4</v>
       </c>
       <c r="T10">
-        <v>5.2607925337320419E-4</v>
+        <v>2.2249714862782819E-4</v>
       </c>
       <c r="U10">
-        <v>5.2121674809648571E-4</v>
+        <v>5.5804985500959104E-4</v>
       </c>
       <c r="V10">
-        <v>9.5136401283376758E-4</v>
+        <v>9.1399013156487786E-4</v>
       </c>
       <c r="W10">
-        <v>-7.1366723973095814E-4</v>
+        <v>-4.7345367227311872E-4</v>
       </c>
       <c r="X10">
-        <v>2.1497128627029527E-3</v>
+        <v>1.8916310297124373E-3</v>
       </c>
       <c r="Y10">
-        <v>2.0753740798782395E-3</v>
+        <v>1.7953279806870353E-3</v>
       </c>
       <c r="Z10">
-        <v>-1.5070820231747413E-4</v>
+        <v>-2.0251937180575481E-5</v>
       </c>
       <c r="AA10">
-        <v>6.3833446360026134E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+        <v>2.7645451651173928E-4</v>
+      </c>
+      <c r="AB10">
+        <v>1.9855477532711207E-4</v>
+      </c>
+      <c r="AC10">
+        <v>3.1621900597430348E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A11" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B11">
-        <v>-0.26839199457985324</v>
+      <c r="B11" s="6">
+        <v>-0.22607857475699872</v>
       </c>
       <c r="C11">
-        <v>-5.7248221353960719E-5</v>
+        <v>-4.5080397324237878E-5</v>
       </c>
       <c r="D11">
-        <v>5.4526236658703974E-7</v>
+        <v>4.1099655365643492E-7</v>
       </c>
       <c r="E11">
-        <v>7.1431219125250584E-4</v>
+        <v>5.2590149333781315E-4</v>
       </c>
       <c r="F11">
-        <v>9.1810499610562603E-4</v>
+        <v>4.1398881200588507E-4</v>
       </c>
       <c r="G11">
-        <v>-3.4193050160394012E-3</v>
+        <v>-2.4162096099183544E-3</v>
       </c>
       <c r="H11">
-        <v>-3.1186916123022053E-3</v>
+        <v>-2.1208006363192759E-3</v>
       </c>
       <c r="I11">
-        <v>-6.0615812449860609E-3</v>
+        <v>-4.7151501078141842E-3</v>
       </c>
       <c r="J11">
-        <v>-2.0545100779324464E-3</v>
+        <v>-9.7388241790037503E-4</v>
       </c>
       <c r="K11">
-        <v>4.0898902740824968E-3</v>
+        <v>3.1257743005265177E-3</v>
       </c>
       <c r="L11">
-        <v>1.2424647022446547E-2</v>
+        <v>9.817514026433237E-3</v>
       </c>
       <c r="M11">
-        <v>3.4376827608491971E-3</v>
+        <v>2.3799586762507105E-3</v>
       </c>
       <c r="N11">
-        <v>2.4856749873729045E-4</v>
+        <v>1.0166850286533072E-4</v>
       </c>
       <c r="O11">
-        <v>1.0735257511427869E-3</v>
+        <v>8.9487323352533863E-4</v>
       </c>
       <c r="P11">
-        <v>6.0951980469168101E-5</v>
+        <v>3.6729489554219254E-4</v>
       </c>
       <c r="Q11">
-        <v>-3.8468629954473913E-4</v>
+        <v>1.8570460960089203E-4</v>
       </c>
       <c r="R11">
-        <v>1.0739892966817028E-4</v>
+        <v>1.9504895071369247E-4</v>
       </c>
       <c r="S11">
-        <v>2.0731548541248722E-3</v>
+        <v>2.5686475092294744E-3</v>
       </c>
       <c r="T11">
-        <v>-5.9572135402678251E-4</v>
+        <v>-7.7484587303197356E-4</v>
       </c>
       <c r="U11">
-        <v>-1.3320515275652349E-3</v>
+        <v>-1.0899334739905707E-3</v>
       </c>
       <c r="V11">
-        <v>-9.4690802960886245E-4</v>
+        <v>-8.7699731079982318E-4</v>
       </c>
       <c r="W11">
-        <v>-1.0031599033056592E-3</v>
+        <v>-7.452637607738078E-4</v>
       </c>
       <c r="X11">
-        <v>2.9263498417931872E-4</v>
+        <v>4.0981457064831407E-4</v>
       </c>
       <c r="Y11">
-        <v>9.1734619175477057E-5</v>
+        <v>1.9697691120778031E-4</v>
       </c>
       <c r="Z11">
-        <v>9.1022961017378655E-5</v>
+        <v>1.8945770379804294E-5</v>
       </c>
       <c r="AA11">
-        <v>1.8115782449125832E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+        <v>5.6063878474343161E-4</v>
+      </c>
+      <c r="AB11">
+        <v>-6.9788838680985674E-4</v>
+      </c>
+      <c r="AC11">
+        <v>1.903852150848664E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A12" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B12">
-        <v>0.44317930965088237</v>
+      <c r="B12" s="6">
+        <v>0.44799868728682973</v>
       </c>
       <c r="C12">
-        <v>-2.0404206844034972E-4</v>
+        <v>-7.6355945419629868E-5</v>
       </c>
       <c r="D12">
-        <v>2.3342694071391416E-6</v>
+        <v>7.9437672360943896E-7</v>
       </c>
       <c r="E12">
-        <v>4.8524896107759975E-5</v>
+        <v>2.3541705924100406E-4</v>
       </c>
       <c r="F12">
-        <v>4.3273833494101384E-4</v>
+        <v>5.2325357747627231E-4</v>
       </c>
       <c r="G12">
-        <v>-3.4945868766390075E-3</v>
+        <v>-2.6200226867082979E-3</v>
       </c>
       <c r="H12">
-        <v>-3.0181546714789466E-3</v>
+        <v>-2.4692645780759535E-3</v>
       </c>
       <c r="I12">
-        <v>-2.0121715630319341E-3</v>
+        <v>-1.4488776529881994E-3</v>
       </c>
       <c r="J12">
-        <v>-6.9156967037248031E-3</v>
+        <v>-4.458197562881871E-3</v>
       </c>
       <c r="K12">
-        <v>3.8663298148724091E-3</v>
+        <v>3.1156143366169618E-3</v>
       </c>
       <c r="L12">
-        <v>3.4376827608491971E-3</v>
+        <v>2.3799586762507105E-3</v>
       </c>
       <c r="M12">
-        <v>1.4486575122759663E-2</v>
+        <v>9.3931794148351712E-3</v>
       </c>
       <c r="N12">
-        <v>6.7500394679244531E-4</v>
+        <v>2.7808951377726642E-4</v>
       </c>
       <c r="O12">
-        <v>7.0578985732845146E-4</v>
+        <v>1.6832417320426096E-4</v>
       </c>
       <c r="P12">
-        <v>2.6979061930693105E-4</v>
+        <v>1.1930988804893374E-4</v>
       </c>
       <c r="Q12">
-        <v>-5.7072909130268467E-4</v>
+        <v>-3.7075390596959766E-4</v>
       </c>
       <c r="R12">
-        <v>-2.0382427185549839E-4</v>
+        <v>-3.6381931794948757E-4</v>
       </c>
       <c r="S12">
-        <v>4.189422553115364E-4</v>
+        <v>2.2636998087882115E-4</v>
       </c>
       <c r="T12">
-        <v>4.9039225871441152E-4</v>
+        <v>6.8722438862755554E-5</v>
       </c>
       <c r="U12">
-        <v>1.139447963041872E-3</v>
+        <v>2.9797695249173016E-4</v>
       </c>
       <c r="V12">
-        <v>1.0777655476555625E-3</v>
+        <v>3.8582041358889917E-4</v>
       </c>
       <c r="W12">
-        <v>1.3369188406740047E-3</v>
+        <v>5.5864721187526766E-4</v>
       </c>
       <c r="X12">
-        <v>-1.1231331845550497E-5</v>
+        <v>2.209056221151905E-4</v>
       </c>
       <c r="Y12">
-        <v>-1.4576067372752536E-4</v>
+        <v>1.0976828877673516E-4</v>
       </c>
       <c r="Z12">
-        <v>3.568860364640798E-5</v>
+        <v>6.6179604842931515E-6</v>
       </c>
       <c r="AA12">
-        <v>4.0348999305787857E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+        <v>1.0637931976069448E-4</v>
+      </c>
+      <c r="AB12">
+        <v>2.0755313689475321E-4</v>
+      </c>
+      <c r="AC12">
+        <v>2.2588095494599772E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A13" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B13">
-        <v>2.3155652962086261E-3</v>
+      <c r="B13" s="6">
+        <v>9.2101439308800142E-3</v>
       </c>
       <c r="C13">
-        <v>6.8924155807696517E-5</v>
+        <v>-8.9811639071983346E-7</v>
       </c>
       <c r="D13">
-        <v>-7.4488190819115847E-7</v>
+        <v>1.5935842873785472E-7</v>
       </c>
       <c r="E13">
-        <v>-1.0999530469873591E-4</v>
+        <v>8.0366711090506312E-6</v>
       </c>
       <c r="F13">
-        <v>-2.4101515916930778E-4</v>
+        <v>9.1941946587159248E-7</v>
       </c>
       <c r="G13">
-        <v>1.5314133290927608E-5</v>
+        <v>2.2142714147318197E-4</v>
       </c>
       <c r="H13">
-        <v>1.007686384241706E-3</v>
+        <v>1.344729070829525E-3</v>
       </c>
       <c r="I13">
-        <v>9.3388117113188309E-6</v>
+        <v>7.7146476162385721E-5</v>
       </c>
       <c r="J13">
-        <v>1.0318269221543499E-4</v>
+        <v>-1.3623550838695402E-4</v>
       </c>
       <c r="K13">
-        <v>-5.8922135583437554E-4</v>
+        <v>-6.1752771414706037E-4</v>
       </c>
       <c r="L13">
-        <v>2.4856749873729045E-4</v>
+        <v>1.0166850286533072E-4</v>
       </c>
       <c r="M13">
-        <v>6.7500394679244531E-4</v>
+        <v>2.7808951377726642E-4</v>
       </c>
       <c r="N13">
-        <v>5.3367913811313552E-3</v>
+        <v>4.1746589083642921E-3</v>
       </c>
       <c r="O13">
-        <v>2.9194335752848809E-3</v>
+        <v>2.5914123531724318E-3</v>
       </c>
       <c r="P13">
-        <v>2.8231105846751293E-3</v>
+        <v>2.639931224707368E-3</v>
       </c>
       <c r="Q13">
-        <v>2.6578831242698503E-3</v>
+        <v>2.5743292370874219E-3</v>
       </c>
       <c r="R13">
-        <v>1.0967267099690487E-4</v>
+        <v>8.6194700358135427E-5</v>
       </c>
       <c r="S13">
-        <v>-2.8249353127137122E-4</v>
+        <v>1.7748879325378824E-4</v>
       </c>
       <c r="T13">
-        <v>5.6017693657018849E-4</v>
+        <v>4.7268895731926403E-4</v>
       </c>
       <c r="U13">
-        <v>5.8201761441521792E-4</v>
+        <v>1.7017996533063076E-4</v>
       </c>
       <c r="V13">
-        <v>4.7793065696496106E-4</v>
+        <v>1.8375819833993596E-4</v>
       </c>
       <c r="W13">
-        <v>1.0662720434685133E-3</v>
+        <v>3.4324658439240888E-4</v>
       </c>
       <c r="X13">
-        <v>-2.8237996168933117E-4</v>
+        <v>-1.0855244209454634E-4</v>
       </c>
       <c r="Y13">
-        <v>-4.3513470225888234E-4</v>
+        <v>-2.0320986415811766E-4</v>
       </c>
       <c r="Z13">
-        <v>4.9348928742859151E-5</v>
+        <v>1.8166145719491827E-6</v>
       </c>
       <c r="AA13">
-        <v>-5.328626199042872E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+        <v>8.9633511359965426E-5</v>
+      </c>
+      <c r="AB13">
+        <v>-5.6074645555351395E-4</v>
+      </c>
+      <c r="AC13">
+        <v>-3.0868922110899857E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A14" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B14">
-        <v>0.10810142370537409</v>
+      <c r="B14" s="6">
+        <v>-0.10632030888724631</v>
       </c>
       <c r="C14">
-        <v>-7.8907894174247472E-5</v>
+        <v>-1.4243661615498507E-4</v>
       </c>
       <c r="D14">
-        <v>6.3039984887366727E-7</v>
+        <v>1.5656349882650757E-6</v>
       </c>
       <c r="E14">
-        <v>-6.4944203977448597E-4</v>
+        <v>-4.3596226691410169E-4</v>
       </c>
       <c r="F14">
-        <v>-4.8255309808465318E-4</v>
+        <v>-1.5815249903943773E-4</v>
       </c>
       <c r="G14">
-        <v>-1.9344169162051252E-4</v>
+        <v>-2.0759630597979137E-5</v>
       </c>
       <c r="H14">
-        <v>7.5402621048960596E-3</v>
+        <v>8.7496762431333377E-3</v>
       </c>
       <c r="I14">
-        <v>1.622899250920505E-3</v>
+        <v>2.7666371013096861E-3</v>
       </c>
       <c r="J14">
-        <v>3.2326262450214091E-3</v>
+        <v>4.0042037434058339E-3</v>
       </c>
       <c r="K14">
-        <v>-5.0747377765732564E-3</v>
+        <v>-4.6513140412407627E-3</v>
       </c>
       <c r="L14">
-        <v>1.0735257511427869E-3</v>
+        <v>8.9487323352533863E-4</v>
       </c>
       <c r="M14">
-        <v>7.0578985732845146E-4</v>
+        <v>1.6832417320426096E-4</v>
       </c>
       <c r="N14">
-        <v>2.9194335752848809E-3</v>
+        <v>2.5914123531724318E-3</v>
       </c>
       <c r="O14">
-        <v>6.8688478205551811E-3</v>
+        <v>7.4569439933236045E-3</v>
       </c>
       <c r="P14">
-        <v>5.4281221449371201E-3</v>
+        <v>6.7939216175359656E-3</v>
       </c>
       <c r="Q14">
-        <v>5.1749255596535279E-3</v>
+        <v>6.7341290731915355E-3</v>
       </c>
       <c r="R14">
-        <v>-9.085691408661071E-5</v>
+        <v>4.5498330636533211E-5</v>
       </c>
       <c r="S14">
-        <v>-1.5182949282960029E-4</v>
+        <v>3.9418197059060839E-4</v>
       </c>
       <c r="T14">
-        <v>4.1233132527234643E-4</v>
+        <v>4.7133527909610758E-5</v>
       </c>
       <c r="U14">
-        <v>4.9066015872077802E-4</v>
+        <v>-1.9596196261535811E-4</v>
       </c>
       <c r="V14">
-        <v>2.8460243003903358E-4</v>
+        <v>-4.0320853665659623E-4</v>
       </c>
       <c r="W14">
-        <v>6.7830259065809794E-4</v>
+        <v>-8.3316199019728269E-5</v>
       </c>
       <c r="X14">
-        <v>-7.8170099441514504E-4</v>
+        <v>-2.0960155934235739E-4</v>
       </c>
       <c r="Y14">
-        <v>-1.2344973092794139E-3</v>
+        <v>-6.9472513965679588E-4</v>
       </c>
       <c r="Z14">
-        <v>1.0266629142124256E-4</v>
+        <v>-2.3976194332510535E-5</v>
       </c>
       <c r="AA14">
-        <v>-4.2892678210792994E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+        <v>4.15171102766153E-4</v>
+      </c>
+      <c r="AB14">
+        <v>-1.308829307843069E-3</v>
+      </c>
+      <c r="AC14">
+        <v>-2.5873291793113381E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A15" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B15">
-        <v>0.17871415827670609</v>
+      <c r="B15" s="6">
+        <v>-7.8699072200902373E-2</v>
       </c>
       <c r="C15">
-        <v>-1.9348500366965689E-4</v>
+        <v>-2.108862071695163E-4</v>
       </c>
       <c r="D15">
-        <v>1.8900745063745474E-6</v>
+        <v>2.2983261389426365E-6</v>
       </c>
       <c r="E15">
-        <v>-3.9627258200331417E-4</v>
+        <v>-2.8653758643618874E-4</v>
       </c>
       <c r="F15">
-        <v>1.1693518898683994E-4</v>
+        <v>5.1106396496075916E-4</v>
       </c>
       <c r="G15">
-        <v>2.8491329249578294E-4</v>
+        <v>1.7033450552535596E-4</v>
       </c>
       <c r="H15">
-        <v>7.854007226147295E-3</v>
+        <v>8.9424103588253076E-3</v>
       </c>
       <c r="I15">
-        <v>3.9290740022983415E-3</v>
+        <v>4.6129350242532325E-3</v>
       </c>
       <c r="J15">
-        <v>4.4241097123509281E-3</v>
+        <v>5.2841728949641464E-3</v>
       </c>
       <c r="K15">
-        <v>-3.9318902037786064E-3</v>
+        <v>-3.3564796114540084E-3</v>
       </c>
       <c r="L15">
-        <v>6.0951980469168101E-5</v>
+        <v>3.6729489554219254E-4</v>
       </c>
       <c r="M15">
-        <v>2.6979061930693105E-4</v>
+        <v>1.1930988804893374E-4</v>
       </c>
       <c r="N15">
-        <v>2.8231105846751293E-3</v>
+        <v>2.639931224707368E-3</v>
       </c>
       <c r="O15">
-        <v>5.4281221449371201E-3</v>
+        <v>6.7939216175359656E-3</v>
       </c>
       <c r="P15">
-        <v>8.8261062634086979E-3</v>
+        <v>9.9274700242646449E-3</v>
       </c>
       <c r="Q15">
-        <v>7.0450741988011944E-3</v>
+        <v>8.5980875777724366E-3</v>
       </c>
       <c r="R15">
-        <v>-1.8154435728653153E-5</v>
+        <v>2.2253016185179688E-4</v>
       </c>
       <c r="S15">
-        <v>3.567103604639176E-5</v>
+        <v>7.5538898531885067E-5</v>
       </c>
       <c r="T15">
-        <v>1.0098159573680193E-3</v>
+        <v>2.724471588862106E-4</v>
       </c>
       <c r="U15">
-        <v>5.9346000763799557E-4</v>
+        <v>-9.56790048321568E-5</v>
       </c>
       <c r="V15">
-        <v>3.8606410724178683E-5</v>
+        <v>-4.2679092005321094E-4</v>
       </c>
       <c r="W15">
-        <v>-1.7377450182778074E-4</v>
+        <v>-4.3573888339197868E-4</v>
       </c>
       <c r="X15">
-        <v>-7.2959975759344983E-4</v>
+        <v>-3.0580024753550073E-4</v>
       </c>
       <c r="Y15">
-        <v>-1.282099891861867E-3</v>
+        <v>-7.686465575673534E-4</v>
       </c>
       <c r="Z15">
-        <v>1.1556183426585467E-5</v>
+        <v>-1.9214806648198713E-5</v>
       </c>
       <c r="AA15">
-        <v>-2.5083576354563457E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+        <v>-8.8753253829328008E-5</v>
+      </c>
+      <c r="AB15">
+        <v>-1.8935727230870089E-3</v>
+      </c>
+      <c r="AC15">
+        <v>-3.1244484805339062E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A16" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B16">
-        <v>8.5222447303502077E-2</v>
+      <c r="B16" s="6">
+        <v>-7.3990999504404936E-2</v>
       </c>
       <c r="C16">
-        <v>-2.0538462979886166E-4</v>
+        <v>-2.4974769598487431E-4</v>
       </c>
       <c r="D16">
-        <v>1.6961179499678863E-6</v>
+        <v>2.5562790126732803E-6</v>
       </c>
       <c r="E16">
-        <v>1.1722402915741155E-3</v>
+        <v>5.4794009906040855E-4</v>
       </c>
       <c r="F16">
-        <v>1.8198139786145713E-3</v>
+        <v>1.201138430688731E-3</v>
       </c>
       <c r="G16">
-        <v>8.6792427646375267E-4</v>
+        <v>5.5201424301613779E-4</v>
       </c>
       <c r="H16">
-        <v>7.4374470844209483E-3</v>
+        <v>8.4229404841254466E-3</v>
       </c>
       <c r="I16">
-        <v>4.1466581030149292E-3</v>
+        <v>4.6057347355231374E-3</v>
       </c>
       <c r="J16">
-        <v>5.5706625630447962E-3</v>
+        <v>5.9235396293028583E-3</v>
       </c>
       <c r="K16">
-        <v>-3.6333558570080049E-3</v>
+        <v>-3.038917292433115E-3</v>
       </c>
       <c r="L16">
-        <v>-3.8468629954473913E-4</v>
+        <v>1.8570460960089203E-4</v>
       </c>
       <c r="M16">
-        <v>-5.7072909130268467E-4</v>
+        <v>-3.7075390596959766E-4</v>
       </c>
       <c r="N16">
-        <v>2.6578831242698503E-3</v>
+        <v>2.5743292370874219E-3</v>
       </c>
       <c r="O16">
-        <v>5.1749255596535279E-3</v>
+        <v>6.7341290731915355E-3</v>
       </c>
       <c r="P16">
-        <v>7.0450741988011944E-3</v>
+        <v>8.5980875777724366E-3</v>
       </c>
       <c r="Q16">
-        <v>1.0956367543691416E-2</v>
+        <v>1.0851906024453304E-2</v>
       </c>
       <c r="R16">
-        <v>-8.4563169943857066E-5</v>
+        <v>4.5210665391607631E-4</v>
       </c>
       <c r="S16">
-        <v>-3.4095212222240407E-4</v>
+        <v>-9.124699645373757E-5</v>
       </c>
       <c r="T16">
-        <v>7.0866667334774686E-4</v>
+        <v>1.0582598932996662E-4</v>
       </c>
       <c r="U16">
-        <v>6.165597625888274E-4</v>
+        <v>-2.9470999275142684E-4</v>
       </c>
       <c r="V16">
-        <v>-1.2591725299155871E-4</v>
+        <v>-7.4337175890838074E-4</v>
       </c>
       <c r="W16">
-        <v>-9.8275903050604836E-4</v>
+        <v>-8.4113256083483069E-4</v>
       </c>
       <c r="X16">
-        <v>6.5152353114273634E-4</v>
+        <v>4.0183214118862652E-4</v>
       </c>
       <c r="Y16">
-        <v>4.031638443363619E-4</v>
+        <v>4.9801166914767523E-5</v>
       </c>
       <c r="Z16">
-        <v>4.2667418071579664E-6</v>
+        <v>-8.9654769154273088E-6</v>
       </c>
       <c r="AA16">
-        <v>-4.1214885371252969E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+        <v>-2.2250874877568095E-4</v>
+      </c>
+      <c r="AB16">
+        <v>-1.8343939942014307E-3</v>
+      </c>
+      <c r="AC16">
+        <v>-3.4523671935213435E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A17" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B17">
-        <v>0.105242203782847</v>
+      <c r="B17" s="6">
+        <v>0.13630703252380591</v>
       </c>
       <c r="C17">
-        <v>9.9086668147713283E-6</v>
+        <v>-6.3330174480018749E-5</v>
       </c>
       <c r="D17">
-        <v>-8.8739646994525231E-9</v>
+        <v>7.0556436762683465E-7</v>
       </c>
       <c r="E17">
-        <v>-5.8590788951267902E-5</v>
+        <v>-4.187421864698657E-5</v>
       </c>
       <c r="F17">
-        <v>-2.3969707241329469E-4</v>
+        <v>-7.0166048484637046E-5</v>
       </c>
       <c r="G17">
-        <v>2.6156926368368601E-4</v>
+        <v>4.2417334195124024E-4</v>
       </c>
       <c r="H17">
-        <v>-2.5927249638401907E-4</v>
+        <v>3.2604585615934043E-4</v>
       </c>
       <c r="I17">
-        <v>-2.6796234759059612E-4</v>
+        <v>-1.4868057444285398E-4</v>
       </c>
       <c r="J17">
-        <v>-1.4590989058524688E-4</v>
+        <v>1.8571446140075351E-4</v>
       </c>
       <c r="K17">
-        <v>5.8768022456127334E-5</v>
+        <v>-3.5064477503457954E-4</v>
       </c>
       <c r="L17">
-        <v>1.0739892966817028E-4</v>
+        <v>1.9504895071369247E-4</v>
       </c>
       <c r="M17">
-        <v>-2.0382427185549839E-4</v>
+        <v>-3.6381931794948757E-4</v>
       </c>
       <c r="N17">
-        <v>1.0967267099690487E-4</v>
+        <v>8.6194700358135427E-5</v>
       </c>
       <c r="O17">
-        <v>-9.085691408661071E-5</v>
+        <v>4.5498330636533211E-5</v>
       </c>
       <c r="P17">
-        <v>-1.8154435728653153E-5</v>
+        <v>2.2253016185179688E-4</v>
       </c>
       <c r="Q17">
-        <v>-8.4563169943857066E-5</v>
+        <v>4.5210665391607631E-4</v>
       </c>
       <c r="R17">
-        <v>5.8203979272483132E-4</v>
+        <v>1.1079486056567943E-3</v>
       </c>
       <c r="S17">
-        <v>-1.1065718264082162E-3</v>
+        <v>-1.3175903540770481E-3</v>
       </c>
       <c r="T17">
-        <v>8.0080051136409552E-5</v>
+        <v>7.7678366691613025E-6</v>
       </c>
       <c r="U17">
-        <v>-8.3358316056398837E-5</v>
+        <v>-1.58449691844575E-4</v>
       </c>
       <c r="V17">
-        <v>-1.1804595636798201E-4</v>
+        <v>-3.1186973246714314E-4</v>
       </c>
       <c r="W17">
-        <v>-1.60156348108151E-4</v>
+        <v>-2.5068015228892228E-4</v>
       </c>
       <c r="X17">
-        <v>2.1877481168000373E-4</v>
+        <v>2.9419560829470109E-4</v>
       </c>
       <c r="Y17">
-        <v>1.2077484544108138E-5</v>
+        <v>1.2275298457496459E-4</v>
       </c>
       <c r="Z17">
-        <v>-7.6922085612075297E-6</v>
+        <v>-6.5384882094179922E-6</v>
       </c>
       <c r="AA17">
-        <v>-3.8669146147274824E-4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+        <v>-9.3122343941148898E-5</v>
+      </c>
+      <c r="AB17">
+        <v>-2.329651980999567E-4</v>
+      </c>
+      <c r="AC17">
+        <v>9.1456124613094759E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18">
-        <v>-6.6440712729050777E-2</v>
+      <c r="B18" s="6">
+        <v>0.31502813220936782</v>
       </c>
       <c r="C18">
-        <v>9.2292659783235821E-5</v>
+        <v>6.7302917304754657E-5</v>
       </c>
       <c r="D18">
-        <v>-7.9066206450086279E-7</v>
+        <v>-5.1019457887426699E-7</v>
       </c>
       <c r="E18">
-        <v>-4.4395472444917397E-4</v>
+        <v>-7.1783076106090465E-5</v>
       </c>
       <c r="F18">
-        <v>-7.3255249068182268E-4</v>
+        <v>-2.8479830204194848E-4</v>
       </c>
       <c r="G18">
-        <v>-4.8703259731160082E-4</v>
+        <v>-3.3600870286515068E-4</v>
       </c>
       <c r="H18">
-        <v>3.4074511389906774E-4</v>
+        <v>-2.7015694449222761E-5</v>
       </c>
       <c r="I18">
-        <v>-1.4716833881053756E-3</v>
+        <v>-2.6157718582448626E-3</v>
       </c>
       <c r="J18">
-        <v>-4.6357827857202599E-4</v>
+        <v>-8.0240098090400428E-4</v>
       </c>
       <c r="K18">
-        <v>1.4505170696460564E-3</v>
+        <v>6.5075808459909962E-4</v>
       </c>
       <c r="L18">
-        <v>2.0731548541248722E-3</v>
+        <v>2.5686475092294744E-3</v>
       </c>
       <c r="M18">
-        <v>4.189422553115364E-4</v>
+        <v>2.2636998087882115E-4</v>
       </c>
       <c r="N18">
-        <v>-2.8249353127137122E-4</v>
+        <v>1.7748879325378824E-4</v>
       </c>
       <c r="O18">
-        <v>-1.5182949282960029E-4</v>
+        <v>3.9418197059060839E-4</v>
       </c>
       <c r="P18">
-        <v>3.567103604639176E-5</v>
+        <v>7.5538898531885067E-5</v>
       </c>
       <c r="Q18">
-        <v>-3.4095212222240407E-4</v>
+        <v>-9.124699645373757E-5</v>
       </c>
       <c r="R18">
-        <v>-1.1065718264082162E-3</v>
+        <v>-1.3175903540770481E-3</v>
       </c>
       <c r="S18">
-        <v>1.3840533857626505E-2</v>
+        <v>1.6888446396797346E-2</v>
       </c>
       <c r="T18">
-        <v>-4.1233822045834721E-4</v>
+        <v>-3.4913480720527969E-4</v>
       </c>
       <c r="U18">
-        <v>-2.3687243364836833E-4</v>
+        <v>-8.2938282876467834E-4</v>
       </c>
       <c r="V18">
-        <v>-2.0810556537406721E-4</v>
+        <v>-8.7754915612128022E-4</v>
       </c>
       <c r="W18">
-        <v>3.5117197099119495E-4</v>
+        <v>-6.8549508235282535E-4</v>
       </c>
       <c r="X18">
-        <v>-1.805411286487747E-4</v>
+        <v>3.2625111195169862E-4</v>
       </c>
       <c r="Y18">
-        <v>1.1630789630579056E-4</v>
+        <v>3.8044103316776619E-4</v>
       </c>
       <c r="Z18">
-        <v>1.4016874306176796E-5</v>
+        <v>-3.3363827859303949E-5</v>
       </c>
       <c r="AA18">
-        <v>-1.5050613455802806E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+        <v>4.3115379721879921E-4</v>
+      </c>
+      <c r="AB18">
+        <v>-8.3520032803129259E-5</v>
+      </c>
+      <c r="AC18">
+        <v>-3.0196220894084045E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A19" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B19">
-        <v>-0.11826680902026188</v>
+      <c r="B19" s="6">
+        <v>-6.0948628531478352E-2</v>
       </c>
       <c r="C19">
-        <v>-8.8814752344549717E-5</v>
+        <v>-2.4815879461119407E-5</v>
       </c>
       <c r="D19">
-        <v>1.0176751154849027E-6</v>
+        <v>2.3258793653721198E-7</v>
       </c>
       <c r="E19">
-        <v>-1.3506579339424155E-4</v>
+        <v>-7.0655755344125904E-5</v>
       </c>
       <c r="F19">
-        <v>4.6160765776884032E-4</v>
+        <v>2.5451582694271122E-4</v>
       </c>
       <c r="G19">
-        <v>-1.7150804829542973E-4</v>
+        <v>-2.7900812695077197E-5</v>
       </c>
       <c r="H19">
-        <v>-3.0001043364205875E-4</v>
+        <v>-2.9296018561280571E-4</v>
       </c>
       <c r="I19">
-        <v>3.4634410730365116E-4</v>
+        <v>3.4597382670133907E-4</v>
       </c>
       <c r="J19">
-        <v>-2.4309608939494971E-4</v>
+        <v>1.6548602395249868E-4</v>
       </c>
       <c r="K19">
-        <v>5.2607925337320419E-4</v>
+        <v>2.2249714862782819E-4</v>
       </c>
       <c r="L19">
-        <v>-5.9572135402678251E-4</v>
+        <v>-7.7484587303197356E-4</v>
       </c>
       <c r="M19">
-        <v>4.9039225871441152E-4</v>
+        <v>6.8722438862755554E-5</v>
       </c>
       <c r="N19">
-        <v>5.6017693657018849E-4</v>
+        <v>4.7268895731926403E-4</v>
       </c>
       <c r="O19">
-        <v>4.1233132527234643E-4</v>
+        <v>4.7133527909610758E-5</v>
       </c>
       <c r="P19">
-        <v>1.0098159573680193E-3</v>
+        <v>2.724471588862106E-4</v>
       </c>
       <c r="Q19">
-        <v>7.0866667334774686E-4</v>
+        <v>1.0582598932996662E-4</v>
       </c>
       <c r="R19">
-        <v>8.0080051136409552E-5</v>
+        <v>7.7678366691613025E-6</v>
       </c>
       <c r="S19">
-        <v>-4.1233822045834721E-4</v>
+        <v>-3.4913480720527969E-4</v>
       </c>
       <c r="T19">
-        <v>2.1050898451250084E-2</v>
+        <v>1.5120285672093241E-2</v>
       </c>
       <c r="U19">
-        <v>1.3657214587979635E-2</v>
+        <v>1.0632281348123808E-2</v>
       </c>
       <c r="V19">
-        <v>1.3758865059633339E-2</v>
+        <v>1.0693031288368045E-2</v>
       </c>
       <c r="W19">
-        <v>1.3641936676313964E-2</v>
+        <v>1.0628215737719177E-2</v>
       </c>
       <c r="X19">
-        <v>1.7354883684943603E-4</v>
+        <v>-1.6474010564720282E-4</v>
       </c>
       <c r="Y19">
-        <v>-4.9307108977384578E-5</v>
+        <v>-3.1084520862297189E-4</v>
       </c>
       <c r="Z19">
-        <v>2.4954970201134918E-5</v>
+        <v>1.5726308021182106E-5</v>
       </c>
       <c r="AA19">
-        <v>-1.3095176270771509E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+        <v>3.6525080024397624E-4</v>
+      </c>
+      <c r="AB19">
+        <v>-8.3548626537838233E-6</v>
+      </c>
+      <c r="AC19">
+        <v>-1.0418031623737355E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A20" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B20">
-        <v>8.6534501125940619E-2</v>
+      <c r="B20" s="6">
+        <v>0.12869295117814855</v>
       </c>
       <c r="C20">
-        <v>-9.9942440618480544E-5</v>
+        <v>8.2571381940919788E-6</v>
       </c>
       <c r="D20">
-        <v>9.3372537852237623E-7</v>
+        <v>-2.014664334014142E-7</v>
       </c>
       <c r="E20">
-        <v>-1.4978393960504824E-4</v>
+        <v>-7.9132332565974854E-5</v>
       </c>
       <c r="F20">
-        <v>5.433477647007216E-4</v>
+        <v>2.9425065825773014E-4</v>
       </c>
       <c r="G20">
-        <v>5.164995881341833E-5</v>
+        <v>3.7353212408097384E-5</v>
       </c>
       <c r="H20">
-        <v>-5.7091648098929709E-4</v>
+        <v>-6.9008104198721291E-4</v>
       </c>
       <c r="I20">
-        <v>1.2417329787355422E-3</v>
+        <v>1.1108659131351683E-3</v>
       </c>
       <c r="J20">
-        <v>5.8312626585185399E-4</v>
+        <v>2.0168717913846218E-4</v>
       </c>
       <c r="K20">
-        <v>5.2121674809648571E-4</v>
+        <v>5.5804985500959104E-4</v>
       </c>
       <c r="L20">
-        <v>-1.3320515275652349E-3</v>
+        <v>-1.0899334739905707E-3</v>
       </c>
       <c r="M20">
-        <v>1.139447963041872E-3</v>
+        <v>2.9797695249173016E-4</v>
       </c>
       <c r="N20">
-        <v>5.8201761441521792E-4</v>
+        <v>1.7017996533063076E-4</v>
       </c>
       <c r="O20">
-        <v>4.9066015872077802E-4</v>
+        <v>-1.9596196261535811E-4</v>
       </c>
       <c r="P20">
-        <v>5.9346000763799557E-4</v>
+        <v>-9.56790048321568E-5</v>
       </c>
       <c r="Q20">
-        <v>6.165597625888274E-4</v>
+        <v>-2.9470999275142684E-4</v>
       </c>
       <c r="R20">
-        <v>-8.3358316056398837E-5</v>
+        <v>-1.58449691844575E-4</v>
       </c>
       <c r="S20">
-        <v>-2.3687243364836833E-4</v>
+        <v>-8.2938282876467834E-4</v>
       </c>
       <c r="T20">
-        <v>1.3657214587979635E-2</v>
+        <v>1.0632281348123808E-2</v>
       </c>
       <c r="U20">
-        <v>1.5784001941241153E-2</v>
+        <v>1.2213336119642506E-2</v>
       </c>
       <c r="V20">
-        <v>1.4185193970365238E-2</v>
+        <v>1.0969383641107069E-2</v>
       </c>
       <c r="W20">
-        <v>1.3923954202981779E-2</v>
+        <v>1.0818103184892434E-2</v>
       </c>
       <c r="X20">
-        <v>-1.0174057863306107E-5</v>
+        <v>-1.3927245806647295E-4</v>
       </c>
       <c r="Y20">
-        <v>-4.1319161747687544E-4</v>
+        <v>-4.8412535996072287E-4</v>
       </c>
       <c r="Z20">
-        <v>-2.2867363708429025E-5</v>
+        <v>5.0340055087793115E-6</v>
       </c>
       <c r="AA20">
-        <v>-1.2048105239722568E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+        <v>1.6018216002546427E-4</v>
+      </c>
+      <c r="AB20">
+        <v>2.1146914647735861E-4</v>
+      </c>
+      <c r="AC20">
+        <v>-1.0770325159951522E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A21" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B21">
-        <v>6.4919028466826595E-2</v>
+      <c r="B21" s="6">
+        <v>0.16802897526104865</v>
       </c>
       <c r="C21">
-        <v>-2.1073227776707956E-5</v>
+        <v>5.7835062224182571E-5</v>
       </c>
       <c r="D21">
-        <v>6.1979349151858002E-7</v>
+        <v>-3.6559205822970531E-7</v>
       </c>
       <c r="E21">
-        <v>1.7591994732640105E-4</v>
+        <v>2.2117416232010178E-4</v>
       </c>
       <c r="F21">
-        <v>1.3475010686484776E-3</v>
+        <v>1.0642959604795525E-3</v>
       </c>
       <c r="G21">
-        <v>-9.5963907302334868E-5</v>
+        <v>-2.2868275642699067E-5</v>
       </c>
       <c r="H21">
-        <v>-8.7058817626509469E-4</v>
+        <v>-1.0139989420001679E-3</v>
       </c>
       <c r="I21">
-        <v>1.1225279712322369E-3</v>
+        <v>1.0278868775958074E-3</v>
       </c>
       <c r="J21">
-        <v>3.3258977845107432E-4</v>
+        <v>-8.6184712382683659E-5</v>
       </c>
       <c r="K21">
-        <v>9.5136401283376758E-4</v>
+        <v>9.1399013156487786E-4</v>
       </c>
       <c r="L21">
-        <v>-9.4690802960886245E-4</v>
+        <v>-8.7699731079982318E-4</v>
       </c>
       <c r="M21">
-        <v>1.0777655476555625E-3</v>
+        <v>3.8582041358889917E-4</v>
       </c>
       <c r="N21">
-        <v>4.7793065696496106E-4</v>
+        <v>1.8375819833993596E-4</v>
       </c>
       <c r="O21">
-        <v>2.8460243003903358E-4</v>
+        <v>-4.0320853665659623E-4</v>
       </c>
       <c r="P21">
-        <v>3.8606410724178683E-5</v>
+        <v>-4.2679092005321094E-4</v>
       </c>
       <c r="Q21">
-        <v>-1.2591725299155871E-4</v>
+        <v>-7.4337175890838074E-4</v>
       </c>
       <c r="R21">
-        <v>-1.1804595636798201E-4</v>
+        <v>-3.1186973246714314E-4</v>
       </c>
       <c r="S21">
-        <v>-2.0810556537406721E-4</v>
+        <v>-8.7754915612128022E-4</v>
       </c>
       <c r="T21">
-        <v>1.3758865059633339E-2</v>
+        <v>1.0693031288368045E-2</v>
       </c>
       <c r="U21">
-        <v>1.4185193970365238E-2</v>
+        <v>1.0969383641107069E-2</v>
       </c>
       <c r="V21">
-        <v>1.6594060273769903E-2</v>
+        <v>1.2659002887720872E-2</v>
       </c>
       <c r="W21">
-        <v>1.5642135440714456E-2</v>
+        <v>1.2016143525800924E-2</v>
       </c>
       <c r="X21">
-        <v>-4.7918285639074465E-4</v>
+        <v>-4.767877229125677E-4</v>
       </c>
       <c r="Y21">
-        <v>-3.3609888553799358E-4</v>
+        <v>-4.6441317471203336E-4</v>
       </c>
       <c r="Z21">
-        <v>-8.4628292050113914E-6</v>
+        <v>-1.9717290832943057E-7</v>
       </c>
       <c r="AA21">
-        <v>-1.5765211356991552E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+        <v>2.099061411143955E-4</v>
+      </c>
+      <c r="AB21">
+        <v>7.950899157588686E-4</v>
+      </c>
+      <c r="AC21">
+        <v>-1.3154372114355902E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A22" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B22">
-        <v>-2.829347388483889E-3</v>
+      <c r="B22" s="6">
+        <v>7.3633925963644181E-2</v>
       </c>
       <c r="C22">
-        <v>1.0298972521610456E-4</v>
+        <v>1.2735351168067198E-4</v>
       </c>
       <c r="D22">
-        <v>-5.422534230578261E-7</v>
+        <v>-9.2195479166456578E-7</v>
       </c>
       <c r="E22">
-        <v>-3.7992267386487849E-4</v>
+        <v>-6.2626569550536379E-5</v>
       </c>
       <c r="F22">
-        <v>6.7107135308089804E-4</v>
+        <v>6.9181451473607084E-4</v>
       </c>
       <c r="G22">
-        <v>-5.0406943577341085E-4</v>
+        <v>-2.3425949705745526E-4</v>
       </c>
       <c r="H22">
-        <v>1.9343581507100856E-4</v>
+        <v>1.7380208556720331E-4</v>
       </c>
       <c r="I22">
-        <v>6.8300647557160586E-4</v>
+        <v>8.7855607215023344E-4</v>
       </c>
       <c r="J22">
-        <v>5.120380966654051E-5</v>
+        <v>-2.0493083256695362E-4</v>
       </c>
       <c r="K22">
-        <v>-7.1366723973095814E-4</v>
+        <v>-4.7345367227311872E-4</v>
       </c>
       <c r="L22">
-        <v>-1.0031599033056592E-3</v>
+        <v>-7.452637607738078E-4</v>
       </c>
       <c r="M22">
-        <v>1.3369188406740047E-3</v>
+        <v>5.5864721187526766E-4</v>
       </c>
       <c r="N22">
-        <v>1.0662720434685133E-3</v>
+        <v>3.4324658439240888E-4</v>
       </c>
       <c r="O22">
-        <v>6.7830259065809794E-4</v>
+        <v>-8.3316199019728269E-5</v>
       </c>
       <c r="P22">
-        <v>-1.7377450182778074E-4</v>
+        <v>-4.3573888339197868E-4</v>
       </c>
       <c r="Q22">
-        <v>-9.8275903050604836E-4</v>
+        <v>-8.4113256083483069E-4</v>
       </c>
       <c r="R22">
-        <v>-1.60156348108151E-4</v>
+        <v>-2.5068015228892228E-4</v>
       </c>
       <c r="S22">
-        <v>3.5117197099119495E-4</v>
+        <v>-6.8549508235282535E-4</v>
       </c>
       <c r="T22">
-        <v>1.3641936676313964E-2</v>
+        <v>1.0628215737719177E-2</v>
       </c>
       <c r="U22">
-        <v>1.3923954202981779E-2</v>
+        <v>1.0818103184892434E-2</v>
       </c>
       <c r="V22">
-        <v>1.5642135440714456E-2</v>
+        <v>1.2016143525800924E-2</v>
       </c>
       <c r="W22">
-        <v>1.855648480801559E-2</v>
+        <v>1.4169060572959141E-2</v>
       </c>
       <c r="X22">
-        <v>-5.827336960628586E-4</v>
+        <v>-5.3300528941467237E-4</v>
       </c>
       <c r="Y22">
-        <v>-7.2733334824645265E-4</v>
+        <v>-6.6675329421667442E-4</v>
       </c>
       <c r="Z22">
-        <v>-1.2437875459830189E-6</v>
+        <v>2.6805619387020811E-6</v>
       </c>
       <c r="AA22">
-        <v>-1.7825640160963992E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+        <v>2.1451878484846955E-5</v>
+      </c>
+      <c r="AB22">
+        <v>8.1328714457672147E-6</v>
+      </c>
+      <c r="AC22">
+        <v>-1.4688438885428418E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A23" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B23">
-        <v>7.6944426232280025E-2</v>
+      <c r="B23" s="6">
+        <v>6.8557430226142302E-2</v>
       </c>
       <c r="C23">
-        <v>-2.0892343686299691E-5</v>
+        <v>-2.9693500119010348E-5</v>
       </c>
       <c r="D23">
-        <v>1.4427746893717043E-7</v>
+        <v>2.3049860915558057E-7</v>
       </c>
       <c r="E23">
-        <v>6.8132918067830527E-4</v>
+        <v>1.4310500612577158E-4</v>
       </c>
       <c r="F23">
-        <v>4.302315724270785E-4</v>
+        <v>-9.2152882640451688E-5</v>
       </c>
       <c r="G23">
-        <v>8.7985231420631199E-5</v>
+        <v>-1.2149062463784289E-6</v>
       </c>
       <c r="H23">
-        <v>-2.0664755103784469E-3</v>
+        <v>-1.6574989059658695E-3</v>
       </c>
       <c r="I23">
-        <v>-1.3860929839552491E-4</v>
+        <v>-2.5055999157076302E-4</v>
       </c>
       <c r="J23">
-        <v>-2.0807174473237364E-5</v>
+        <v>1.4586561471782982E-4</v>
       </c>
       <c r="K23">
-        <v>2.1497128627029527E-3</v>
+        <v>1.8916310297124373E-3</v>
       </c>
       <c r="L23">
-        <v>2.9263498417931872E-4</v>
+        <v>4.0981457064831407E-4</v>
       </c>
       <c r="M23">
-        <v>-1.1231331845550497E-5</v>
+        <v>2.209056221151905E-4</v>
       </c>
       <c r="N23">
-        <v>-2.8237996168933117E-4</v>
+        <v>-1.0855244209454634E-4</v>
       </c>
       <c r="O23">
-        <v>-7.8170099441514504E-4</v>
+        <v>-2.0960155934235739E-4</v>
       </c>
       <c r="P23">
-        <v>-7.2959975759344983E-4</v>
+        <v>-3.0580024753550073E-4</v>
       </c>
       <c r="Q23">
-        <v>6.5152353114273634E-4</v>
+        <v>4.0183214118862652E-4</v>
       </c>
       <c r="R23">
-        <v>2.1877481168000373E-4</v>
+        <v>2.9419560829470109E-4</v>
       </c>
       <c r="S23">
-        <v>-1.805411286487747E-4</v>
+        <v>3.2625111195169862E-4</v>
       </c>
       <c r="T23">
-        <v>1.7354883684943603E-4</v>
+        <v>-1.6474010564720282E-4</v>
       </c>
       <c r="U23">
-        <v>-1.0174057863306107E-5</v>
+        <v>-1.3927245806647295E-4</v>
       </c>
       <c r="V23">
-        <v>-4.7918285639074465E-4</v>
+        <v>-4.767877229125677E-4</v>
       </c>
       <c r="W23">
-        <v>-5.827336960628586E-4</v>
+        <v>-5.3300528941467237E-4</v>
       </c>
       <c r="X23">
-        <v>4.1612273694183171E-3</v>
+        <v>2.993048373452413E-3</v>
       </c>
       <c r="Y23">
-        <v>2.7047518111831589E-3</v>
+        <v>1.9307703813802412E-3</v>
       </c>
       <c r="Z23">
-        <v>-8.1127716390273151E-5</v>
+        <v>-3.6306919497163347E-5</v>
       </c>
       <c r="AA23">
-        <v>-6.0098143725287822E-4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+        <v>2.6552810859410805E-4</v>
+      </c>
+      <c r="AB23">
+        <v>3.1022927700085343E-4</v>
+      </c>
+      <c r="AC23">
+        <v>-1.7311516825233161E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A24" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B24">
-        <v>0.12998588984980533</v>
+      <c r="B24" s="6">
+        <v>9.5931038569342555E-2</v>
       </c>
       <c r="C24">
-        <v>5.6416418968749556E-5</v>
+        <v>1.5571456501394876E-5</v>
       </c>
       <c r="D24">
-        <v>-7.0435708457544893E-7</v>
+        <v>-2.4775433473414816E-7</v>
       </c>
       <c r="E24">
-        <v>7.5400158646880963E-4</v>
+        <v>2.0958957240459208E-4</v>
       </c>
       <c r="F24">
-        <v>7.8545716169021508E-4</v>
+        <v>9.75061225358528E-6</v>
       </c>
       <c r="G24">
-        <v>9.5646189017572873E-5</v>
+        <v>3.8817223602476397E-6</v>
       </c>
       <c r="H24">
-        <v>-2.13823787804804E-3</v>
+        <v>-1.817737952112976E-3</v>
       </c>
       <c r="I24">
-        <v>-4.6118670933585366E-4</v>
+        <v>-5.1061968759366421E-4</v>
       </c>
       <c r="J24">
-        <v>1.2132702993473618E-4</v>
+        <v>5.4613466622904609E-5</v>
       </c>
       <c r="K24">
-        <v>2.0753740798782395E-3</v>
+        <v>1.7953279806870353E-3</v>
       </c>
       <c r="L24">
-        <v>9.1734619175477057E-5</v>
+        <v>1.9697691120778031E-4</v>
       </c>
       <c r="M24">
-        <v>-1.4576067372752536E-4</v>
+        <v>1.0976828877673516E-4</v>
       </c>
       <c r="N24">
-        <v>-4.3513470225888234E-4</v>
+        <v>-2.0320986415811766E-4</v>
       </c>
       <c r="O24">
-        <v>-1.2344973092794139E-3</v>
+        <v>-6.9472513965679588E-4</v>
       </c>
       <c r="P24">
-        <v>-1.282099891861867E-3</v>
+        <v>-7.686465575673534E-4</v>
       </c>
       <c r="Q24">
-        <v>4.031638443363619E-4</v>
+        <v>4.9801166914767523E-5</v>
       </c>
       <c r="R24">
-        <v>1.2077484544108138E-5</v>
+        <v>1.2275298457496459E-4</v>
       </c>
       <c r="S24">
-        <v>1.1630789630579056E-4</v>
+        <v>3.8044103316776619E-4</v>
       </c>
       <c r="T24">
-        <v>-4.9307108977384578E-5</v>
+        <v>-3.1084520862297189E-4</v>
       </c>
       <c r="U24">
-        <v>-4.1319161747687544E-4</v>
+        <v>-4.8412535996072287E-4</v>
       </c>
       <c r="V24">
-        <v>-3.3609888553799358E-4</v>
+        <v>-4.6441317471203336E-4</v>
       </c>
       <c r="W24">
-        <v>-7.2733334824645265E-4</v>
+        <v>-6.6675329421667442E-4</v>
       </c>
       <c r="X24">
-        <v>2.7047518111831589E-3</v>
+        <v>1.9307703813802412E-3</v>
       </c>
       <c r="Y24">
-        <v>3.6874561843150055E-3</v>
+        <v>2.6530277537297033E-3</v>
       </c>
       <c r="Z24">
-        <v>-7.0461202551461784E-5</v>
+        <v>-2.9699716338749702E-5</v>
       </c>
       <c r="AA24">
-        <v>-1.9366476824054304E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+        <v>2.2535135737314035E-4</v>
+      </c>
+      <c r="AB24">
+        <v>1.5448814658788304E-4</v>
+      </c>
+      <c r="AC24">
+        <v>-7.4866533992788405E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A25" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B25">
-        <v>1.9952422223041156E-2</v>
+      <c r="B25" s="6">
+        <v>2.1137107329079804E-2</v>
       </c>
       <c r="C25">
-        <v>4.667843896244959E-6</v>
+        <v>1.9103593262135595E-6</v>
       </c>
       <c r="D25">
-        <v>-7.1458661797853307E-8</v>
+        <v>-3.5130397686171473E-8</v>
       </c>
       <c r="E25">
-        <v>-6.836835451377632E-5</v>
+        <v>-5.2024431154068301E-6</v>
       </c>
       <c r="F25">
-        <v>-8.2062628164357053E-5</v>
+        <v>-1.5558917202512836E-5</v>
       </c>
       <c r="G25">
-        <v>-2.3984382686234568E-5</v>
+        <v>-2.2494839677385872E-5</v>
       </c>
       <c r="H25">
-        <v>5.1934087150985872E-5</v>
+        <v>-5.4038324636060072E-5</v>
       </c>
       <c r="I25">
-        <v>-9.1069452709808922E-6</v>
+        <v>3.9187170841608536E-5</v>
       </c>
       <c r="J25">
-        <v>2.3505173801232574E-5</v>
+        <v>4.5010309024486181E-5</v>
       </c>
       <c r="K25">
-        <v>-1.5070820231747413E-4</v>
+        <v>-2.0251937180575481E-5</v>
       </c>
       <c r="L25">
-        <v>9.1022961017378655E-5</v>
+        <v>1.8945770379804294E-5</v>
       </c>
       <c r="M25">
-        <v>3.568860364640798E-5</v>
+        <v>6.6179604842931515E-6</v>
       </c>
       <c r="N25">
-        <v>4.9348928742859151E-5</v>
+        <v>1.8166145719491827E-6</v>
       </c>
       <c r="O25">
-        <v>1.0266629142124256E-4</v>
+        <v>-2.3976194332510535E-5</v>
       </c>
       <c r="P25">
-        <v>1.1556183426585467E-5</v>
+        <v>-1.9214806648198713E-5</v>
       </c>
       <c r="Q25">
-        <v>4.2667418071579664E-6</v>
+        <v>-8.9654769154273088E-6</v>
       </c>
       <c r="R25">
-        <v>-7.6922085612075297E-6</v>
+        <v>-6.5384882094179922E-6</v>
       </c>
       <c r="S25">
-        <v>1.4016874306176796E-5</v>
+        <v>-3.3363827859303949E-5</v>
       </c>
       <c r="T25">
-        <v>2.4954970201134918E-5</v>
+        <v>1.5726308021182106E-5</v>
       </c>
       <c r="U25">
-        <v>-2.2867363708429025E-5</v>
+        <v>5.0340055087793115E-6</v>
       </c>
       <c r="V25">
-        <v>-8.4628292050113914E-6</v>
+        <v>-1.9717290832943057E-7</v>
       </c>
       <c r="W25">
-        <v>-1.2437875459830189E-6</v>
+        <v>2.6805619387020811E-6</v>
       </c>
       <c r="X25">
-        <v>-8.1127716390273151E-5</v>
+        <v>-3.6306919497163347E-5</v>
       </c>
       <c r="Y25">
-        <v>-7.0461202551461784E-5</v>
+        <v>-2.9699716338749702E-5</v>
       </c>
       <c r="Z25">
-        <v>6.4091161788084293E-5</v>
+        <v>2.5350097941227414E-5</v>
       </c>
       <c r="AA25">
-        <v>-9.3480518680893055E-4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+        <v>-9.0219542773908607E-5</v>
+      </c>
+      <c r="AB25">
+        <v>-1.0992279745450199E-4</v>
+      </c>
+      <c r="AC25">
+        <v>-3.8605189115919905E-4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A26" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="6">
+        <v>1.6211536031281167E-2</v>
+      </c>
+      <c r="C26">
+        <v>1.8223907379184856E-5</v>
+      </c>
+      <c r="D26">
+        <v>-1.3754759373152996E-7</v>
+      </c>
+      <c r="E26">
+        <v>-1.8095922953169277E-5</v>
+      </c>
+      <c r="F26">
+        <v>1.6351182800877469E-5</v>
+      </c>
+      <c r="G26">
+        <v>-2.5206524173308466E-5</v>
+      </c>
+      <c r="H26">
+        <v>-1.7632171503473076E-4</v>
+      </c>
+      <c r="I26">
+        <v>-4.7728506253634593E-4</v>
+      </c>
+      <c r="J26">
+        <v>-6.2434279132598776E-4</v>
+      </c>
+      <c r="K26">
+        <v>2.7645451651173928E-4</v>
+      </c>
+      <c r="L26">
+        <v>5.6063878474343161E-4</v>
+      </c>
+      <c r="M26">
+        <v>1.0637931976069448E-4</v>
+      </c>
+      <c r="N26">
+        <v>8.9633511359965426E-5</v>
+      </c>
+      <c r="O26">
+        <v>4.15171102766153E-4</v>
+      </c>
+      <c r="P26">
+        <v>-8.8753253829328008E-5</v>
+      </c>
+      <c r="Q26">
+        <v>-2.2250874877568095E-4</v>
+      </c>
+      <c r="R26">
+        <v>-9.3122343941148898E-5</v>
+      </c>
+      <c r="S26">
+        <v>4.3115379721879921E-4</v>
+      </c>
+      <c r="T26">
+        <v>3.6525080024397624E-4</v>
+      </c>
+      <c r="U26">
+        <v>1.6018216002546427E-4</v>
+      </c>
+      <c r="V26">
+        <v>2.099061411143955E-4</v>
+      </c>
+      <c r="W26">
+        <v>2.1451878484846955E-5</v>
+      </c>
+      <c r="X26">
+        <v>2.6552810859410805E-4</v>
+      </c>
+      <c r="Y26">
+        <v>2.2535135737314035E-4</v>
+      </c>
+      <c r="Z26">
+        <v>-9.0219542773908607E-5</v>
+      </c>
+      <c r="AA26">
+        <v>6.1383666661691087E-3</v>
+      </c>
+      <c r="AB26">
+        <v>7.7698549553531049E-4</v>
+      </c>
+      <c r="AC26">
+        <v>3.9780878682936461E-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A27" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" s="6">
+        <v>0.10605473442646296</v>
+      </c>
+      <c r="C27">
+        <v>8.9907345621433564E-5</v>
+      </c>
+      <c r="D27">
+        <v>-1.0212721864964888E-6</v>
+      </c>
+      <c r="E27">
+        <v>4.234934148419692E-4</v>
+      </c>
+      <c r="F27">
+        <v>8.0779903324818729E-4</v>
+      </c>
+      <c r="G27">
+        <v>9.6466756696710087E-5</v>
+      </c>
+      <c r="H27">
+        <v>-1.3129186436465915E-3</v>
+      </c>
+      <c r="I27">
+        <v>-8.2569422329143794E-4</v>
+      </c>
+      <c r="J27">
+        <v>-1.2402345621786229E-3</v>
+      </c>
+      <c r="K27">
+        <v>1.9855477532711207E-4</v>
+      </c>
+      <c r="L27">
+        <v>-6.9788838680985674E-4</v>
+      </c>
+      <c r="M27">
+        <v>2.0755313689475321E-4</v>
+      </c>
+      <c r="N27">
+        <v>-5.6074645555351395E-4</v>
+      </c>
+      <c r="O27">
+        <v>-1.308829307843069E-3</v>
+      </c>
+      <c r="P27">
+        <v>-1.8935727230870089E-3</v>
+      </c>
+      <c r="Q27">
+        <v>-1.8343939942014307E-3</v>
+      </c>
+      <c r="R27">
+        <v>-2.329651980999567E-4</v>
+      </c>
+      <c r="S27">
+        <v>-8.3520032803129259E-5</v>
+      </c>
+      <c r="T27">
+        <v>-8.3548626537838233E-6</v>
+      </c>
+      <c r="U27">
+        <v>2.1146914647735861E-4</v>
+      </c>
+      <c r="V27">
+        <v>7.950899157588686E-4</v>
+      </c>
+      <c r="W27">
+        <v>8.1328714457672147E-6</v>
+      </c>
+      <c r="X27">
+        <v>3.1022927700085343E-4</v>
+      </c>
+      <c r="Y27">
+        <v>1.5448814658788304E-4</v>
+      </c>
+      <c r="Z27">
+        <v>-1.0992279745450199E-4</v>
+      </c>
+      <c r="AA27">
+        <v>7.7698549553531049E-4</v>
+      </c>
+      <c r="AB27">
+        <v>9.7103700888895098E-3</v>
+      </c>
+      <c r="AC27">
+        <v>4.2529445876863874E-4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A28" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B26">
-        <v>-2.7816446672343025</v>
-      </c>
-      <c r="C26">
-        <v>-1.868090169805151E-3</v>
-      </c>
-      <c r="D26">
-        <v>1.9700787690689118E-5</v>
-      </c>
-      <c r="E26">
-        <v>-2.9512225068044854E-3</v>
-      </c>
-      <c r="F26">
-        <v>-2.5917155908881358E-3</v>
-      </c>
-      <c r="G26">
-        <v>-1.6863565025339161E-3</v>
-      </c>
-      <c r="H26">
-        <v>-1.0664949113431455E-2</v>
-      </c>
-      <c r="I26">
-        <v>-2.6387004310563919E-3</v>
-      </c>
-      <c r="J26">
-        <v>-9.1164263859241628E-3</v>
-      </c>
-      <c r="K26">
-        <v>6.3833446360026134E-3</v>
-      </c>
-      <c r="L26">
-        <v>1.8115782449125832E-3</v>
-      </c>
-      <c r="M26">
-        <v>4.0348999305787857E-3</v>
-      </c>
-      <c r="N26">
-        <v>-5.328626199042872E-3</v>
-      </c>
-      <c r="O26">
-        <v>-4.2892678210792994E-3</v>
-      </c>
-      <c r="P26">
-        <v>-2.5083576354563457E-3</v>
-      </c>
-      <c r="Q26">
-        <v>-4.1214885371252969E-3</v>
-      </c>
-      <c r="R26">
-        <v>-3.8669146147274824E-4</v>
-      </c>
-      <c r="S26">
-        <v>-1.5050613455802806E-3</v>
-      </c>
-      <c r="T26">
-        <v>-1.3095176270771509E-2</v>
-      </c>
-      <c r="U26">
-        <v>-1.2048105239722568E-2</v>
-      </c>
-      <c r="V26">
-        <v>-1.5765211356991552E-2</v>
-      </c>
-      <c r="W26">
-        <v>-1.7825640160963992E-2</v>
-      </c>
-      <c r="X26">
-        <v>-6.0098143725287822E-4</v>
-      </c>
-      <c r="Y26">
-        <v>-1.9366476824054304E-3</v>
-      </c>
-      <c r="Z26">
-        <v>-9.3480518680893055E-4</v>
-      </c>
-      <c r="AA26">
-        <v>7.7385148269095677E-2</v>
+      <c r="B28" s="6">
+        <v>-2.6163331530443088</v>
+      </c>
+      <c r="C28">
+        <v>-1.2876505408453084E-3</v>
+      </c>
+      <c r="D28">
+        <v>1.3313527183669973E-5</v>
+      </c>
+      <c r="E28">
+        <v>-2.5315590998353527E-3</v>
+      </c>
+      <c r="F28">
+        <v>-3.3957799221103792E-3</v>
+      </c>
+      <c r="G28">
+        <v>-1.2241651038162791E-3</v>
+      </c>
+      <c r="H28">
+        <v>-7.9062341569965614E-3</v>
+      </c>
+      <c r="I28">
+        <v>-4.9304255007563882E-3</v>
+      </c>
+      <c r="J28">
+        <v>-7.7714187707702779E-3</v>
+      </c>
+      <c r="K28">
+        <v>3.1621900597430348E-3</v>
+      </c>
+      <c r="L28">
+        <v>1.903852150848664E-3</v>
+      </c>
+      <c r="M28">
+        <v>2.2588095494599772E-3</v>
+      </c>
+      <c r="N28">
+        <v>-3.0868922110899857E-3</v>
+      </c>
+      <c r="O28">
+        <v>-2.5873291793113381E-3</v>
+      </c>
+      <c r="P28">
+        <v>-3.1244484805339062E-3</v>
+      </c>
+      <c r="Q28">
+        <v>-3.4523671935213435E-3</v>
+      </c>
+      <c r="R28">
+        <v>9.1456124613094759E-4</v>
+      </c>
+      <c r="S28">
+        <v>-3.0196220894084045E-4</v>
+      </c>
+      <c r="T28">
+        <v>-1.0418031623737355E-2</v>
+      </c>
+      <c r="U28">
+        <v>-1.0770325159951522E-2</v>
+      </c>
+      <c r="V28">
+        <v>-1.3154372114355902E-2</v>
+      </c>
+      <c r="W28">
+        <v>-1.4688438885428418E-2</v>
+      </c>
+      <c r="X28">
+        <v>-1.7311516825233161E-4</v>
+      </c>
+      <c r="Y28">
+        <v>-7.4866533992788405E-4</v>
+      </c>
+      <c r="Z28">
+        <v>-3.8605189115919905E-4</v>
+      </c>
+      <c r="AA28">
+        <v>3.9780878682936461E-4</v>
+      </c>
+      <c r="AB28">
+        <v>4.2529445876863874E-4</v>
+      </c>
+      <c r="AC28">
+        <v>5.4091896492213999E-2</v>
       </c>
     </row>
   </sheetData>
@@ -3501,17 +3841,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB23CB7F-C1D3-4667-AC86-F85D5E3D71F0}">
-  <dimension ref="A1:AD29"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AF31"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="6" t="s">
         <v>66</v>
       </c>
       <c r="C1" t="s">
@@ -3596,2583 +3936,2953 @@
         <v>33</v>
       </c>
       <c r="AD1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>-9.8715996796744834E-3</v>
+      <c r="B2" s="6">
+        <v>-2.2018039255952342E-2</v>
       </c>
       <c r="C2">
-        <v>1.2902034712120673E-4</v>
+        <v>1.0647436835097816E-4</v>
       </c>
       <c r="D2">
-        <v>-1.1165363552281048E-6</v>
+        <v>-9.1316831405725799E-7</v>
       </c>
       <c r="E2">
-        <v>-7.5586951480558938E-5</v>
+        <v>-3.5289556556885953E-5</v>
       </c>
       <c r="F2">
-        <v>-3.9918610338812808E-5</v>
+        <v>-5.4478820870194859E-6</v>
       </c>
       <c r="G2">
-        <v>2.9733120026595862E-5</v>
+        <v>-6.4110563983165759E-6</v>
       </c>
       <c r="H2">
-        <v>7.1236228852620929E-5</v>
+        <v>-8.0640460991758642E-6</v>
       </c>
       <c r="I2">
-        <v>-1.2763271192856067E-4</v>
+        <v>-7.8991900242596658E-5</v>
       </c>
       <c r="J2">
-        <v>-1.2646396263698277E-4</v>
+        <v>-7.5761662336525017E-5</v>
       </c>
       <c r="K2">
-        <v>-1.6452442733559582E-5</v>
+        <v>-2.3666840433689927E-5</v>
       </c>
       <c r="L2">
-        <v>-2.0599599342434674E-4</v>
+        <v>-1.5718446725152555E-4</v>
       </c>
       <c r="M2">
-        <v>5.2812551407837097E-9</v>
+        <v>7.6546862329193168E-6</v>
       </c>
       <c r="N2">
-        <v>-5.1135979701289208E-5</v>
+        <v>-3.5770529891458638E-5</v>
       </c>
       <c r="O2">
-        <v>7.0912160548793784E-5</v>
+        <v>5.4050735389449855E-5</v>
       </c>
       <c r="P2">
-        <v>2.4153807288942823E-4</v>
+        <v>2.0696059228727276E-4</v>
       </c>
       <c r="Q2">
-        <v>-3.3989659233709372E-5</v>
+        <v>-1.3412683638652849E-5</v>
       </c>
       <c r="R2">
-        <v>9.133883271685711E-4</v>
+        <v>9.0046885170894445E-4</v>
       </c>
       <c r="S2">
-        <v>-6.9292455370259963E-6</v>
+        <v>-1.7955110280620017E-6</v>
       </c>
       <c r="T2">
-        <v>-3.3870549460523602E-5</v>
+        <v>3.8382325664881265E-5</v>
       </c>
       <c r="U2">
-        <v>1.9801894684279617E-4</v>
+        <v>3.8090811983070302E-5</v>
       </c>
       <c r="V2">
-        <v>-1.1703242075174767E-4</v>
+        <v>-8.6828576679871556E-5</v>
       </c>
       <c r="W2">
-        <v>3.5562492979773888E-5</v>
+        <v>5.6033772668763427E-6</v>
       </c>
       <c r="X2">
-        <v>4.8445654155235881E-6</v>
+        <v>3.1592115263134424E-5</v>
       </c>
       <c r="Y2">
-        <v>-1.0789094434702941E-5</v>
+        <v>-1.7480759087325443E-6</v>
       </c>
       <c r="Z2">
-        <v>-6.6537400118598603E-7</v>
+        <v>6.0230660932944317E-7</v>
       </c>
       <c r="AA2">
-        <v>-1.6301977568594335E-4</v>
+        <v>-1.6278069639933529E-4</v>
       </c>
       <c r="AB2">
-        <v>-1.1976712083592266E-4</v>
+        <v>-1.2410676048442947E-4</v>
       </c>
       <c r="AC2">
-        <v>8.9645053744355279E-6</v>
+        <v>-7.7027230271747816E-7</v>
       </c>
       <c r="AD2">
-        <v>-3.3567715897170553E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+        <v>7.3861203519133718E-5</v>
+      </c>
+      <c r="AE2">
+        <v>-1.0199386846639481E-5</v>
+      </c>
+      <c r="AF2">
+        <v>-2.7346799284920782E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>2.1078384451805299E-4</v>
+      <c r="B3" s="6">
+        <v>3.159030843789998E-4</v>
       </c>
       <c r="C3">
-        <v>-1.1165363552281048E-6</v>
+        <v>-9.1316831405725799E-7</v>
       </c>
       <c r="D3">
-        <v>1.0217851210699728E-8</v>
+        <v>8.2437386299875871E-9</v>
       </c>
       <c r="E3">
-        <v>5.5716769385686949E-7</v>
+        <v>2.3912326550682891E-7</v>
       </c>
       <c r="F3">
-        <v>1.8299094856058205E-7</v>
+        <v>-7.7929930846856177E-8</v>
       </c>
       <c r="G3">
-        <v>1.2657967833590781E-7</v>
+        <v>2.7031261490847756E-7</v>
       </c>
       <c r="H3">
-        <v>-2.3372817133875018E-7</v>
+        <v>2.5865230771609484E-7</v>
       </c>
       <c r="I3">
-        <v>1.0830154478133442E-6</v>
+        <v>6.6646891063212033E-7</v>
       </c>
       <c r="J3">
-        <v>1.0932758889978531E-6</v>
+        <v>6.4596684131072603E-7</v>
       </c>
       <c r="K3">
-        <v>3.2562211283780671E-7</v>
+        <v>3.5058844031807069E-7</v>
       </c>
       <c r="L3">
-        <v>1.5227370097081709E-6</v>
+        <v>1.2598011457956303E-6</v>
       </c>
       <c r="M3">
-        <v>-2.8503973303184574E-8</v>
+        <v>-7.9016667526494513E-8</v>
       </c>
       <c r="N3">
-        <v>2.8581917186769172E-7</v>
+        <v>2.0296195944636791E-7</v>
       </c>
       <c r="O3">
-        <v>-4.2475812022058375E-7</v>
+        <v>-3.5578084280068162E-7</v>
       </c>
       <c r="P3">
-        <v>-1.4600920086123375E-6</v>
+        <v>-1.4698605737466175E-6</v>
       </c>
       <c r="Q3">
-        <v>2.3004539478438686E-7</v>
+        <v>7.4623833711695237E-8</v>
       </c>
       <c r="R3">
-        <v>-6.4421137133345422E-6</v>
+        <v>-6.3856697760577704E-6</v>
       </c>
       <c r="S3">
-        <v>2.0516899362250907E-8</v>
+        <v>-1.3976727754325782E-8</v>
       </c>
       <c r="T3">
-        <v>5.8075930602089375E-7</v>
+        <v>-1.0084427138470514E-7</v>
       </c>
       <c r="U3">
-        <v>-1.3069421735541475E-6</v>
+        <v>-1.6234633934936216E-7</v>
       </c>
       <c r="V3">
-        <v>1.0811929010068969E-6</v>
+        <v>7.5321982589755599E-7</v>
       </c>
       <c r="W3">
-        <v>-4.5616439824163679E-7</v>
+        <v>-1.9887492688959488E-7</v>
       </c>
       <c r="X3">
-        <v>-8.1921663266900431E-7</v>
+        <v>-8.3815158119837034E-7</v>
       </c>
       <c r="Y3">
-        <v>1.217690790768251E-7</v>
+        <v>3.7341272887660509E-8</v>
       </c>
       <c r="Z3">
-        <v>-4.184032750873903E-8</v>
+        <v>-3.7792549415255948E-8</v>
       </c>
       <c r="AA3">
-        <v>1.3295155588514075E-6</v>
+        <v>1.330686073849671E-6</v>
       </c>
       <c r="AB3">
-        <v>1.080225374529677E-6</v>
+        <v>1.1107980010601134E-6</v>
       </c>
       <c r="AC3">
-        <v>-9.9747076246547744E-8</v>
+        <v>-9.4819608590898977E-9</v>
       </c>
       <c r="AD3">
-        <v>2.7253982962244117E-5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+        <v>-5.9645218572987454E-7</v>
+      </c>
+      <c r="AE3">
+        <v>1.6152166128984766E-8</v>
+      </c>
+      <c r="AF3">
+        <v>2.218125414983913E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B4">
-        <v>-2.9996296770750878E-2</v>
+      <c r="B4" s="6">
+        <v>-1.8096698204425445E-3</v>
       </c>
       <c r="C4">
-        <v>-7.5586951480558938E-5</v>
+        <v>-3.5289556556885953E-5</v>
       </c>
       <c r="D4">
-        <v>5.5716769385686949E-7</v>
+        <v>2.3912326550682891E-7</v>
       </c>
       <c r="E4">
-        <v>4.2910927196898882E-3</v>
+        <v>2.9708449733539294E-3</v>
       </c>
       <c r="F4">
-        <v>3.7959974089467404E-3</v>
+        <v>2.6401126390835621E-3</v>
       </c>
       <c r="G4">
-        <v>-2.0693891309364436E-3</v>
+        <v>-1.0965802250434231E-3</v>
       </c>
       <c r="H4">
-        <v>-2.2900561471444385E-3</v>
+        <v>-1.2837996055304628E-3</v>
       </c>
       <c r="I4">
-        <v>-3.8209112523353983E-5</v>
+        <v>4.965174821357421E-5</v>
       </c>
       <c r="J4">
-        <v>3.1822582780942658E-4</v>
+        <v>2.1676731857559468E-4</v>
       </c>
       <c r="K4">
-        <v>-1.3131152021966929E-4</v>
+        <v>1.0363109802346379E-4</v>
       </c>
       <c r="L4">
-        <v>3.0711241445923756E-4</v>
+        <v>-5.8645518278625493E-5</v>
       </c>
       <c r="M4">
-        <v>1.4980789934574508E-7</v>
+        <v>-3.4928813899106573E-5</v>
       </c>
       <c r="N4">
-        <v>-2.4022397956307358E-4</v>
+        <v>2.796850304904727E-5</v>
       </c>
       <c r="O4">
-        <v>3.6775934799998143E-4</v>
+        <v>1.287523391565828E-4</v>
       </c>
       <c r="P4">
-        <v>-1.9641372325281868E-4</v>
+        <v>3.6816114915567738E-4</v>
       </c>
       <c r="Q4">
-        <v>-2.6029101506552544E-6</v>
+        <v>9.0781108738329305E-5</v>
       </c>
       <c r="R4">
-        <v>-1.5503571593261534E-3</v>
+        <v>-1.4804492174878355E-3</v>
       </c>
       <c r="S4">
-        <v>2.540831527178121E-5</v>
+        <v>9.4875453435220044E-6</v>
       </c>
       <c r="T4">
-        <v>1.1370868876292921E-4</v>
+        <v>9.1717100797533558E-5</v>
       </c>
       <c r="U4">
-        <v>-2.1136660209210127E-4</v>
+        <v>-8.3498932950226695E-5</v>
       </c>
       <c r="V4">
-        <v>1.5656079715241288E-3</v>
+        <v>1.4156587835665555E-4</v>
       </c>
       <c r="W4">
-        <v>1.0004135531202726E-3</v>
+        <v>6.0495340076359753E-4</v>
       </c>
       <c r="X4">
-        <v>1.5549676921342603E-3</v>
+        <v>3.8207794346629406E-4</v>
       </c>
       <c r="Y4">
-        <v>1.6324932452880123E-4</v>
+        <v>3.3716480888306905E-5</v>
       </c>
       <c r="Z4">
-        <v>-1.2963511929662769E-4</v>
+        <v>4.019255945485821E-5</v>
       </c>
       <c r="AA4">
-        <v>4.0350009458330651E-4</v>
+        <v>-1.382617427276914E-4</v>
       </c>
       <c r="AB4">
-        <v>4.0134710336728037E-4</v>
+        <v>-9.0292619220349538E-5</v>
       </c>
       <c r="AC4">
-        <v>-9.5978944424619545E-5</v>
+        <v>-6.2534073427722745E-7</v>
       </c>
       <c r="AD4">
-        <v>2.1705805698139639E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+        <v>-3.1101141959164987E-4</v>
+      </c>
+      <c r="AE4">
+        <v>1.688453077583437E-4</v>
+      </c>
+      <c r="AF4">
+        <v>-8.1754932110142679E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B5">
-        <v>5.4353504830851232E-2</v>
+      <c r="B5" s="6">
+        <v>4.0227363697209251E-2</v>
       </c>
       <c r="C5">
-        <v>-3.9918610338812808E-5</v>
+        <v>-5.4478820870194859E-6</v>
       </c>
       <c r="D5">
-        <v>1.8299094856058205E-7</v>
+        <v>-7.7929930846856177E-8</v>
       </c>
       <c r="E5">
-        <v>3.7959974089467404E-3</v>
+        <v>2.6401126390835621E-3</v>
       </c>
       <c r="F5">
-        <v>6.109759899776742E-3</v>
+        <v>4.5331191273611749E-3</v>
       </c>
       <c r="G5">
-        <v>-2.4512349870596684E-3</v>
+        <v>-1.4205737979061705E-3</v>
       </c>
       <c r="H5">
-        <v>-4.0685324187376588E-3</v>
+        <v>-2.6794331690125832E-3</v>
       </c>
       <c r="I5">
-        <v>2.1892672545961305E-4</v>
+        <v>5.3856517666136039E-5</v>
       </c>
       <c r="J5">
-        <v>5.7905748733444928E-4</v>
+        <v>2.9414613530151425E-4</v>
       </c>
       <c r="K5">
-        <v>2.0063486414140193E-4</v>
+        <v>1.8520712326473832E-4</v>
       </c>
       <c r="L5">
-        <v>1.5552128695216227E-3</v>
+        <v>6.5748717005584571E-4</v>
       </c>
       <c r="M5">
-        <v>1.0922982729672886E-4</v>
+        <v>3.9750432967029759E-5</v>
       </c>
       <c r="N5">
-        <v>-3.4276378687588911E-5</v>
+        <v>1.5731405884457142E-4</v>
       </c>
       <c r="O5">
-        <v>5.1285471709014321E-4</v>
+        <v>2.7138208120149873E-4</v>
       </c>
       <c r="P5">
-        <v>-4.1988956632363822E-4</v>
+        <v>2.9876599947354873E-4</v>
       </c>
       <c r="Q5">
-        <v>-1.2381937600795896E-4</v>
+        <v>2.4209957147453091E-6</v>
       </c>
       <c r="R5">
-        <v>-4.1246569946116942E-4</v>
+        <v>-6.1515416376975787E-4</v>
       </c>
       <c r="S5">
-        <v>3.1127148270404169E-5</v>
+        <v>1.6283074279119469E-5</v>
       </c>
       <c r="T5">
-        <v>7.0095529154420191E-5</v>
+        <v>-9.5832877369391128E-6</v>
       </c>
       <c r="U5">
-        <v>-1.1467574183447689E-4</v>
+        <v>1.7074104313563178E-4</v>
       </c>
       <c r="V5">
-        <v>1.2471614351456843E-3</v>
+        <v>5.958112915693261E-5</v>
       </c>
       <c r="W5">
-        <v>8.8404302163382282E-4</v>
+        <v>4.7161838033296248E-4</v>
       </c>
       <c r="X5">
-        <v>1.3690305106246982E-3</v>
+        <v>3.1916844547943399E-4</v>
       </c>
       <c r="Y5">
-        <v>1.9067726172473167E-4</v>
+        <v>6.2959755369157135E-5</v>
       </c>
       <c r="Z5">
-        <v>-1.0244870217883265E-4</v>
+        <v>3.4880444615807806E-5</v>
       </c>
       <c r="AA5">
-        <v>1.9402012155253436E-4</v>
+        <v>-3.321115496248226E-4</v>
       </c>
       <c r="AB5">
-        <v>2.3380232001760505E-4</v>
+        <v>-2.426868033559423E-4</v>
       </c>
       <c r="AC5">
-        <v>-5.8386599492620835E-5</v>
+        <v>8.9179586546010107E-6</v>
       </c>
       <c r="AD5">
-        <v>-9.3402746847200862E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+        <v>-3.6062266910151563E-4</v>
+      </c>
+      <c r="AE5">
+        <v>-1.7795515442782376E-4</v>
+      </c>
+      <c r="AF5">
+        <v>-1.3217627658550005E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B6">
-        <v>5.0533469048888502E-2</v>
+      <c r="B6" s="6">
+        <v>4.3242271172059379E-2</v>
       </c>
       <c r="C6">
-        <v>2.9733120026595862E-5</v>
+        <v>-6.4110563983165759E-6</v>
       </c>
       <c r="D6">
-        <v>1.2657967833590781E-7</v>
+        <v>2.7031261490847756E-7</v>
       </c>
       <c r="E6">
-        <v>-2.0693891309364436E-3</v>
+        <v>-1.0965802250434231E-3</v>
       </c>
       <c r="F6">
-        <v>-2.4512349870596684E-3</v>
+        <v>-1.4205737979061705E-3</v>
       </c>
       <c r="G6">
-        <v>5.39240598998331E-3</v>
+        <v>3.6421000157521098E-3</v>
       </c>
       <c r="H6">
-        <v>5.1541137303345282E-3</v>
+        <v>3.4529499462131862E-3</v>
       </c>
       <c r="I6">
-        <v>-8.9273473839357193E-5</v>
+        <v>-3.1838798934320138E-5</v>
       </c>
       <c r="J6">
-        <v>-8.2433778155078922E-5</v>
+        <v>2.8356964922704436E-5</v>
       </c>
       <c r="K6">
-        <v>2.5530630731200512E-4</v>
+        <v>2.822477197953575E-5</v>
       </c>
       <c r="L6">
-        <v>-1.8208573318252044E-3</v>
+        <v>-1.1459393698880515E-3</v>
       </c>
       <c r="M6">
-        <v>1.1904294488733282E-4</v>
+        <v>2.1382769627584453E-4</v>
       </c>
       <c r="N6">
-        <v>2.1997374641936161E-4</v>
+        <v>8.7154667083394355E-5</v>
       </c>
       <c r="O6">
-        <v>5.063928424374059E-4</v>
+        <v>4.7608805057542471E-4</v>
       </c>
       <c r="P6">
-        <v>3.0833167772524998E-3</v>
+        <v>1.8313509466162592E-3</v>
       </c>
       <c r="Q6">
-        <v>2.3479236250703594E-5</v>
+        <v>-2.6242186339707665E-5</v>
       </c>
       <c r="R6">
-        <v>-4.2358129492047602E-3</v>
+        <v>-3.3383245527403441E-3</v>
       </c>
       <c r="S6">
-        <v>-5.8691425368852383E-5</v>
+        <v>-1.98293355785714E-5</v>
       </c>
       <c r="T6">
-        <v>1.5716659929154595E-4</v>
+        <v>1.7075448901746228E-4</v>
       </c>
       <c r="U6">
-        <v>5.7737052293500347E-4</v>
+        <v>5.1218098524073155E-4</v>
       </c>
       <c r="V6">
-        <v>-6.3279282224828928E-4</v>
+        <v>2.6963927923996217E-4</v>
       </c>
       <c r="W6">
-        <v>-1.0858683861084794E-4</v>
+        <v>-2.8819023666126721E-4</v>
       </c>
       <c r="X6">
-        <v>-1.0439006385994816E-3</v>
+        <v>-1.5355886403261903E-4</v>
       </c>
       <c r="Y6">
-        <v>-1.4875567846115985E-4</v>
+        <v>-2.8207570451666294E-5</v>
       </c>
       <c r="Z6">
-        <v>1.3723838307930764E-4</v>
+        <v>-1.2758712518292572E-5</v>
       </c>
       <c r="AA6">
-        <v>-1.0769515836030884E-3</v>
+        <v>-5.7809176532118011E-4</v>
       </c>
       <c r="AB6">
-        <v>-6.0990855980879192E-4</v>
+        <v>-3.1506925007231839E-4</v>
       </c>
       <c r="AC6">
-        <v>2.3188929441263586E-5</v>
+        <v>-5.7084749322126237E-6</v>
       </c>
       <c r="AD6">
-        <v>-4.0786374833639855E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+        <v>5.5021923632297639E-4</v>
+      </c>
+      <c r="AE6">
+        <v>5.3537751378341866E-4</v>
+      </c>
+      <c r="AF6">
+        <v>-2.4405821502499329E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B7">
-        <v>7.8522030053460271E-2</v>
+      <c r="B7" s="6">
+        <v>6.9229661008424523E-2</v>
       </c>
       <c r="C7">
-        <v>7.1236228852620929E-5</v>
+        <v>-8.0640460991758642E-6</v>
       </c>
       <c r="D7">
-        <v>-2.3372817133875018E-7</v>
+        <v>2.5865230771609484E-7</v>
       </c>
       <c r="E7">
-        <v>-2.2900561471444385E-3</v>
+        <v>-1.2837996055304628E-3</v>
       </c>
       <c r="F7">
-        <v>-4.0685324187376588E-3</v>
+        <v>-2.6794331690125832E-3</v>
       </c>
       <c r="G7">
-        <v>5.1541137303345282E-3</v>
+        <v>3.4529499462131862E-3</v>
       </c>
       <c r="H7">
-        <v>8.13604814837692E-3</v>
+        <v>5.9123078924909729E-3</v>
       </c>
       <c r="I7">
-        <v>-1.0712748500059003E-4</v>
+        <v>-1.7599280843137526E-4</v>
       </c>
       <c r="J7">
-        <v>8.395253995089778E-5</v>
+        <v>5.6639663079907318E-5</v>
       </c>
       <c r="K7">
-        <v>5.7973544668925346E-4</v>
+        <v>2.0087980678151776E-4</v>
       </c>
       <c r="L7">
-        <v>-1.934012441294665E-3</v>
+        <v>-1.1273318260776638E-3</v>
       </c>
       <c r="M7">
-        <v>1.96475965734711E-4</v>
+        <v>2.4756819551773372E-4</v>
       </c>
       <c r="N7">
-        <v>4.4668874035797614E-4</v>
+        <v>2.3363614136772819E-4</v>
       </c>
       <c r="O7">
-        <v>7.4079670709475704E-4</v>
+        <v>6.3958219582185177E-4</v>
       </c>
       <c r="P7">
-        <v>3.616672002281707E-3</v>
+        <v>2.2507899128863212E-3</v>
       </c>
       <c r="Q7">
-        <v>1.0237202153785731E-4</v>
+        <v>1.546250320428733E-5</v>
       </c>
       <c r="R7">
-        <v>-3.5561649527341855E-3</v>
+        <v>-3.0705567566303394E-3</v>
       </c>
       <c r="S7">
-        <v>-3.7501700799017659E-5</v>
+        <v>-1.43754681925611E-5</v>
       </c>
       <c r="T7">
-        <v>-2.3792843754094715E-5</v>
+        <v>-1.2490182937991318E-4</v>
       </c>
       <c r="U7">
-        <v>1.0892774099144262E-3</v>
+        <v>8.533767903554691E-4</v>
       </c>
       <c r="V7">
-        <v>-6.6522848859453931E-4</v>
+        <v>1.6835683715023817E-4</v>
       </c>
       <c r="W7">
-        <v>-5.3761010221849148E-4</v>
+        <v>-5.7269361997556805E-4</v>
       </c>
       <c r="X7">
-        <v>-1.3675002865126391E-3</v>
+        <v>-5.0009962350374164E-4</v>
       </c>
       <c r="Y7">
-        <v>-1.8010983994015849E-4</v>
+        <v>-6.5483718816112762E-5</v>
       </c>
       <c r="Z7">
-        <v>1.1214935404203205E-4</v>
+        <v>-3.1114043569524122E-5</v>
       </c>
       <c r="AA7">
-        <v>-9.4539293536489077E-4</v>
+        <v>-4.4218928293325772E-4</v>
       </c>
       <c r="AB7">
-        <v>-7.9691337579308697E-4</v>
+        <v>-4.183960583878407E-4</v>
       </c>
       <c r="AC7">
-        <v>3.9043474136391768E-5</v>
+        <v>-5.0965279339928342E-6</v>
       </c>
       <c r="AD7">
-        <v>-5.3455214883186882E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+        <v>5.5724840539350662E-4</v>
+      </c>
+      <c r="AE7">
+        <v>7.0228396192561419E-4</v>
+      </c>
+      <c r="AF7">
+        <v>-2.0514615009544069E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B8">
-        <v>0.27803932773116524</v>
+      <c r="B8" s="6">
+        <v>0.27815738203368812</v>
       </c>
       <c r="C8">
-        <v>-1.2763271192856067E-4</v>
+        <v>-7.8991900242596658E-5</v>
       </c>
       <c r="D8">
-        <v>1.0830154478133442E-6</v>
+        <v>6.6646891063212033E-7</v>
       </c>
       <c r="E8">
-        <v>-3.8209112523353983E-5</v>
+        <v>4.965174821357421E-5</v>
       </c>
       <c r="F8">
-        <v>2.1892672545961305E-4</v>
+        <v>5.3856517666136039E-5</v>
       </c>
       <c r="G8">
-        <v>-8.9273473839357193E-5</v>
+        <v>-3.1838798934320138E-5</v>
       </c>
       <c r="H8">
-        <v>-1.0712748500059003E-4</v>
+        <v>-1.7599280843137526E-4</v>
       </c>
       <c r="I8">
-        <v>1.279794012543857E-2</v>
+        <v>1.0548076062179603E-2</v>
       </c>
       <c r="J8">
-        <v>1.1157642697277415E-2</v>
+        <v>9.0714040355966037E-3</v>
       </c>
       <c r="K8">
-        <v>1.1462842385134094E-2</v>
+        <v>9.232374614428664E-3</v>
       </c>
       <c r="L8">
-        <v>1.2114216660678332E-2</v>
+        <v>9.4536461809592159E-3</v>
       </c>
       <c r="M8">
-        <v>-1.4429776662527947E-3</v>
+        <v>-1.1454760811939137E-3</v>
       </c>
       <c r="N8">
-        <v>-1.2884959123359865E-3</v>
+        <v>-1.1296320593076252E-3</v>
       </c>
       <c r="O8">
-        <v>-1.3860812795690716E-3</v>
+        <v>-1.0626813218285861E-3</v>
       </c>
       <c r="P8">
-        <v>-3.3301112766709827E-3</v>
+        <v>-1.7680069492837329E-3</v>
       </c>
       <c r="Q8">
-        <v>-1.2135745751176339E-4</v>
+        <v>-6.5741570490558188E-5</v>
       </c>
       <c r="R8">
-        <v>2.5524715999415346E-4</v>
+        <v>-9.9463411751266051E-5</v>
       </c>
       <c r="S8">
-        <v>4.4492206455387739E-6</v>
+        <v>2.2280322823532836E-6</v>
       </c>
       <c r="T8">
-        <v>1.3793042358575325E-4</v>
+        <v>5.3078072396304469E-5</v>
       </c>
       <c r="U8">
-        <v>2.6133210278364127E-4</v>
+        <v>4.323558713973733E-4</v>
       </c>
       <c r="V8">
-        <v>-8.094556619024874E-4</v>
+        <v>-4.6847858209746965E-4</v>
       </c>
       <c r="W8">
-        <v>-4.991821197399503E-4</v>
+        <v>-4.4648999861516821E-4</v>
       </c>
       <c r="X8">
-        <v>3.8320532433007599E-4</v>
+        <v>2.6949544311344765E-4</v>
       </c>
       <c r="Y8">
-        <v>2.4325755546735082E-5</v>
+        <v>2.6329715831874094E-6</v>
       </c>
       <c r="Z8">
-        <v>1.3552570931533439E-4</v>
+        <v>8.3198032451868055E-5</v>
       </c>
       <c r="AA8">
-        <v>-7.469729753714514E-4</v>
+        <v>-3.1306227598372049E-4</v>
       </c>
       <c r="AB8">
-        <v>-5.3281578227960293E-4</v>
+        <v>-2.3608828496797258E-4</v>
       </c>
       <c r="AC8">
-        <v>-4.7150721942894281E-5</v>
+        <v>-1.418959104827961E-5</v>
       </c>
       <c r="AD8">
-        <v>-5.1217426009654635E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+        <v>-4.1852157777738088E-4</v>
+      </c>
+      <c r="AE8">
+        <v>3.57202351989105E-4</v>
+      </c>
+      <c r="AF8">
+        <v>-5.3412942072990476E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B9">
-        <v>0.21034585942105305</v>
+      <c r="B9" s="6">
+        <v>0.27789944927101079</v>
       </c>
       <c r="C9">
-        <v>-1.2646396263698277E-4</v>
+        <v>-7.5761662336525017E-5</v>
       </c>
       <c r="D9">
-        <v>1.0932758889978531E-6</v>
+        <v>6.4596684131072603E-7</v>
       </c>
       <c r="E9">
-        <v>3.1822582780942658E-4</v>
+        <v>2.1676731857559468E-4</v>
       </c>
       <c r="F9">
-        <v>5.7905748733444928E-4</v>
+        <v>2.9414613530151425E-4</v>
       </c>
       <c r="G9">
-        <v>-8.2433778155078922E-5</v>
+        <v>2.8356964922704436E-5</v>
       </c>
       <c r="H9">
-        <v>8.395253995089778E-5</v>
+        <v>5.6639663079907318E-5</v>
       </c>
       <c r="I9">
-        <v>1.1157642697277415E-2</v>
+        <v>9.0714040355966037E-3</v>
       </c>
       <c r="J9">
-        <v>1.2650164526939362E-2</v>
+        <v>1.0184069130564369E-2</v>
       </c>
       <c r="K9">
-        <v>1.1986462323489353E-2</v>
+        <v>9.6236255853516944E-3</v>
       </c>
       <c r="L9">
-        <v>1.2603311755119936E-2</v>
+        <v>9.6971788329619953E-3</v>
       </c>
       <c r="M9">
-        <v>-1.3584642737156682E-3</v>
+        <v>-1.1073861066474354E-3</v>
       </c>
       <c r="N9">
-        <v>-2.0160544263305873E-3</v>
+        <v>-1.6468307806116337E-3</v>
       </c>
       <c r="O9">
-        <v>-1.620669058316691E-3</v>
+        <v>-1.2898604611971804E-3</v>
       </c>
       <c r="P9">
-        <v>-3.491874514520103E-3</v>
+        <v>-1.6589511182616219E-3</v>
       </c>
       <c r="Q9">
-        <v>-5.6797702578364551E-5</v>
+        <v>1.8923105959279065E-5</v>
       </c>
       <c r="R9">
-        <v>-4.8668158863379718E-4</v>
+        <v>-4.0347367685430666E-4</v>
       </c>
       <c r="S9">
-        <v>-5.2760308631880936E-6</v>
+        <v>9.4039742963594156E-7</v>
       </c>
       <c r="T9">
-        <v>1.1146408407477311E-4</v>
+        <v>-5.5979685694443771E-5</v>
       </c>
       <c r="U9">
-        <v>2.0981571654852941E-4</v>
+        <v>6.1666802460003806E-4</v>
       </c>
       <c r="V9">
-        <v>-6.8473171829057638E-4</v>
+        <v>-6.0470790873334607E-4</v>
       </c>
       <c r="W9">
-        <v>-3.3135889764255016E-4</v>
+        <v>-4.5395227357255511E-4</v>
       </c>
       <c r="X9">
-        <v>3.544836695168448E-4</v>
+        <v>1.4639374313599532E-5</v>
       </c>
       <c r="Y9">
-        <v>-2.6493523982369049E-6</v>
+        <v>-3.6961832179721848E-5</v>
       </c>
       <c r="Z9">
-        <v>9.1198628244385351E-5</v>
+        <v>7.3635548324031371E-5</v>
       </c>
       <c r="AA9">
-        <v>-7.2729662155864797E-4</v>
+        <v>-3.2146510373196133E-4</v>
       </c>
       <c r="AB9">
-        <v>-3.247180481061613E-4</v>
+        <v>-9.267894295989388E-5</v>
       </c>
       <c r="AC9">
-        <v>-7.6334342647537247E-5</v>
+        <v>-1.6364963557512013E-5</v>
       </c>
       <c r="AD9">
-        <v>-5.437005993848356E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+        <v>-6.85214328265237E-4</v>
+      </c>
+      <c r="AE9">
+        <v>5.3365507672991589E-4</v>
+      </c>
+      <c r="AF9">
+        <v>-5.6799468728162671E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B10">
-        <v>0.35108090974607226</v>
+      <c r="B10" s="6">
+        <v>0.35544571092526928</v>
       </c>
       <c r="C10">
-        <v>-1.6452442733559582E-5</v>
+        <v>-2.3666840433689927E-5</v>
       </c>
       <c r="D10">
-        <v>3.2562211283780671E-7</v>
+        <v>3.5058844031807069E-7</v>
       </c>
       <c r="E10">
-        <v>-1.3131152021966929E-4</v>
+        <v>1.0363109802346379E-4</v>
       </c>
       <c r="F10">
-        <v>2.0063486414140193E-4</v>
+        <v>1.8520712326473832E-4</v>
       </c>
       <c r="G10">
-        <v>2.5530630731200512E-4</v>
+        <v>2.822477197953575E-5</v>
       </c>
       <c r="H10">
-        <v>5.7973544668925346E-4</v>
+        <v>2.0087980678151776E-4</v>
       </c>
       <c r="I10">
-        <v>1.1462842385134094E-2</v>
+        <v>9.232374614428664E-3</v>
       </c>
       <c r="J10">
-        <v>1.1986462323489353E-2</v>
+        <v>9.6236255853516944E-3</v>
       </c>
       <c r="K10">
-        <v>1.4750473200483127E-2</v>
+        <v>1.1641974544061276E-2</v>
       </c>
       <c r="L10">
-        <v>1.4616807150538294E-2</v>
+        <v>1.1508985281024758E-2</v>
       </c>
       <c r="M10">
-        <v>-1.2728916283670248E-3</v>
+        <v>-1.050539615175018E-3</v>
       </c>
       <c r="N10">
-        <v>-1.9169953175989215E-3</v>
+        <v>-1.7010724161966623E-3</v>
       </c>
       <c r="O10">
-        <v>-2.9819758550688551E-3</v>
+        <v>-2.2722987267008343E-3</v>
       </c>
       <c r="P10">
-        <v>-4.2366284009272889E-3</v>
+        <v>-2.9117324633967795E-3</v>
       </c>
       <c r="Q10">
-        <v>-1.4705941776558488E-5</v>
+        <v>1.7603183433755965E-6</v>
       </c>
       <c r="R10">
-        <v>1.5202629670967652E-3</v>
+        <v>9.7748744663664344E-4</v>
       </c>
       <c r="S10">
-        <v>1.8875148919345627E-5</v>
+        <v>3.1932107941970336E-6</v>
       </c>
       <c r="T10">
-        <v>-2.819637225212634E-5</v>
+        <v>-1.0615726827461667E-4</v>
       </c>
       <c r="U10">
-        <v>5.5063922203171811E-4</v>
+        <v>7.3840159010819394E-4</v>
       </c>
       <c r="V10">
-        <v>-1.182032868694843E-3</v>
+        <v>-4.1726804656912436E-4</v>
       </c>
       <c r="W10">
-        <v>-5.6763927368720733E-4</v>
+        <v>-4.3558793867004217E-4</v>
       </c>
       <c r="X10">
-        <v>1.6238979545381976E-4</v>
+        <v>3.4435298999307626E-4</v>
       </c>
       <c r="Y10">
-        <v>-7.9114542007616728E-5</v>
+        <v>-3.2564893657812148E-5</v>
       </c>
       <c r="Z10">
-        <v>1.5189485411922421E-4</v>
+        <v>2.4036495030395187E-5</v>
       </c>
       <c r="AA10">
-        <v>-1.2508592232811965E-3</v>
+        <v>-3.4190334182490449E-4</v>
       </c>
       <c r="AB10">
-        <v>-6.4055121589923908E-4</v>
+        <v>-1.4044457356431755E-5</v>
       </c>
       <c r="AC10">
-        <v>-2.5523155140404815E-5</v>
+        <v>-2.7788521319121063E-5</v>
       </c>
       <c r="AD10">
-        <v>-9.5902606281384403E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+        <v>-4.3587908494871133E-4</v>
+      </c>
+      <c r="AE10">
+        <v>-2.9229407498307424E-4</v>
+      </c>
+      <c r="AF10">
+        <v>-7.8936396648088894E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B11">
-        <v>0.38463049539091376</v>
+      <c r="B11" s="6">
+        <v>0.36408742120760157</v>
       </c>
       <c r="C11">
-        <v>-2.0599599342434674E-4</v>
+        <v>-1.5718446725152555E-4</v>
       </c>
       <c r="D11">
-        <v>1.5227370097081709E-6</v>
+        <v>1.2598011457956303E-6</v>
       </c>
       <c r="E11">
-        <v>3.0711241445923756E-4</v>
+        <v>-5.8645518278625493E-5</v>
       </c>
       <c r="F11">
-        <v>1.5552128695216227E-3</v>
+        <v>6.5748717005584571E-4</v>
       </c>
       <c r="G11">
-        <v>-1.8208573318252044E-3</v>
+        <v>-1.1459393698880515E-3</v>
       </c>
       <c r="H11">
-        <v>-1.934012441294665E-3</v>
+        <v>-1.1273318260776638E-3</v>
       </c>
       <c r="I11">
-        <v>1.2114216660678332E-2</v>
+        <v>9.4536461809592159E-3</v>
       </c>
       <c r="J11">
-        <v>1.2603311755119936E-2</v>
+        <v>9.6971788329619953E-3</v>
       </c>
       <c r="K11">
-        <v>1.4616807150538294E-2</v>
+        <v>1.1508985281024758E-2</v>
       </c>
       <c r="L11">
-        <v>2.7205157917825719E-2</v>
+        <v>2.1143686197734383E-2</v>
       </c>
       <c r="M11">
-        <v>-1.2086527536425791E-3</v>
+        <v>-9.6027157550109693E-4</v>
       </c>
       <c r="N11">
-        <v>-1.2523529704282941E-3</v>
+        <v>-1.1988712044486193E-3</v>
       </c>
       <c r="O11">
-        <v>-3.9124508032317108E-3</v>
+        <v>-2.8580643254921597E-3</v>
       </c>
       <c r="P11">
-        <v>-1.3187936086476551E-2</v>
+        <v>-9.6142963448122287E-3</v>
       </c>
       <c r="Q11">
-        <v>5.1014576281869931E-5</v>
+        <v>-1.3479460574288016E-5</v>
       </c>
       <c r="R11">
-        <v>-1.281981873802622E-3</v>
+        <v>-6.9032721634557093E-4</v>
       </c>
       <c r="S11">
-        <v>7.2887038688144426E-5</v>
+        <v>1.7677015463310767E-6</v>
       </c>
       <c r="T11">
-        <v>8.7860246821416972E-5</v>
+        <v>-1.7459956676692408E-4</v>
       </c>
       <c r="U11">
-        <v>-4.7500124702087865E-4</v>
+        <v>-2.6216296185612342E-4</v>
       </c>
       <c r="V11">
-        <v>-2.4389010431272295E-3</v>
+        <v>-1.529367706243645E-3</v>
       </c>
       <c r="W11">
-        <v>-4.0253704256630845E-4</v>
+        <v>-2.3887179596480956E-4</v>
       </c>
       <c r="X11">
-        <v>2.6113494516881441E-4</v>
+        <v>1.6980301738517669E-4</v>
       </c>
       <c r="Y11">
-        <v>-5.4368161401392833E-5</v>
+        <v>-6.0991293261990578E-5</v>
       </c>
       <c r="Z11">
-        <v>2.1382809066022791E-4</v>
+        <v>1.1169315681604857E-4</v>
       </c>
       <c r="AA11">
-        <v>-2.6918079367940079E-5</v>
+        <v>4.4975273226549074E-4</v>
       </c>
       <c r="AB11">
-        <v>-1.8324760725494521E-4</v>
+        <v>3.9100560866519446E-4</v>
       </c>
       <c r="AC11">
-        <v>3.341727545061934E-5</v>
+        <v>1.4327190755126227E-5</v>
       </c>
       <c r="AD11">
-        <v>-3.5077769015876229E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+        <v>-1.1987249616369157E-3</v>
+      </c>
+      <c r="AE11">
+        <v>-1.9155408470141902E-3</v>
+      </c>
+      <c r="AF11">
+        <v>-3.1782711808574721E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B12">
-        <v>-0.54920285754173592</v>
+      <c r="B12" s="6">
+        <v>-0.55023681061446184</v>
       </c>
       <c r="C12">
-        <v>5.2812551407837097E-9</v>
+        <v>7.6546862329193168E-6</v>
       </c>
       <c r="D12">
-        <v>-2.8503973303184574E-8</v>
+        <v>-7.9016667526494513E-8</v>
       </c>
       <c r="E12">
-        <v>1.4980789934574508E-7</v>
+        <v>-3.4928813899106573E-5</v>
       </c>
       <c r="F12">
-        <v>1.0922982729672886E-4</v>
+        <v>3.9750432967029759E-5</v>
       </c>
       <c r="G12">
-        <v>1.1904294488733282E-4</v>
+        <v>2.1382769627584453E-4</v>
       </c>
       <c r="H12">
-        <v>1.96475965734711E-4</v>
+        <v>2.4756819551773372E-4</v>
       </c>
       <c r="I12">
-        <v>-1.4429776662527947E-3</v>
+        <v>-1.1454760811939137E-3</v>
       </c>
       <c r="J12">
-        <v>-1.3584642737156682E-3</v>
+        <v>-1.1073861066474354E-3</v>
       </c>
       <c r="K12">
-        <v>-1.2728916283670248E-3</v>
+        <v>-1.050539615175018E-3</v>
       </c>
       <c r="L12">
-        <v>-1.2086527536425791E-3</v>
+        <v>-9.6027157550109693E-4</v>
       </c>
       <c r="M12">
-        <v>4.6754278250928484E-3</v>
+        <v>3.8007449592142905E-3</v>
       </c>
       <c r="N12">
-        <v>3.0250853069525721E-3</v>
+        <v>2.4929639413666955E-3</v>
       </c>
       <c r="O12">
-        <v>3.0434534818361459E-3</v>
+        <v>2.4896238532938781E-3</v>
       </c>
       <c r="P12">
-        <v>3.1795359583893516E-3</v>
+        <v>2.5421146863831841E-3</v>
       </c>
       <c r="Q12">
-        <v>4.2222770999130388E-5</v>
+        <v>5.1995924360962183E-5</v>
       </c>
       <c r="R12">
-        <v>-4.6469005934981784E-4</v>
+        <v>-4.432644172259765E-4</v>
       </c>
       <c r="S12">
-        <v>-1.3502788036829725E-5</v>
+        <v>-1.3817185956437962E-5</v>
       </c>
       <c r="T12">
-        <v>-1.8573457404695961E-5</v>
+        <v>3.1215901792259999E-5</v>
       </c>
       <c r="U12">
-        <v>1.2906266010764337E-4</v>
+        <v>6.8773970583667514E-5</v>
       </c>
       <c r="V12">
-        <v>-2.0533978396159174E-4</v>
+        <v>-5.2484022208679497E-5</v>
       </c>
       <c r="W12">
-        <v>-1.1609686175027012E-4</v>
+        <v>-3.869312658970846E-5</v>
       </c>
       <c r="X12">
-        <v>9.3115341180752004E-6</v>
+        <v>4.2132878727692182E-5</v>
       </c>
       <c r="Y12">
-        <v>-2.5415063411910044E-5</v>
+        <v>-1.1375745144313093E-5</v>
       </c>
       <c r="Z12">
-        <v>2.2363984031337076E-5</v>
+        <v>1.6912900297234756E-5</v>
       </c>
       <c r="AA12">
-        <v>2.7105693227414632E-6</v>
+        <v>1.5714636846807391E-5</v>
       </c>
       <c r="AB12">
-        <v>-1.4631156797921909E-4</v>
+        <v>-6.2195909892679997E-5</v>
       </c>
       <c r="AC12">
-        <v>2.1489696286698217E-5</v>
+        <v>1.0003560389292667E-5</v>
       </c>
       <c r="AD12">
-        <v>-1.9969395063206882E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+        <v>2.7107958978974853E-4</v>
+      </c>
+      <c r="AE12">
+        <v>1.0685435631157039E-4</v>
+      </c>
+      <c r="AF12">
+        <v>-2.0176602850587051E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B13">
-        <v>-0.92289391995916958</v>
+      <c r="B13" s="6">
+        <v>-0.94350431022709669</v>
       </c>
       <c r="C13">
-        <v>-5.1135979701289208E-5</v>
+        <v>-3.5770529891458638E-5</v>
       </c>
       <c r="D13">
-        <v>2.8581917186769172E-7</v>
+        <v>2.0296195944636791E-7</v>
       </c>
       <c r="E13">
-        <v>-2.4022397956307358E-4</v>
+        <v>2.796850304904727E-5</v>
       </c>
       <c r="F13">
-        <v>-3.4276378687588911E-5</v>
+        <v>1.5731405884457142E-4</v>
       </c>
       <c r="G13">
-        <v>2.1997374641936161E-4</v>
+        <v>8.7154667083394355E-5</v>
       </c>
       <c r="H13">
-        <v>4.4668874035797614E-4</v>
+        <v>2.3363614136772819E-4</v>
       </c>
       <c r="I13">
-        <v>-1.2884959123359865E-3</v>
+        <v>-1.1296320593076252E-3</v>
       </c>
       <c r="J13">
-        <v>-2.0160544263305873E-3</v>
+        <v>-1.6468307806116337E-3</v>
       </c>
       <c r="K13">
-        <v>-1.9169953175989215E-3</v>
+        <v>-1.7010724161966623E-3</v>
       </c>
       <c r="L13">
-        <v>-1.2523529704282941E-3</v>
+        <v>-1.1988712044486193E-3</v>
       </c>
       <c r="M13">
-        <v>3.0250853069525721E-3</v>
+        <v>2.4929639413666955E-3</v>
       </c>
       <c r="N13">
-        <v>4.712481271148177E-3</v>
+        <v>3.7033929361480699E-3</v>
       </c>
       <c r="O13">
-        <v>3.3617231287917104E-3</v>
+        <v>2.8215965389084977E-3</v>
       </c>
       <c r="P13">
-        <v>3.2107351416947698E-3</v>
+        <v>2.6848526592639786E-3</v>
       </c>
       <c r="Q13">
-        <v>1.1886614533826833E-4</v>
+        <v>3.0542088648941412E-5</v>
       </c>
       <c r="R13">
-        <v>-1.6676453677677066E-3</v>
+        <v>-1.2733458983894149E-3</v>
       </c>
       <c r="S13">
-        <v>-1.1179756736209949E-5</v>
+        <v>-4.7920877446868055E-7</v>
       </c>
       <c r="T13">
-        <v>-1.3020144295928322E-5</v>
+        <v>3.6117504934412024E-5</v>
       </c>
       <c r="U13">
-        <v>1.3157874013419103E-4</v>
+        <v>-1.1313983534740522E-4</v>
       </c>
       <c r="V13">
-        <v>-2.9520125029034697E-4</v>
+        <v>3.2570622550372863E-4</v>
       </c>
       <c r="W13">
-        <v>-6.5274850547636864E-5</v>
+        <v>-2.0490873908365773E-5</v>
       </c>
       <c r="X13">
-        <v>-7.3553511535314831E-5</v>
+        <v>3.1184041461505244E-4</v>
       </c>
       <c r="Y13">
-        <v>-9.0642850717894395E-5</v>
+        <v>-1.8429574757362752E-5</v>
       </c>
       <c r="Z13">
-        <v>1.4768048594308343E-4</v>
+        <v>3.6984886528809378E-5</v>
       </c>
       <c r="AA13">
-        <v>2.4281082814712931E-4</v>
+        <v>1.9297473281414828E-4</v>
       </c>
       <c r="AB13">
-        <v>-9.2467141321276453E-5</v>
+        <v>-5.651113387966796E-5</v>
       </c>
       <c r="AC13">
-        <v>3.7597769021241272E-5</v>
+        <v>9.0821070093710489E-6</v>
       </c>
       <c r="AD13">
-        <v>-1.0923856990754553E-4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+        <v>1.670013450360284E-4</v>
+      </c>
+      <c r="AE13">
+        <v>-1.7977426763165735E-4</v>
+      </c>
+      <c r="AF13">
+        <v>-3.6286374658167495E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A14" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B14">
-        <v>-0.95047622206269544</v>
+      <c r="B14" s="6">
+        <v>-1.0114001832531281</v>
       </c>
       <c r="C14">
-        <v>7.0912160548793784E-5</v>
+        <v>5.4050735389449855E-5</v>
       </c>
       <c r="D14">
-        <v>-4.2475812022058375E-7</v>
+        <v>-3.5578084280068162E-7</v>
       </c>
       <c r="E14">
-        <v>3.6775934799998143E-4</v>
+        <v>1.287523391565828E-4</v>
       </c>
       <c r="F14">
-        <v>5.1285471709014321E-4</v>
+        <v>2.7138208120149873E-4</v>
       </c>
       <c r="G14">
-        <v>5.063928424374059E-4</v>
+        <v>4.7608805057542471E-4</v>
       </c>
       <c r="H14">
-        <v>7.4079670709475704E-4</v>
+        <v>6.3958219582185177E-4</v>
       </c>
       <c r="I14">
-        <v>-1.3860812795690716E-3</v>
+        <v>-1.0626813218285861E-3</v>
       </c>
       <c r="J14">
-        <v>-1.620669058316691E-3</v>
+        <v>-1.2898604611971804E-3</v>
       </c>
       <c r="K14">
-        <v>-2.9819758550688551E-3</v>
+        <v>-2.2722987267008343E-3</v>
       </c>
       <c r="L14">
-        <v>-3.9124508032317108E-3</v>
+        <v>-2.8580643254921597E-3</v>
       </c>
       <c r="M14">
-        <v>3.0434534818361459E-3</v>
+        <v>2.4896238532938781E-3</v>
       </c>
       <c r="N14">
-        <v>3.3617231287917104E-3</v>
+        <v>2.8215965389084977E-3</v>
       </c>
       <c r="O14">
-        <v>6.4607847807135101E-3</v>
+        <v>4.9937246233304443E-3</v>
       </c>
       <c r="P14">
-        <v>6.2033214395992645E-3</v>
+        <v>4.7887883450104954E-3</v>
       </c>
       <c r="Q14">
-        <v>-1.8213348287519367E-4</v>
+        <v>-5.5008427332173458E-5</v>
       </c>
       <c r="R14">
-        <v>6.4974825018856812E-4</v>
+        <v>5.2764003944639169E-4</v>
       </c>
       <c r="S14">
-        <v>-5.2170359456315337E-5</v>
+        <v>-3.4511756434333122E-5</v>
       </c>
       <c r="T14">
-        <v>3.641161962318623E-5</v>
+        <v>8.9846756414651435E-5</v>
       </c>
       <c r="U14">
-        <v>1.0975559838629983E-4</v>
+        <v>-1.9397734316304785E-4</v>
       </c>
       <c r="V14">
-        <v>1.333663307419815E-3</v>
+        <v>6.5817675016175249E-4</v>
       </c>
       <c r="W14">
-        <v>4.0286685592567836E-4</v>
+        <v>3.8607938541636029E-4</v>
       </c>
       <c r="X14">
-        <v>1.0125684411239552E-3</v>
+        <v>5.6126184562425591E-4</v>
       </c>
       <c r="Y14">
-        <v>3.9695959474735176E-5</v>
+        <v>5.4850684495358403E-6</v>
       </c>
       <c r="Z14">
-        <v>-7.9495714688689316E-6</v>
+        <v>6.3653670861337384E-5</v>
       </c>
       <c r="AA14">
-        <v>-1.7757010644623111E-4</v>
+        <v>-2.7032923240946378E-4</v>
       </c>
       <c r="AB14">
-        <v>-3.4037087998989388E-4</v>
+        <v>-3.9164398272523767E-4</v>
       </c>
       <c r="AC14">
-        <v>-4.2271292836679414E-5</v>
+        <v>-3.2658021992503167E-5</v>
       </c>
       <c r="AD14">
-        <v>-5.0740718635921356E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+        <v>2.4564227627467113E-4</v>
+      </c>
+      <c r="AE14">
+        <v>4.1817895296336984E-4</v>
+      </c>
+      <c r="AF14">
+        <v>-3.5969623343463175E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A15" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B15">
-        <v>-0.85057073665016081</v>
+      <c r="B15" s="6">
+        <v>-0.86284668446332591</v>
       </c>
       <c r="C15">
-        <v>2.4153807288942823E-4</v>
+        <v>2.0696059228727276E-4</v>
       </c>
       <c r="D15">
-        <v>-1.4600920086123375E-6</v>
+        <v>-1.4698605737466175E-6</v>
       </c>
       <c r="E15">
-        <v>-1.9641372325281868E-4</v>
+        <v>3.6816114915567738E-4</v>
       </c>
       <c r="F15">
-        <v>-4.1988956632363822E-4</v>
+        <v>2.9876599947354873E-4</v>
       </c>
       <c r="G15">
-        <v>3.0833167772524998E-3</v>
+        <v>1.8313509466162592E-3</v>
       </c>
       <c r="H15">
-        <v>3.616672002281707E-3</v>
+        <v>2.2507899128863212E-3</v>
       </c>
       <c r="I15">
-        <v>-3.3301112766709827E-3</v>
+        <v>-1.7680069492837329E-3</v>
       </c>
       <c r="J15">
-        <v>-3.491874514520103E-3</v>
+        <v>-1.6589511182616219E-3</v>
       </c>
       <c r="K15">
-        <v>-4.2366284009272889E-3</v>
+        <v>-2.9117324633967795E-3</v>
       </c>
       <c r="L15">
-        <v>-1.3187936086476551E-2</v>
+        <v>-9.6142963448122287E-3</v>
       </c>
       <c r="M15">
-        <v>3.1795359583893516E-3</v>
+        <v>2.5421146863831841E-3</v>
       </c>
       <c r="N15">
-        <v>3.2107351416947698E-3</v>
+        <v>2.6848526592639786E-3</v>
       </c>
       <c r="O15">
-        <v>6.2033214395992645E-3</v>
+        <v>4.7887883450104954E-3</v>
       </c>
       <c r="P15">
-        <v>1.8921791381277808E-2</v>
+        <v>1.4878413631835667E-2</v>
       </c>
       <c r="Q15">
-        <v>-6.0322881108770333E-4</v>
+        <v>-1.1103942706722446E-4</v>
       </c>
       <c r="R15">
-        <v>-2.6796469571494647E-3</v>
+        <v>-1.2530183287589418E-3</v>
       </c>
       <c r="S15">
-        <v>-8.299549302586719E-5</v>
+        <v>-1.3079669128930203E-5</v>
       </c>
       <c r="T15">
-        <v>3.3032184719388445E-5</v>
+        <v>-8.479584198900264E-5</v>
       </c>
       <c r="U15">
-        <v>6.801521335714929E-4</v>
+        <v>9.9328546479505423E-4</v>
       </c>
       <c r="V15">
-        <v>3.276139209885268E-3</v>
+        <v>1.6985492030455874E-3</v>
       </c>
       <c r="W15">
-        <v>-2.140690925875309E-4</v>
+        <v>-2.9247063465830526E-4</v>
       </c>
       <c r="X15">
-        <v>8.4976324766813504E-4</v>
+        <v>3.891434345454632E-4</v>
       </c>
       <c r="Y15">
-        <v>-1.8777143649765633E-5</v>
+        <v>-1.3333444828734315E-5</v>
       </c>
       <c r="Z15">
-        <v>-1.9661844580047704E-4</v>
+        <v>-2.7471380818892312E-5</v>
       </c>
       <c r="AA15">
-        <v>-8.9213331702589667E-4</v>
+        <v>-1.1145356779564343E-3</v>
       </c>
       <c r="AB15">
-        <v>-5.6393098015509145E-4</v>
+        <v>-8.467904557471163E-4</v>
       </c>
       <c r="AC15">
-        <v>1.1619804629672175E-5</v>
+        <v>-5.5821331285881506E-5</v>
       </c>
       <c r="AD15">
-        <v>-1.1331071096443568E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+        <v>1.9318716798235715E-3</v>
+      </c>
+      <c r="AE15">
+        <v>2.8159004844021136E-3</v>
+      </c>
+      <c r="AF15">
+        <v>-8.5713684056973709E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A16" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B16">
-        <v>-4.9920133883656098E-2</v>
+      <c r="B16" s="6">
+        <v>-4.055455344869547E-2</v>
       </c>
       <c r="C16">
-        <v>-3.3989659233709372E-5</v>
+        <v>-1.3412683638652849E-5</v>
       </c>
       <c r="D16">
-        <v>2.3004539478438686E-7</v>
+        <v>7.4623833711695237E-8</v>
       </c>
       <c r="E16">
-        <v>-2.6029101506552544E-6</v>
+        <v>9.0781108738329305E-5</v>
       </c>
       <c r="F16">
-        <v>-1.2381937600795896E-4</v>
+        <v>2.4209957147453091E-6</v>
       </c>
       <c r="G16">
-        <v>2.3479236250703594E-5</v>
+        <v>-2.6242186339707665E-5</v>
       </c>
       <c r="H16">
-        <v>1.0237202153785731E-4</v>
+        <v>1.546250320428733E-5</v>
       </c>
       <c r="I16">
-        <v>-1.2135745751176339E-4</v>
+        <v>-6.5741570490558188E-5</v>
       </c>
       <c r="J16">
-        <v>-5.6797702578364551E-5</v>
+        <v>1.8923105959279065E-5</v>
       </c>
       <c r="K16">
-        <v>-1.4705941776558488E-5</v>
+        <v>1.7603183433755965E-6</v>
       </c>
       <c r="L16">
-        <v>5.1014576281869931E-5</v>
+        <v>-1.3479460574288016E-5</v>
       </c>
       <c r="M16">
-        <v>4.2222770999130388E-5</v>
+        <v>5.1995924360962183E-5</v>
       </c>
       <c r="N16">
-        <v>1.1886614533826833E-4</v>
+        <v>3.0542088648941412E-5</v>
       </c>
       <c r="O16">
-        <v>-1.8213348287519367E-4</v>
+        <v>-5.5008427332173458E-5</v>
       </c>
       <c r="P16">
-        <v>-6.0322881108770333E-4</v>
+        <v>-1.1103942706722446E-4</v>
       </c>
       <c r="Q16">
-        <v>7.4338582656606879E-4</v>
+        <v>5.1268835743172698E-4</v>
       </c>
       <c r="R16">
-        <v>3.9338215292084033E-4</v>
+        <v>4.4709616823935183E-4</v>
       </c>
       <c r="S16">
-        <v>3.3576979890964782E-6</v>
+        <v>7.8863675060851582E-6</v>
       </c>
       <c r="T16">
-        <v>-4.2916536642118588E-5</v>
+        <v>-1.4214040234102572E-5</v>
       </c>
       <c r="U16">
-        <v>-4.2785022431614127E-5</v>
+        <v>-1.6629368355788749E-4</v>
       </c>
       <c r="V16">
-        <v>-4.0808413860297352E-4</v>
+        <v>-8.736325616601586E-5</v>
       </c>
       <c r="W16">
-        <v>7.4856035080885763E-5</v>
+        <v>3.7064700973434933E-5</v>
       </c>
       <c r="X16">
-        <v>-2.7157104340804112E-4</v>
+        <v>-6.7991644484844934E-5</v>
       </c>
       <c r="Y16">
-        <v>-4.4994713610867822E-5</v>
+        <v>-1.0534659439876739E-5</v>
       </c>
       <c r="Z16">
-        <v>6.5089878391042181E-5</v>
+        <v>1.6336696564624869E-5</v>
       </c>
       <c r="AA16">
-        <v>7.585679942638231E-5</v>
+        <v>3.0852529163507387E-5</v>
       </c>
       <c r="AB16">
-        <v>1.0826100084275502E-4</v>
+        <v>3.2092286027092369E-5</v>
       </c>
       <c r="AC16">
-        <v>-5.161565956071274E-5</v>
+        <v>-7.1061945715503687E-7</v>
       </c>
       <c r="AD16">
-        <v>9.8102780865993631E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+        <v>-1.1363367262163333E-4</v>
+      </c>
+      <c r="AE16">
+        <v>-9.9841858933966658E-5</v>
+      </c>
+      <c r="AF16">
+        <v>-4.0998497993821197E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A17" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B17">
-        <v>0.94781223141784599</v>
+      <c r="B17" s="6">
+        <v>0.85319917471050577</v>
       </c>
       <c r="C17">
-        <v>9.133883271685711E-4</v>
+        <v>9.0046885170894445E-4</v>
       </c>
       <c r="D17">
-        <v>-6.4421137133345422E-6</v>
+        <v>-6.3856697760577704E-6</v>
       </c>
       <c r="E17">
-        <v>-1.5503571593261534E-3</v>
+        <v>-1.4804492174878355E-3</v>
       </c>
       <c r="F17">
-        <v>-4.1246569946116942E-4</v>
+        <v>-6.1515416376975787E-4</v>
       </c>
       <c r="G17">
-        <v>-4.2358129492047602E-3</v>
+        <v>-3.3383245527403441E-3</v>
       </c>
       <c r="H17">
-        <v>-3.5561649527341855E-3</v>
+        <v>-3.0705567566303394E-3</v>
       </c>
       <c r="I17">
-        <v>2.5524715999415346E-4</v>
+        <v>-9.9463411751266051E-5</v>
       </c>
       <c r="J17">
-        <v>-4.8668158863379718E-4</v>
+        <v>-4.0347367685430666E-4</v>
       </c>
       <c r="K17">
-        <v>1.5202629670967652E-3</v>
+        <v>9.7748744663664344E-4</v>
       </c>
       <c r="L17">
-        <v>-1.281981873802622E-3</v>
+        <v>-6.9032721634557093E-4</v>
       </c>
       <c r="M17">
-        <v>-4.6469005934981784E-4</v>
+        <v>-4.432644172259765E-4</v>
       </c>
       <c r="N17">
-        <v>-1.6676453677677066E-3</v>
+        <v>-1.2733458983894149E-3</v>
       </c>
       <c r="O17">
-        <v>6.4974825018856812E-4</v>
+        <v>5.2764003944639169E-4</v>
       </c>
       <c r="P17">
-        <v>-2.6796469571494647E-3</v>
+        <v>-1.2530183287589418E-3</v>
       </c>
       <c r="Q17">
-        <v>3.9338215292084033E-4</v>
+        <v>4.4709616823935183E-4</v>
       </c>
       <c r="R17">
-        <v>7.4524104921122297E-2</v>
+        <v>5.9728483093435272E-2</v>
       </c>
       <c r="S17">
-        <v>-1.9043361089430511E-4</v>
+        <v>-1.4082488825360848E-4</v>
       </c>
       <c r="T17">
-        <v>1.7003572312819263E-4</v>
+        <v>4.5125708871507472E-4</v>
       </c>
       <c r="U17">
-        <v>6.124653496688828E-4</v>
+        <v>7.9094535270194419E-5</v>
       </c>
       <c r="V17">
-        <v>-2.1204830238096824E-3</v>
+        <v>-1.4715610271889585E-3</v>
       </c>
       <c r="W17">
-        <v>-3.4265686340309897E-3</v>
+        <v>-3.0390844234498169E-3</v>
       </c>
       <c r="X17">
-        <v>-4.1369115802127772E-3</v>
+        <v>-3.1956907797417037E-3</v>
       </c>
       <c r="Y17">
-        <v>5.1879118133475071E-5</v>
+        <v>8.3712209323960726E-5</v>
       </c>
       <c r="Z17">
-        <v>-2.4562307668481018E-4</v>
+        <v>-2.2678699726700501E-4</v>
       </c>
       <c r="AA17">
-        <v>-3.8919172005575844E-3</v>
+        <v>-3.0109224821943943E-3</v>
       </c>
       <c r="AB17">
-        <v>-3.4223204516250893E-3</v>
+        <v>-2.6349312695134837E-3</v>
       </c>
       <c r="AC17">
-        <v>-7.3379171140614636E-5</v>
+        <v>-9.7111117685139966E-5</v>
       </c>
       <c r="AD17">
-        <v>-2.0867279269172291E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+        <v>-1.0869192201384682E-3</v>
+      </c>
+      <c r="AE17">
+        <v>-2.2860814667542127E-3</v>
+      </c>
+      <c r="AF17">
+        <v>-2.1584184721224711E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B18">
-        <v>8.5293682816652127E-3</v>
+      <c r="B18" s="6">
+        <v>1.0608612450187899E-2</v>
       </c>
       <c r="C18">
-        <v>-6.9292455370259963E-6</v>
+        <v>-1.7955110280620017E-6</v>
       </c>
       <c r="D18">
-        <v>2.0516899362250907E-8</v>
+        <v>-1.3976727754325782E-8</v>
       </c>
       <c r="E18">
-        <v>2.540831527178121E-5</v>
+        <v>9.4875453435220044E-6</v>
       </c>
       <c r="F18">
-        <v>3.1127148270404169E-5</v>
+        <v>1.6283074279119469E-5</v>
       </c>
       <c r="G18">
-        <v>-5.8691425368852383E-5</v>
+        <v>-1.98293355785714E-5</v>
       </c>
       <c r="H18">
-        <v>-3.7501700799017659E-5</v>
+        <v>-1.43754681925611E-5</v>
       </c>
       <c r="I18">
-        <v>4.4492206455387739E-6</v>
+        <v>2.2280322823532836E-6</v>
       </c>
       <c r="J18">
-        <v>-5.2760308631880936E-6</v>
+        <v>9.4039742963594156E-7</v>
       </c>
       <c r="K18">
-        <v>1.8875148919345627E-5</v>
+        <v>3.1932107941970336E-6</v>
       </c>
       <c r="L18">
-        <v>7.2887038688144426E-5</v>
+        <v>1.7677015463310767E-6</v>
       </c>
       <c r="M18">
-        <v>-1.3502788036829725E-5</v>
+        <v>-1.3817185956437962E-5</v>
       </c>
       <c r="N18">
-        <v>-1.1179756736209949E-5</v>
+        <v>-4.7920877446868055E-7</v>
       </c>
       <c r="O18">
-        <v>-5.2170359456315337E-5</v>
+        <v>-3.4511756434333122E-5</v>
       </c>
       <c r="P18">
-        <v>-8.299549302586719E-5</v>
+        <v>-1.3079669128930203E-5</v>
       </c>
       <c r="Q18">
-        <v>3.3576979890964782E-6</v>
+        <v>7.8863675060851582E-6</v>
       </c>
       <c r="R18">
-        <v>-1.9043361089430511E-4</v>
+        <v>-1.4082488825360848E-4</v>
       </c>
       <c r="S18">
-        <v>2.2930323997885686E-5</v>
+        <v>1.7773089987950235E-5</v>
       </c>
       <c r="T18">
-        <v>-3.9840720498691069E-5</v>
+        <v>-1.9835464091510616E-5</v>
       </c>
       <c r="U18">
-        <v>-7.3191576160696055E-8</v>
+        <v>-7.0469442481631519E-6</v>
       </c>
       <c r="V18">
-        <v>9.3517585576234264E-5</v>
+        <v>6.4009594127779895E-6</v>
       </c>
       <c r="W18">
-        <v>-1.0476425617399281E-5</v>
+        <v>-5.508485428054116E-6</v>
       </c>
       <c r="X18">
-        <v>6.6509203507857467E-5</v>
+        <v>1.7414394241457242E-5</v>
       </c>
       <c r="Y18">
-        <v>1.1262642810457851E-6</v>
+        <v>-1.7897333179004016E-6</v>
       </c>
       <c r="Z18">
-        <v>-5.4033571737770631E-6</v>
+        <v>4.47205641020785E-6</v>
       </c>
       <c r="AA18">
-        <v>3.2711428563324035E-5</v>
+        <v>-9.7422932452443671E-6</v>
       </c>
       <c r="AB18">
-        <v>1.6462988043291273E-5</v>
+        <v>-1.8459081491638084E-5</v>
       </c>
       <c r="AC18">
-        <v>2.5805263150591864E-6</v>
+        <v>1.9447174780393602E-6</v>
       </c>
       <c r="AD18">
-        <v>3.2977410859307742E-4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+        <v>-2.1557183881715188E-6</v>
+      </c>
+      <c r="AE18">
+        <v>4.8547083869859043E-5</v>
+      </c>
+      <c r="AF18">
+        <v>1.8371319804637141E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A19" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B19">
-        <v>3.778173875810082E-2</v>
+      <c r="B19" s="6">
+        <v>1.9925412755593976E-2</v>
       </c>
       <c r="C19">
-        <v>-3.3870549460523602E-5</v>
+        <v>3.8382325664881265E-5</v>
       </c>
       <c r="D19">
-        <v>5.8075930602089375E-7</v>
+        <v>-1.0084427138470514E-7</v>
       </c>
       <c r="E19">
-        <v>1.1370868876292921E-4</v>
+        <v>9.1717100797533558E-5</v>
       </c>
       <c r="F19">
-        <v>7.0095529154420191E-5</v>
+        <v>-9.5832877369391128E-6</v>
       </c>
       <c r="G19">
-        <v>1.5716659929154595E-4</v>
+        <v>1.7075448901746228E-4</v>
       </c>
       <c r="H19">
-        <v>-2.3792843754094715E-5</v>
+        <v>-1.2490182937991318E-4</v>
       </c>
       <c r="I19">
-        <v>1.3793042358575325E-4</v>
+        <v>5.3078072396304469E-5</v>
       </c>
       <c r="J19">
-        <v>1.1146408407477311E-4</v>
+        <v>-5.5979685694443771E-5</v>
       </c>
       <c r="K19">
-        <v>-2.819637225212634E-5</v>
+        <v>-1.0615726827461667E-4</v>
       </c>
       <c r="L19">
-        <v>8.7860246821416972E-5</v>
+        <v>-1.7459956676692408E-4</v>
       </c>
       <c r="M19">
-        <v>-1.8573457404695961E-5</v>
+        <v>3.1215901792259999E-5</v>
       </c>
       <c r="N19">
-        <v>-1.3020144295928322E-5</v>
+        <v>3.6117504934412024E-5</v>
       </c>
       <c r="O19">
-        <v>3.641161962318623E-5</v>
+        <v>8.9846756414651435E-5</v>
       </c>
       <c r="P19">
-        <v>3.3032184719388445E-5</v>
+        <v>-8.479584198900264E-5</v>
       </c>
       <c r="Q19">
-        <v>-4.2916536642118588E-5</v>
+        <v>-1.4214040234102572E-5</v>
       </c>
       <c r="R19">
-        <v>1.7003572312819263E-4</v>
+        <v>4.5125708871507472E-4</v>
       </c>
       <c r="S19">
-        <v>-3.9840720498691069E-5</v>
+        <v>-1.9835464091510616E-5</v>
       </c>
       <c r="T19">
-        <v>6.6939345565544405E-4</v>
+        <v>7.8203528730629458E-4</v>
       </c>
       <c r="U19">
-        <v>-1.6163467519404124E-4</v>
+        <v>-7.0530794052093432E-4</v>
       </c>
       <c r="V19">
-        <v>2.4316971072638346E-4</v>
+        <v>-2.5268192319176917E-6</v>
       </c>
       <c r="W19">
-        <v>-7.3884969462822872E-5</v>
+        <v>-1.3629190507534207E-4</v>
       </c>
       <c r="X19">
-        <v>-2.3239592524659748E-4</v>
+        <v>-9.9560195731323458E-5</v>
       </c>
       <c r="Y19">
-        <v>9.7170873684056538E-6</v>
+        <v>8.1949753938475559E-6</v>
       </c>
       <c r="Z19">
-        <v>-9.0344119608238476E-6</v>
+        <v>2.0112114400324812E-5</v>
       </c>
       <c r="AA19">
-        <v>1.1247939868356258E-4</v>
+        <v>-9.8514247948297594E-5</v>
       </c>
       <c r="AB19">
-        <v>1.0951487704258982E-4</v>
+        <v>-3.2259292936509011E-5</v>
       </c>
       <c r="AC19">
-        <v>-1.690465334121022E-5</v>
+        <v>4.8426370600201393E-6</v>
       </c>
       <c r="AD19">
-        <v>-4.2951510406001592E-4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+        <v>-1.309750727520884E-4</v>
+      </c>
+      <c r="AE19">
+        <v>-2.9378064998808072E-4</v>
+      </c>
+      <c r="AF19">
+        <v>-2.2626621473227451E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B20">
-        <v>-0.10430395070526412</v>
+      <c r="B20" s="6">
+        <v>-0.19757093622815436</v>
       </c>
       <c r="C20">
-        <v>1.9801894684279617E-4</v>
+        <v>3.8090811983070302E-5</v>
       </c>
       <c r="D20">
-        <v>-1.3069421735541475E-6</v>
+        <v>-1.6234633934936216E-7</v>
       </c>
       <c r="E20">
-        <v>-2.1136660209210127E-4</v>
+        <v>-8.3498932950226695E-5</v>
       </c>
       <c r="F20">
-        <v>-1.1467574183447689E-4</v>
+        <v>1.7074104313563178E-4</v>
       </c>
       <c r="G20">
-        <v>5.7737052293500347E-4</v>
+        <v>5.1218098524073155E-4</v>
       </c>
       <c r="H20">
-        <v>1.0892774099144262E-3</v>
+        <v>8.533767903554691E-4</v>
       </c>
       <c r="I20">
-        <v>2.6133210278364127E-4</v>
+        <v>4.323558713973733E-4</v>
       </c>
       <c r="J20">
-        <v>2.0981571654852941E-4</v>
+        <v>6.1666802460003806E-4</v>
       </c>
       <c r="K20">
-        <v>5.5063922203171811E-4</v>
+        <v>7.3840159010819394E-4</v>
       </c>
       <c r="L20">
-        <v>-4.7500124702087865E-4</v>
+        <v>-2.6216296185612342E-4</v>
       </c>
       <c r="M20">
-        <v>1.2906266010764337E-4</v>
+        <v>6.8773970583667514E-5</v>
       </c>
       <c r="N20">
-        <v>1.3157874013419103E-4</v>
+        <v>-1.1313983534740522E-4</v>
       </c>
       <c r="O20">
-        <v>1.0975559838629983E-4</v>
+        <v>-1.9397734316304785E-4</v>
       </c>
       <c r="P20">
-        <v>6.801521335714929E-4</v>
+        <v>9.9328546479505423E-4</v>
       </c>
       <c r="Q20">
-        <v>-4.2785022431614127E-5</v>
+        <v>-1.6629368355788749E-4</v>
       </c>
       <c r="R20">
-        <v>6.124653496688828E-4</v>
+        <v>7.9094535270194419E-5</v>
       </c>
       <c r="S20">
-        <v>-7.3191576160696055E-8</v>
+        <v>-7.0469442481631519E-6</v>
       </c>
       <c r="T20">
-        <v>-1.6163467519404124E-4</v>
+        <v>-7.0530794052093432E-4</v>
       </c>
       <c r="U20">
-        <v>1.0050915847959946E-2</v>
+        <v>1.1062555244488882E-2</v>
       </c>
       <c r="V20">
-        <v>-5.1491931233060232E-4</v>
+        <v>3.6270987142162639E-5</v>
       </c>
       <c r="W20">
-        <v>-3.0477314427670051E-3</v>
+        <v>-1.7207985429710314E-3</v>
       </c>
       <c r="X20">
-        <v>-2.2915330975580555E-3</v>
+        <v>-1.2511931795811603E-3</v>
       </c>
       <c r="Y20">
-        <v>-1.9578346124337682E-4</v>
+        <v>-1.1648270404496829E-4</v>
       </c>
       <c r="Z20">
-        <v>2.5149253368577718E-5</v>
+        <v>-9.1157146145567593E-5</v>
       </c>
       <c r="AA20">
-        <v>-2.0291917157290299E-4</v>
+        <v>-1.876296755375516E-4</v>
       </c>
       <c r="AB20">
-        <v>-2.5720332576280834E-4</v>
+        <v>-3.4342611794038226E-4</v>
       </c>
       <c r="AC20">
-        <v>-1.2844312019069193E-5</v>
+        <v>-1.883640037831051E-5</v>
       </c>
       <c r="AD20">
-        <v>-5.4075776226834658E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+        <v>-1.7379193348604857E-4</v>
+      </c>
+      <c r="AE20">
+        <v>4.3936719746557685E-4</v>
+      </c>
+      <c r="AF20">
+        <v>-7.0241072223157044E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A21" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B21">
-        <v>6.9277648837905423E-2</v>
+      <c r="B21" s="6">
+        <v>0.121838020751528</v>
       </c>
       <c r="C21">
-        <v>-1.1703242075174767E-4</v>
+        <v>-8.6828576679871556E-5</v>
       </c>
       <c r="D21">
-        <v>1.0811929010068969E-6</v>
+        <v>7.5321982589755599E-7</v>
       </c>
       <c r="E21">
-        <v>1.5656079715241288E-3</v>
+        <v>1.4156587835665555E-4</v>
       </c>
       <c r="F21">
-        <v>1.2471614351456843E-3</v>
+        <v>5.958112915693261E-5</v>
       </c>
       <c r="G21">
-        <v>-6.3279282224828928E-4</v>
+        <v>2.6963927923996217E-4</v>
       </c>
       <c r="H21">
-        <v>-6.6522848859453931E-4</v>
+        <v>1.6835683715023817E-4</v>
       </c>
       <c r="I21">
-        <v>-8.094556619024874E-4</v>
+        <v>-4.6847858209746965E-4</v>
       </c>
       <c r="J21">
-        <v>-6.8473171829057638E-4</v>
+        <v>-6.0470790873334607E-4</v>
       </c>
       <c r="K21">
-        <v>-1.182032868694843E-3</v>
+        <v>-4.1726804656912436E-4</v>
       </c>
       <c r="L21">
-        <v>-2.4389010431272295E-3</v>
+        <v>-1.529367706243645E-3</v>
       </c>
       <c r="M21">
-        <v>-2.0533978396159174E-4</v>
+        <v>-5.2484022208679497E-5</v>
       </c>
       <c r="N21">
-        <v>-2.9520125029034697E-4</v>
+        <v>3.2570622550372863E-4</v>
       </c>
       <c r="O21">
-        <v>1.333663307419815E-3</v>
+        <v>6.5817675016175249E-4</v>
       </c>
       <c r="P21">
-        <v>3.276139209885268E-3</v>
+        <v>1.6985492030455874E-3</v>
       </c>
       <c r="Q21">
-        <v>-4.0808413860297352E-4</v>
+        <v>-8.736325616601586E-5</v>
       </c>
       <c r="R21">
-        <v>-2.1204830238096824E-3</v>
+        <v>-1.4715610271889585E-3</v>
       </c>
       <c r="S21">
-        <v>9.3517585576234264E-5</v>
+        <v>6.4009594127779895E-6</v>
       </c>
       <c r="T21">
-        <v>2.4316971072638346E-4</v>
+        <v>-2.5268192319176917E-6</v>
       </c>
       <c r="U21">
-        <v>-5.1491931233060232E-4</v>
+        <v>3.6270987142162639E-5</v>
       </c>
       <c r="V21">
-        <v>1.2166200404358613E-2</v>
+        <v>7.43756815166941E-3</v>
       </c>
       <c r="W21">
-        <v>-6.8057387884378373E-4</v>
+        <v>-7.0756571271103066E-5</v>
       </c>
       <c r="X21">
-        <v>5.5700373234102265E-3</v>
+        <v>2.964706023490157E-3</v>
       </c>
       <c r="Y21">
-        <v>5.6987684747813409E-4</v>
+        <v>2.5322484586111832E-4</v>
       </c>
       <c r="Z21">
-        <v>-1.1444119180857794E-3</v>
+        <v>-5.4010248219539211E-4</v>
       </c>
       <c r="AA21">
-        <v>8.7506733420306343E-4</v>
+        <v>3.673412259979662E-4</v>
       </c>
       <c r="AB21">
-        <v>9.3158117872527819E-4</v>
+        <v>3.0359173745203604E-4</v>
       </c>
       <c r="AC21">
-        <v>-7.3878948049232475E-5</v>
+        <v>2.3424620971051101E-5</v>
       </c>
       <c r="AD21">
-        <v>-2.1330430140486314E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+        <v>-1.9573707715641805E-4</v>
+      </c>
+      <c r="AE21">
+        <v>-3.6007183812123626E-4</v>
+      </c>
+      <c r="AF21">
+        <v>-1.4525435374599706E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A22" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B22">
-        <v>0.10073500700749992</v>
+      <c r="B22" s="6">
+        <v>4.8841582820636296E-2</v>
       </c>
       <c r="C22">
-        <v>3.5562492979773888E-5</v>
+        <v>5.6033772668763427E-6</v>
       </c>
       <c r="D22">
-        <v>-4.5616439824163679E-7</v>
+        <v>-1.9887492688959488E-7</v>
       </c>
       <c r="E22">
-        <v>1.0004135531202726E-3</v>
+        <v>6.0495340076359753E-4</v>
       </c>
       <c r="F22">
-        <v>8.8404302163382282E-4</v>
+        <v>4.7161838033296248E-4</v>
       </c>
       <c r="G22">
-        <v>-1.0858683861084794E-4</v>
+        <v>-2.8819023666126721E-4</v>
       </c>
       <c r="H22">
-        <v>-5.3761010221849148E-4</v>
+        <v>-5.7269361997556805E-4</v>
       </c>
       <c r="I22">
-        <v>-4.991821197399503E-4</v>
+        <v>-4.4648999861516821E-4</v>
       </c>
       <c r="J22">
-        <v>-3.3135889764255016E-4</v>
+        <v>-4.5395227357255511E-4</v>
       </c>
       <c r="K22">
-        <v>-5.6763927368720733E-4</v>
+        <v>-4.3558793867004217E-4</v>
       </c>
       <c r="L22">
-        <v>-4.0253704256630845E-4</v>
+        <v>-2.3887179596480956E-4</v>
       </c>
       <c r="M22">
-        <v>-1.1609686175027012E-4</v>
+        <v>-3.869312658970846E-5</v>
       </c>
       <c r="N22">
-        <v>-6.5274850547636864E-5</v>
+        <v>-2.0490873908365773E-5</v>
       </c>
       <c r="O22">
-        <v>4.0286685592567836E-4</v>
+        <v>3.8607938541636029E-4</v>
       </c>
       <c r="P22">
-        <v>-2.140690925875309E-4</v>
+        <v>-2.9247063465830526E-4</v>
       </c>
       <c r="Q22">
-        <v>7.4856035080885763E-5</v>
+        <v>3.7064700973434933E-5</v>
       </c>
       <c r="R22">
-        <v>-3.4265686340309897E-3</v>
+        <v>-3.0390844234498169E-3</v>
       </c>
       <c r="S22">
-        <v>-1.0476425617399281E-5</v>
+        <v>-5.508485428054116E-6</v>
       </c>
       <c r="T22">
-        <v>-7.3884969462822872E-5</v>
+        <v>-1.3629190507534207E-4</v>
       </c>
       <c r="U22">
-        <v>-3.0477314427670051E-3</v>
+        <v>-1.7207985429710314E-3</v>
       </c>
       <c r="V22">
-        <v>-6.8057387884378373E-4</v>
+        <v>-7.0756571271103066E-5</v>
       </c>
       <c r="W22">
-        <v>9.2040020012829158E-3</v>
+        <v>7.2025824783844639E-3</v>
       </c>
       <c r="X22">
-        <v>4.3464039484070469E-3</v>
+        <v>3.6837546602804441E-3</v>
       </c>
       <c r="Y22">
-        <v>4.855377991489236E-4</v>
+        <v>3.7740068688005572E-4</v>
       </c>
       <c r="Z22">
-        <v>3.7032167781069012E-4</v>
+        <v>2.5650010608507817E-4</v>
       </c>
       <c r="AA22">
-        <v>4.4897902018601232E-4</v>
+        <v>6.5572720413938903E-4</v>
       </c>
       <c r="AB22">
-        <v>1.7754652076213372E-4</v>
+        <v>4.1525225316789188E-4</v>
       </c>
       <c r="AC22">
-        <v>-9.6691330930080905E-5</v>
+        <v>-5.208493562665456E-5</v>
       </c>
       <c r="AD22">
-        <v>-4.1545881314521164E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+        <v>1.3766331361539784E-4</v>
+      </c>
+      <c r="AE22">
+        <v>-5.149452788454611E-4</v>
+      </c>
+      <c r="AF22">
+        <v>-2.82066528247877E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A23" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B23">
-        <v>0.13420474980197539</v>
+      <c r="B23" s="6">
+        <v>7.1063277172599054E-2</v>
       </c>
       <c r="C23">
-        <v>4.8445654155235881E-6</v>
+        <v>3.1592115263134424E-5</v>
       </c>
       <c r="D23">
-        <v>-8.1921663266900431E-7</v>
+        <v>-8.3815158119837034E-7</v>
       </c>
       <c r="E23">
-        <v>1.5549676921342603E-3</v>
+        <v>3.8207794346629406E-4</v>
       </c>
       <c r="F23">
-        <v>1.3690305106246982E-3</v>
+        <v>3.1916844547943399E-4</v>
       </c>
       <c r="G23">
-        <v>-1.0439006385994816E-3</v>
+        <v>-1.5355886403261903E-4</v>
       </c>
       <c r="H23">
-        <v>-1.3675002865126391E-3</v>
+        <v>-5.0009962350374164E-4</v>
       </c>
       <c r="I23">
-        <v>3.8320532433007599E-4</v>
+        <v>2.6949544311344765E-4</v>
       </c>
       <c r="J23">
-        <v>3.544836695168448E-4</v>
+        <v>1.4639374313599532E-5</v>
       </c>
       <c r="K23">
-        <v>1.6238979545381976E-4</v>
+        <v>3.4435298999307626E-4</v>
       </c>
       <c r="L23">
-        <v>2.6113494516881441E-4</v>
+        <v>1.6980301738517669E-4</v>
       </c>
       <c r="M23">
-        <v>9.3115341180752004E-6</v>
+        <v>4.2132878727692182E-5</v>
       </c>
       <c r="N23">
-        <v>-7.3553511535314831E-5</v>
+        <v>3.1184041461505244E-4</v>
       </c>
       <c r="O23">
-        <v>1.0125684411239552E-3</v>
+        <v>5.6126184562425591E-4</v>
       </c>
       <c r="P23">
-        <v>8.4976324766813504E-4</v>
+        <v>3.891434345454632E-4</v>
       </c>
       <c r="Q23">
-        <v>-2.7157104340804112E-4</v>
+        <v>-6.7991644484844934E-5</v>
       </c>
       <c r="R23">
-        <v>-4.1369115802127772E-3</v>
+        <v>-3.1956907797417037E-3</v>
       </c>
       <c r="S23">
-        <v>6.6509203507857467E-5</v>
+        <v>1.7414394241457242E-5</v>
       </c>
       <c r="T23">
-        <v>-2.3239592524659748E-4</v>
+        <v>-9.9560195731323458E-5</v>
       </c>
       <c r="U23">
-        <v>-2.2915330975580555E-3</v>
+        <v>-1.2511931795811603E-3</v>
       </c>
       <c r="V23">
-        <v>5.5700373234102265E-3</v>
+        <v>2.964706023490157E-3</v>
       </c>
       <c r="W23">
-        <v>4.3464039484070469E-3</v>
+        <v>3.6837546602804441E-3</v>
       </c>
       <c r="X23">
-        <v>9.7668485291287806E-3</v>
+        <v>6.7467776806360855E-3</v>
       </c>
       <c r="Y23">
-        <v>9.5228847340313877E-4</v>
+        <v>6.2871228508174426E-4</v>
       </c>
       <c r="Z23">
-        <v>-5.5228433936440084E-4</v>
+        <v>-2.0443344268174926E-4</v>
       </c>
       <c r="AA23">
-        <v>5.0948746586026343E-4</v>
+        <v>1.9021643112358214E-4</v>
       </c>
       <c r="AB23">
-        <v>2.9521825683501146E-4</v>
+        <v>2.034172811666516E-5</v>
       </c>
       <c r="AC23">
-        <v>-1.1605389468358532E-4</v>
+        <v>-3.041786178558303E-5</v>
       </c>
       <c r="AD23">
-        <v>-5.2951395879393438E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+        <v>-8.9496605842125706E-5</v>
+      </c>
+      <c r="AE23">
+        <v>-2.4927042735509966E-4</v>
+      </c>
+      <c r="AF23">
+        <v>-4.9706930070755216E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A24" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B24">
-        <v>1.0425169133388675E-2</v>
+      <c r="B24" s="6">
+        <v>-1.6056631313754513E-3</v>
       </c>
       <c r="C24">
-        <v>-1.0789094434702941E-5</v>
+        <v>-1.7480759087325443E-6</v>
       </c>
       <c r="D24">
-        <v>1.217690790768251E-7</v>
+        <v>3.7341272887660509E-8</v>
       </c>
       <c r="E24">
-        <v>1.6324932452880123E-4</v>
+        <v>3.3716480888306905E-5</v>
       </c>
       <c r="F24">
-        <v>1.9067726172473167E-4</v>
+        <v>6.2959755369157135E-5</v>
       </c>
       <c r="G24">
-        <v>-1.4875567846115985E-4</v>
+        <v>-2.8207570451666294E-5</v>
       </c>
       <c r="H24">
-        <v>-1.8010983994015849E-4</v>
+        <v>-6.5483718816112762E-5</v>
       </c>
       <c r="I24">
-        <v>2.4325755546735082E-5</v>
+        <v>2.6329715831874094E-6</v>
       </c>
       <c r="J24">
-        <v>-2.6493523982369049E-6</v>
+        <v>-3.6961832179721848E-5</v>
       </c>
       <c r="K24">
-        <v>-7.9114542007616728E-5</v>
+        <v>-3.2564893657812148E-5</v>
       </c>
       <c r="L24">
-        <v>-5.4368161401392833E-5</v>
+        <v>-6.0991293261990578E-5</v>
       </c>
       <c r="M24">
-        <v>-2.5415063411910044E-5</v>
+        <v>-1.1375745144313093E-5</v>
       </c>
       <c r="N24">
-        <v>-9.0642850717894395E-5</v>
+        <v>-1.8429574757362752E-5</v>
       </c>
       <c r="O24">
-        <v>3.9695959474735176E-5</v>
+        <v>5.4850684495358403E-6</v>
       </c>
       <c r="P24">
-        <v>-1.8777143649765633E-5</v>
+        <v>-1.3333444828734315E-5</v>
       </c>
       <c r="Q24">
-        <v>-4.4994713610867822E-5</v>
+        <v>-1.0534659439876739E-5</v>
       </c>
       <c r="R24">
-        <v>5.1879118133475071E-5</v>
+        <v>8.3712209323960726E-5</v>
       </c>
       <c r="S24">
-        <v>1.1262642810457851E-6</v>
+        <v>-1.7897333179004016E-6</v>
       </c>
       <c r="T24">
-        <v>9.7170873684056538E-6</v>
+        <v>8.1949753938475559E-6</v>
       </c>
       <c r="U24">
-        <v>-1.9578346124337682E-4</v>
+        <v>-1.1648270404496829E-4</v>
       </c>
       <c r="V24">
-        <v>5.6987684747813409E-4</v>
+        <v>2.5322484586111832E-4</v>
       </c>
       <c r="W24">
-        <v>4.855377991489236E-4</v>
+        <v>3.7740068688005572E-4</v>
       </c>
       <c r="X24">
-        <v>9.5228847340313877E-4</v>
+        <v>6.2871228508174426E-4</v>
       </c>
       <c r="Y24">
-        <v>1.8694502156270726E-4</v>
+        <v>1.2978000330473194E-4</v>
       </c>
       <c r="Z24">
-        <v>-1.055113583827668E-4</v>
+        <v>-5.4050717704613418E-5</v>
       </c>
       <c r="AA24">
-        <v>8.7740746748453326E-5</v>
+        <v>-5.9636800667873862E-6</v>
       </c>
       <c r="AB24">
-        <v>7.1130049674921381E-5</v>
+        <v>-2.6450074907785506E-5</v>
       </c>
       <c r="AC24">
-        <v>-2.3293318571912538E-5</v>
+        <v>-8.7826889219226761E-6</v>
       </c>
       <c r="AD24">
-        <v>-6.3525598374882084E-4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+        <v>-4.4785233923195612E-5</v>
+      </c>
+      <c r="AE24">
+        <v>-1.9539318806478264E-5</v>
+      </c>
+      <c r="AF24">
+        <v>-6.4628039760338712E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A25" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B25">
-        <v>1.3713605585915707E-2</v>
+      <c r="B25" s="6">
+        <v>1.326649360774429E-2</v>
       </c>
       <c r="C25">
-        <v>-6.6537400118598603E-7</v>
+        <v>6.0230660932944317E-7</v>
       </c>
       <c r="D25">
-        <v>-4.184032750873903E-8</v>
+        <v>-3.7792549415255948E-8</v>
       </c>
       <c r="E25">
-        <v>-1.2963511929662769E-4</v>
+        <v>4.019255945485821E-5</v>
       </c>
       <c r="F25">
-        <v>-1.0244870217883265E-4</v>
+        <v>3.4880444615807806E-5</v>
       </c>
       <c r="G25">
-        <v>1.3723838307930764E-4</v>
+        <v>-1.2758712518292572E-5</v>
       </c>
       <c r="H25">
-        <v>1.1214935404203205E-4</v>
+        <v>-3.1114043569524122E-5</v>
       </c>
       <c r="I25">
-        <v>1.3552570931533439E-4</v>
+        <v>8.3198032451868055E-5</v>
       </c>
       <c r="J25">
-        <v>9.1198628244385351E-5</v>
+        <v>7.3635548324031371E-5</v>
       </c>
       <c r="K25">
-        <v>1.5189485411922421E-4</v>
+        <v>2.4036495030395187E-5</v>
       </c>
       <c r="L25">
-        <v>2.1382809066022791E-4</v>
+        <v>1.1169315681604857E-4</v>
       </c>
       <c r="M25">
-        <v>2.2363984031337076E-5</v>
+        <v>1.6912900297234756E-5</v>
       </c>
       <c r="N25">
-        <v>1.4768048594308343E-4</v>
+        <v>3.6984886528809378E-5</v>
       </c>
       <c r="O25">
-        <v>-7.9495714688689316E-6</v>
+        <v>6.3653670861337384E-5</v>
       </c>
       <c r="P25">
-        <v>-1.9661844580047704E-4</v>
+        <v>-2.7471380818892312E-5</v>
       </c>
       <c r="Q25">
-        <v>6.5089878391042181E-5</v>
+        <v>1.6336696564624869E-5</v>
       </c>
       <c r="R25">
-        <v>-2.4562307668481018E-4</v>
+        <v>-2.2678699726700501E-4</v>
       </c>
       <c r="S25">
-        <v>-5.4033571737770631E-6</v>
+        <v>4.47205641020785E-6</v>
       </c>
       <c r="T25">
-        <v>-9.0344119608238476E-6</v>
+        <v>2.0112114400324812E-5</v>
       </c>
       <c r="U25">
-        <v>2.5149253368577718E-5</v>
+        <v>-9.1157146145567593E-5</v>
       </c>
       <c r="V25">
-        <v>-1.1444119180857794E-3</v>
+        <v>-5.4010248219539211E-4</v>
       </c>
       <c r="W25">
-        <v>3.7032167781069012E-4</v>
+        <v>2.5650010608507817E-4</v>
       </c>
       <c r="X25">
-        <v>-5.5228433936440084E-4</v>
+        <v>-2.0443344268174926E-4</v>
       </c>
       <c r="Y25">
-        <v>-1.055113583827668E-4</v>
+        <v>-5.4050717704613418E-5</v>
       </c>
       <c r="Z25">
-        <v>2.0787047892130314E-4</v>
+        <v>1.0819013542893667E-4</v>
       </c>
       <c r="AA25">
-        <v>-1.1369874252412641E-4</v>
+        <v>7.7057617156492094E-7</v>
       </c>
       <c r="AB25">
-        <v>-1.1681194912551785E-4</v>
+        <v>-7.6236477738046531E-7</v>
       </c>
       <c r="AC25">
-        <v>1.1710248689744465E-5</v>
+        <v>1.8691543521497074E-6</v>
       </c>
       <c r="AD25">
-        <v>5.5594983569445073E-4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+        <v>-1.6092489193543792E-5</v>
+      </c>
+      <c r="AE25">
+        <v>2.3490822704119572E-5</v>
+      </c>
+      <c r="AF25">
+        <v>2.6664198818527815E-4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A26" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B26">
-        <v>9.2935726465997098E-2</v>
+      <c r="B26" s="6">
+        <v>0.1120318679808866</v>
       </c>
       <c r="C26">
-        <v>-1.6301977568594335E-4</v>
+        <v>-1.6278069639933529E-4</v>
       </c>
       <c r="D26">
-        <v>1.3295155588514075E-6</v>
+        <v>1.330686073849671E-6</v>
       </c>
       <c r="E26">
-        <v>4.0350009458330651E-4</v>
+        <v>-1.382617427276914E-4</v>
       </c>
       <c r="F26">
-        <v>1.9402012155253436E-4</v>
+        <v>-3.321115496248226E-4</v>
       </c>
       <c r="G26">
-        <v>-1.0769515836030884E-3</v>
+        <v>-5.7809176532118011E-4</v>
       </c>
       <c r="H26">
-        <v>-9.4539293536489077E-4</v>
+        <v>-4.4218928293325772E-4</v>
       </c>
       <c r="I26">
-        <v>-7.469729753714514E-4</v>
+        <v>-3.1306227598372049E-4</v>
       </c>
       <c r="J26">
-        <v>-7.2729662155864797E-4</v>
+        <v>-3.2146510373196133E-4</v>
       </c>
       <c r="K26">
-        <v>-1.2508592232811965E-3</v>
+        <v>-3.4190334182490449E-4</v>
       </c>
       <c r="L26">
-        <v>-2.6918079367940079E-5</v>
+        <v>4.4975273226549074E-4</v>
       </c>
       <c r="M26">
-        <v>2.7105693227414632E-6</v>
+        <v>1.5714636846807391E-5</v>
       </c>
       <c r="N26">
-        <v>2.4281082814712931E-4</v>
+        <v>1.9297473281414828E-4</v>
       </c>
       <c r="O26">
-        <v>-1.7757010644623111E-4</v>
+        <v>-2.7032923240946378E-4</v>
       </c>
       <c r="P26">
-        <v>-8.9213331702589667E-4</v>
+        <v>-1.1145356779564343E-3</v>
       </c>
       <c r="Q26">
-        <v>7.585679942638231E-5</v>
+        <v>3.0852529163507387E-5</v>
       </c>
       <c r="R26">
-        <v>-3.8919172005575844E-3</v>
+        <v>-3.0109224821943943E-3</v>
       </c>
       <c r="S26">
-        <v>3.2711428563324035E-5</v>
+        <v>-9.7422932452443671E-6</v>
       </c>
       <c r="T26">
-        <v>1.1247939868356258E-4</v>
+        <v>-9.8514247948297594E-5</v>
       </c>
       <c r="U26">
-        <v>-2.0291917157290299E-4</v>
+        <v>-1.876296755375516E-4</v>
       </c>
       <c r="V26">
-        <v>8.7506733420306343E-4</v>
+        <v>3.673412259979662E-4</v>
       </c>
       <c r="W26">
-        <v>4.4897902018601232E-4</v>
+        <v>6.5572720413938903E-4</v>
       </c>
       <c r="X26">
-        <v>5.0948746586026343E-4</v>
+        <v>1.9021643112358214E-4</v>
       </c>
       <c r="Y26">
-        <v>8.7740746748453326E-5</v>
+        <v>-5.9636800667873862E-6</v>
       </c>
       <c r="Z26">
-        <v>-1.1369874252412641E-4</v>
+        <v>7.7057617156492094E-7</v>
       </c>
       <c r="AA26">
-        <v>3.6541798656902127E-3</v>
+        <v>2.9742530254816442E-3</v>
       </c>
       <c r="AB26">
-        <v>2.3452642522771875E-3</v>
+        <v>1.9631702189769409E-3</v>
       </c>
       <c r="AC26">
-        <v>-5.1339947137979514E-5</v>
+        <v>7.4919601126159977E-7</v>
       </c>
       <c r="AD26">
-        <v>3.9241069607188657E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+        <v>-2.093956694620101E-4</v>
+      </c>
+      <c r="AE26">
+        <v>-3.8680027018281392E-4</v>
+      </c>
+      <c r="AF26">
+        <v>3.5891955759971058E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A27" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B27">
-        <v>6.6579786652100903E-2</v>
+      <c r="B27" s="6">
+        <v>0.1095703465151619</v>
       </c>
       <c r="C27">
-        <v>-1.1976712083592266E-4</v>
+        <v>-1.2410676048442947E-4</v>
       </c>
       <c r="D27">
-        <v>1.080225374529677E-6</v>
+        <v>1.1107980010601134E-6</v>
       </c>
       <c r="E27">
-        <v>4.0134710336728037E-4</v>
+        <v>-9.0292619220349538E-5</v>
       </c>
       <c r="F27">
-        <v>2.3380232001760505E-4</v>
+        <v>-2.426868033559423E-4</v>
       </c>
       <c r="G27">
-        <v>-6.0990855980879192E-4</v>
+        <v>-3.1506925007231839E-4</v>
       </c>
       <c r="H27">
-        <v>-7.9691337579308697E-4</v>
+        <v>-4.183960583878407E-4</v>
       </c>
       <c r="I27">
-        <v>-5.3281578227960293E-4</v>
+        <v>-2.3608828496797258E-4</v>
       </c>
       <c r="J27">
-        <v>-3.247180481061613E-4</v>
+        <v>-9.267894295989388E-5</v>
       </c>
       <c r="K27">
-        <v>-6.4055121589923908E-4</v>
+        <v>-1.4044457356431755E-5</v>
       </c>
       <c r="L27">
-        <v>-1.8324760725494521E-4</v>
+        <v>3.9100560866519446E-4</v>
       </c>
       <c r="M27">
-        <v>-1.4631156797921909E-4</v>
+        <v>-6.2195909892679997E-5</v>
       </c>
       <c r="N27">
-        <v>-9.2467141321276453E-5</v>
+        <v>-5.651113387966796E-5</v>
       </c>
       <c r="O27">
-        <v>-3.4037087998989388E-4</v>
+        <v>-3.9164398272523767E-4</v>
       </c>
       <c r="P27">
-        <v>-5.6393098015509145E-4</v>
+        <v>-8.467904557471163E-4</v>
       </c>
       <c r="Q27">
-        <v>1.0826100084275502E-4</v>
+        <v>3.2092286027092369E-5</v>
       </c>
       <c r="R27">
-        <v>-3.4223204516250893E-3</v>
+        <v>-2.6349312695134837E-3</v>
       </c>
       <c r="S27">
-        <v>1.6462988043291273E-5</v>
+        <v>-1.8459081491638084E-5</v>
       </c>
       <c r="T27">
-        <v>1.0951487704258982E-4</v>
+        <v>-3.2259292936509011E-5</v>
       </c>
       <c r="U27">
-        <v>-2.5720332576280834E-4</v>
+        <v>-3.4342611794038226E-4</v>
       </c>
       <c r="V27">
-        <v>9.3158117872527819E-4</v>
+        <v>3.0359173745203604E-4</v>
       </c>
       <c r="W27">
-        <v>1.7754652076213372E-4</v>
+        <v>4.1525225316789188E-4</v>
       </c>
       <c r="X27">
-        <v>2.9521825683501146E-4</v>
+        <v>2.034172811666516E-5</v>
       </c>
       <c r="Y27">
-        <v>7.1130049674921381E-5</v>
+        <v>-2.6450074907785506E-5</v>
       </c>
       <c r="Z27">
-        <v>-1.1681194912551785E-4</v>
+        <v>-7.6236477738046531E-7</v>
       </c>
       <c r="AA27">
-        <v>2.3452642522771875E-3</v>
+        <v>1.9631702189769409E-3</v>
       </c>
       <c r="AB27">
-        <v>2.9851284669675689E-3</v>
+        <v>2.4982086469457227E-3</v>
       </c>
       <c r="AC27">
-        <v>-7.2904382680289277E-5</v>
+        <v>-6.3395889009073377E-6</v>
       </c>
       <c r="AD27">
-        <v>2.2002207345914564E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+        <v>-2.1718936631889539E-4</v>
+      </c>
+      <c r="AE27">
+        <v>-3.2148023760755436E-4</v>
+      </c>
+      <c r="AF27">
+        <v>2.0609688265931588E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A28" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B28">
-        <v>1.1701870500059168E-3</v>
+      <c r="B28" s="6">
+        <v>5.7245119915729633E-3</v>
       </c>
       <c r="C28">
-        <v>8.9645053744355279E-6</v>
+        <v>-7.7027230271747816E-7</v>
       </c>
       <c r="D28">
-        <v>-9.9747076246547744E-8</v>
+        <v>-9.4819608590898977E-9</v>
       </c>
       <c r="E28">
-        <v>-9.5978944424619545E-5</v>
+        <v>-6.2534073427722745E-7</v>
       </c>
       <c r="F28">
-        <v>-5.8386599492620835E-5</v>
+        <v>8.9179586546010107E-6</v>
       </c>
       <c r="G28">
-        <v>2.3188929441263586E-5</v>
+        <v>-5.7084749322126237E-6</v>
       </c>
       <c r="H28">
-        <v>3.9043474136391768E-5</v>
+        <v>-5.0965279339928342E-6</v>
       </c>
       <c r="I28">
-        <v>-4.7150721942894281E-5</v>
+        <v>-1.418959104827961E-5</v>
       </c>
       <c r="J28">
-        <v>-7.6334342647537247E-5</v>
+        <v>-1.6364963557512013E-5</v>
       </c>
       <c r="K28">
-        <v>-2.5523155140404815E-5</v>
+        <v>-2.7788521319121063E-5</v>
       </c>
       <c r="L28">
-        <v>3.341727545061934E-5</v>
+        <v>1.4327190755126227E-5</v>
       </c>
       <c r="M28">
-        <v>2.1489696286698217E-5</v>
+        <v>1.0003560389292667E-5</v>
       </c>
       <c r="N28">
-        <v>3.7597769021241272E-5</v>
+        <v>9.0821070093710489E-6</v>
       </c>
       <c r="O28">
-        <v>-4.2271292836679414E-5</v>
+        <v>-3.2658021992503167E-5</v>
       </c>
       <c r="P28">
-        <v>1.1619804629672175E-5</v>
+        <v>-5.5821331285881506E-5</v>
       </c>
       <c r="Q28">
-        <v>-5.161565956071274E-5</v>
+        <v>-7.1061945715503687E-7</v>
       </c>
       <c r="R28">
-        <v>-7.3379171140614636E-5</v>
+        <v>-9.7111117685139966E-5</v>
       </c>
       <c r="S28">
-        <v>2.5805263150591864E-6</v>
+        <v>1.9447174780393602E-6</v>
       </c>
       <c r="T28">
-        <v>-1.690465334121022E-5</v>
+        <v>4.8426370600201393E-6</v>
       </c>
       <c r="U28">
-        <v>-1.2844312019069193E-5</v>
+        <v>-1.883640037831051E-5</v>
       </c>
       <c r="V28">
-        <v>-7.3878948049232475E-5</v>
+        <v>2.3424620971051101E-5</v>
       </c>
       <c r="W28">
-        <v>-9.6691330930080905E-5</v>
+        <v>-5.208493562665456E-5</v>
       </c>
       <c r="X28">
-        <v>-1.1605389468358532E-4</v>
+        <v>-3.041786178558303E-5</v>
       </c>
       <c r="Y28">
-        <v>-2.3293318571912538E-5</v>
+        <v>-8.7826889219226761E-6</v>
       </c>
       <c r="Z28">
-        <v>1.1710248689744465E-5</v>
+        <v>1.8691543521497074E-6</v>
       </c>
       <c r="AA28">
-        <v>-5.1339947137979514E-5</v>
+        <v>7.4919601126159977E-7</v>
       </c>
       <c r="AB28">
-        <v>-7.2904382680289277E-5</v>
+        <v>-6.3395889009073377E-6</v>
       </c>
       <c r="AC28">
-        <v>5.1729755302335621E-5</v>
+        <v>2.1811742564139184E-5</v>
       </c>
       <c r="AD28">
-        <v>-5.3555979586122524E-4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+        <v>-8.3071400007780525E-5</v>
+      </c>
+      <c r="AE28">
+        <v>-9.4632068167563741E-5</v>
+      </c>
+      <c r="AF28">
+        <v>-1.8584975382335584E-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A29" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="6">
+        <v>-0.15788292867079554</v>
+      </c>
+      <c r="C29">
+        <v>7.3861203519133718E-5</v>
+      </c>
+      <c r="D29">
+        <v>-5.9645218572987454E-7</v>
+      </c>
+      <c r="E29">
+        <v>-3.1101141959164987E-4</v>
+      </c>
+      <c r="F29">
+        <v>-3.6062266910151563E-4</v>
+      </c>
+      <c r="G29">
+        <v>5.5021923632297639E-4</v>
+      </c>
+      <c r="H29">
+        <v>5.5724840539350662E-4</v>
+      </c>
+      <c r="I29">
+        <v>-4.1852157777738088E-4</v>
+      </c>
+      <c r="J29">
+        <v>-6.85214328265237E-4</v>
+      </c>
+      <c r="K29">
+        <v>-4.3587908494871133E-4</v>
+      </c>
+      <c r="L29">
+        <v>-1.1987249616369157E-3</v>
+      </c>
+      <c r="M29">
+        <v>2.7107958978974853E-4</v>
+      </c>
+      <c r="N29">
+        <v>1.670013450360284E-4</v>
+      </c>
+      <c r="O29">
+        <v>2.4564227627467113E-4</v>
+      </c>
+      <c r="P29">
+        <v>1.9318716798235715E-3</v>
+      </c>
+      <c r="Q29">
+        <v>-1.1363367262163333E-4</v>
+      </c>
+      <c r="R29">
+        <v>-1.0869192201384682E-3</v>
+      </c>
+      <c r="S29">
+        <v>-2.1557183881715188E-6</v>
+      </c>
+      <c r="T29">
+        <v>-1.309750727520884E-4</v>
+      </c>
+      <c r="U29">
+        <v>-1.7379193348604857E-4</v>
+      </c>
+      <c r="V29">
+        <v>-1.9573707715641805E-4</v>
+      </c>
+      <c r="W29">
+        <v>1.3766331361539784E-4</v>
+      </c>
+      <c r="X29">
+        <v>-8.9496605842125706E-5</v>
+      </c>
+      <c r="Y29">
+        <v>-4.4785233923195612E-5</v>
+      </c>
+      <c r="Z29">
+        <v>-1.6092489193543792E-5</v>
+      </c>
+      <c r="AA29">
+        <v>-2.093956694620101E-4</v>
+      </c>
+      <c r="AB29">
+        <v>-2.1718936631889539E-4</v>
+      </c>
+      <c r="AC29">
+        <v>-8.3071400007780525E-5</v>
+      </c>
+      <c r="AD29">
+        <v>6.4012855192838664E-3</v>
+      </c>
+      <c r="AE29">
+        <v>7.4792788943191062E-4</v>
+      </c>
+      <c r="AF29">
+        <v>-4.7813878870329974E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A30" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="6">
+        <v>1.595480770393766E-2</v>
+      </c>
+      <c r="C30">
+        <v>-1.0199386846639481E-5</v>
+      </c>
+      <c r="D30">
+        <v>1.6152166128984766E-8</v>
+      </c>
+      <c r="E30">
+        <v>1.688453077583437E-4</v>
+      </c>
+      <c r="F30">
+        <v>-1.7795515442782376E-4</v>
+      </c>
+      <c r="G30">
+        <v>5.3537751378341866E-4</v>
+      </c>
+      <c r="H30">
+        <v>7.0228396192561419E-4</v>
+      </c>
+      <c r="I30">
+        <v>3.57202351989105E-4</v>
+      </c>
+      <c r="J30">
+        <v>5.3365507672991589E-4</v>
+      </c>
+      <c r="K30">
+        <v>-2.9229407498307424E-4</v>
+      </c>
+      <c r="L30">
+        <v>-1.9155408470141902E-3</v>
+      </c>
+      <c r="M30">
+        <v>1.0685435631157039E-4</v>
+      </c>
+      <c r="N30">
+        <v>-1.7977426763165735E-4</v>
+      </c>
+      <c r="O30">
+        <v>4.1817895296336984E-4</v>
+      </c>
+      <c r="P30">
+        <v>2.8159004844021136E-3</v>
+      </c>
+      <c r="Q30">
+        <v>-9.9841858933966658E-5</v>
+      </c>
+      <c r="R30">
+        <v>-2.2860814667542127E-3</v>
+      </c>
+      <c r="S30">
+        <v>4.8547083869859043E-5</v>
+      </c>
+      <c r="T30">
+        <v>-2.9378064998808072E-4</v>
+      </c>
+      <c r="U30">
+        <v>4.3936719746557685E-4</v>
+      </c>
+      <c r="V30">
+        <v>-3.6007183812123626E-4</v>
+      </c>
+      <c r="W30">
+        <v>-5.149452788454611E-4</v>
+      </c>
+      <c r="X30">
+        <v>-2.4927042735509966E-4</v>
+      </c>
+      <c r="Y30">
+        <v>-1.9539318806478264E-5</v>
+      </c>
+      <c r="Z30">
+        <v>2.3490822704119572E-5</v>
+      </c>
+      <c r="AA30">
+        <v>-3.8680027018281392E-4</v>
+      </c>
+      <c r="AB30">
+        <v>-3.2148023760755436E-4</v>
+      </c>
+      <c r="AC30">
+        <v>-9.4632068167563741E-5</v>
+      </c>
+      <c r="AD30">
+        <v>7.4792788943191062E-4</v>
+      </c>
+      <c r="AE30">
+        <v>8.8607638905623121E-3</v>
+      </c>
+      <c r="AF30">
+        <v>1.8607345380785736E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A31" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B29">
-        <v>-1.8125428137724202</v>
-      </c>
-      <c r="C29">
-        <v>-3.3567715897170553E-3</v>
-      </c>
-      <c r="D29">
-        <v>2.7253982962244117E-5</v>
-      </c>
-      <c r="E29">
-        <v>2.1705805698139639E-4</v>
-      </c>
-      <c r="F29">
-        <v>-9.3402746847200862E-4</v>
-      </c>
-      <c r="G29">
-        <v>-4.0786374833639855E-3</v>
-      </c>
-      <c r="H29">
-        <v>-5.3455214883186882E-3</v>
-      </c>
-      <c r="I29">
-        <v>-5.1217426009654635E-3</v>
-      </c>
-      <c r="J29">
-        <v>-5.437005993848356E-3</v>
-      </c>
-      <c r="K29">
-        <v>-9.5902606281384403E-3</v>
-      </c>
-      <c r="L29">
-        <v>-3.5077769015876229E-3</v>
-      </c>
-      <c r="M29">
-        <v>-1.9969395063206882E-3</v>
-      </c>
-      <c r="N29">
-        <v>-1.0923856990754553E-4</v>
-      </c>
-      <c r="O29">
-        <v>-5.0740718635921356E-3</v>
-      </c>
-      <c r="P29">
-        <v>-1.1331071096443568E-2</v>
-      </c>
-      <c r="Q29">
-        <v>9.8102780865993631E-4</v>
-      </c>
-      <c r="R29">
-        <v>-2.0867279269172291E-2</v>
-      </c>
-      <c r="S29">
-        <v>3.2977410859307742E-4</v>
-      </c>
-      <c r="T29">
-        <v>-4.2951510406001592E-4</v>
-      </c>
-      <c r="U29">
-        <v>-5.4075776226834658E-3</v>
-      </c>
-      <c r="V29">
-        <v>-2.1330430140486314E-3</v>
-      </c>
-      <c r="W29">
-        <v>-4.1545881314521164E-3</v>
-      </c>
-      <c r="X29">
-        <v>-5.2951395879393438E-3</v>
-      </c>
-      <c r="Y29">
-        <v>-6.3525598374882084E-4</v>
-      </c>
-      <c r="Z29">
-        <v>5.5594983569445073E-4</v>
-      </c>
-      <c r="AA29">
-        <v>3.9241069607188657E-3</v>
-      </c>
-      <c r="AB29">
-        <v>2.2002207345914564E-3</v>
-      </c>
-      <c r="AC29">
-        <v>-5.3555979586122524E-4</v>
-      </c>
-      <c r="AD29">
-        <v>0.12193860458538452</v>
+      <c r="B31" s="6">
+        <v>-1.4870662721503085</v>
+      </c>
+      <c r="C31">
+        <v>-2.7346799284920782E-3</v>
+      </c>
+      <c r="D31">
+        <v>2.218125414983913E-5</v>
+      </c>
+      <c r="E31">
+        <v>-8.1754932110142679E-4</v>
+      </c>
+      <c r="F31">
+        <v>-1.3217627658550005E-3</v>
+      </c>
+      <c r="G31">
+        <v>-2.4405821502499329E-3</v>
+      </c>
+      <c r="H31">
+        <v>-2.0514615009544069E-3</v>
+      </c>
+      <c r="I31">
+        <v>-5.3412942072990476E-3</v>
+      </c>
+      <c r="J31">
+        <v>-5.6799468728162671E-3</v>
+      </c>
+      <c r="K31">
+        <v>-7.8936396648088894E-3</v>
+      </c>
+      <c r="L31">
+        <v>-3.1782711808574721E-3</v>
+      </c>
+      <c r="M31">
+        <v>-2.0176602850587051E-3</v>
+      </c>
+      <c r="N31">
+        <v>-3.6286374658167495E-4</v>
+      </c>
+      <c r="O31">
+        <v>-3.5969623343463175E-3</v>
+      </c>
+      <c r="P31">
+        <v>-8.5713684056973709E-3</v>
+      </c>
+      <c r="Q31">
+        <v>-4.0998497993821197E-4</v>
+      </c>
+      <c r="R31">
+        <v>-2.1584184721224711E-2</v>
+      </c>
+      <c r="S31">
+        <v>1.8371319804637141E-4</v>
+      </c>
+      <c r="T31">
+        <v>-2.2626621473227451E-3</v>
+      </c>
+      <c r="U31">
+        <v>-7.0241072223157044E-4</v>
+      </c>
+      <c r="V31">
+        <v>-1.4525435374599706E-3</v>
+      </c>
+      <c r="W31">
+        <v>-2.82066528247877E-3</v>
+      </c>
+      <c r="X31">
+        <v>-4.9706930070755216E-3</v>
+      </c>
+      <c r="Y31">
+        <v>-6.4628039760338712E-4</v>
+      </c>
+      <c r="Z31">
+        <v>2.6664198818527815E-4</v>
+      </c>
+      <c r="AA31">
+        <v>3.5891955759971058E-3</v>
+      </c>
+      <c r="AB31">
+        <v>2.0609688265931588E-3</v>
+      </c>
+      <c r="AC31">
+        <v>-1.8584975382335584E-4</v>
+      </c>
+      <c r="AD31">
+        <v>-4.7813878870329974E-4</v>
+      </c>
+      <c r="AE31">
+        <v>1.8607345380785736E-3</v>
+      </c>
+      <c r="AF31">
+        <v>9.9305799818477869E-2</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_partnership.xlsx
+++ b/input/reg_partnership.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1735D7DD-014E-456C-A71F-AD948DED9179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDB7C9D-0F10-4B71-85A7-FE50BBF76BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -221,16 +221,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -249,14 +240,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -275,11 +259,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -626,10 +608,10 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -658,7 +640,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B10" t="s">
@@ -672,7 +654,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="18.265625" customWidth="1"/>
@@ -965,26 +947,6 @@
       <c r="J9">
         <v>63.225347536917525</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3856,7 +3818,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AG33"/>
+  <dimension ref="A1:AG32"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="41.1328125" customWidth="1"/>
@@ -7094,10 +7056,6 @@
         <v>0.10601873046600838</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A33" s="1"/>
-      <c r="B33" s="2"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
